--- a/data/台股_警戒掃描.xlsx
+++ b/data/台股_警戒掃描.xlsx
@@ -10,8 +10,9 @@
     <sheet name="警戒總覽" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="處置股票" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="暫停交易" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="借券排行" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="下市" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="暫停融券" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="借券排行" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="下市" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,12 +513,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>30d 95450 股, 最新日 171 股</t>
+          <t>30d 88714 股, 最新日 1470 股</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -567,12 +568,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -582,55 +583,51 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>30d 222729 股, 最新日 391 股</t>
+          <t>30d 51339 股, 最新日 450 股</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>⚠️ 處置</t>
+          <t>🪦 借券爆量</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>連續三次 / 第一次處置</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-05-26 ~ 2026-06-08</t>
-        </is>
-      </c>
+          <t>30d 184965 股, 最新日 73 股</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -647,20 +644,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>🪦 借券爆量</t>
+          <t>⚠️ 處置</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>30d 80465 股, 最新日 120 股</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
+          <t>連續三次 / 第一次處置</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-05-26 ~ 2026-06-08</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>C</t>
@@ -670,12 +671,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -685,67 +686,67 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>30d 297937 股, 最新日 310 股</t>
+          <t>30d 104272 股, 最新日 30 股</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>⚠️ 處置</t>
+          <t>📉 暫停融券</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>連續五次及當日沖銷標準 / 第一次處置</t>
+          <t>除息</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-01-09 ~ 2026-01-26</t>
+          <t>~ 2026-06-10</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -755,100 +756,100 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>30d 236329 股, 最新日 5080 股</t>
+          <t>30d 299503 股, 最新日 100 股</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>🪦 借券爆量</t>
+          <t>⚠️ 處置</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>30d 113907 股, 最新日 309 股</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
+          <t>連續五次及當日沖銷標準 / 第一次處置</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-01-09 ~ 2026-01-26</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>⚠️ 處置</t>
+          <t>🪦 借券爆量</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>連續三次 / 第一次處置</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-03-03 ~ 2026-03-16</t>
-        </is>
-      </c>
+          <t>30d 178228 股, 最新日 2000 股</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -858,12 +859,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>30d 70757 股, 最新日 7 股</t>
+          <t>30d 85406 股, 最新日 136 股</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -876,12 +877,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -891,17 +892,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>最近十個營業日已有六次 / 第一次處置</t>
+          <t>連續三次 / 第一次處置</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-18 ~ 2026-07-02</t>
+          <t>2026-03-03 ~ 2026-03-16</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -913,82 +914,82 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>⚠️ 處置</t>
+          <t>🪦 借券爆量</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>最近十個營業日已有六次 / 第二次處置</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-01-09 ~ 2026-01-22</t>
-        </is>
-      </c>
+          <t>30d 50657 股, 最新日 388 股</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🪦 借券爆量</t>
+          <t>⚠️ 處置</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>30d 110061 股, 最新日 76 股</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
+          <t>最近十個營業日已有六次 / 第一次處置</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-06-18 ~ 2026-07-02</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -998,71 +999,67 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>連續三次 / 第一次處置</t>
+          <t>最近十個營業日已有六次 / 第二次處置</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-07 ~ 2026-05-20</t>
+          <t>2026-01-09 ~ 2026-01-22</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>⚠️ 處置</t>
+          <t>🪦 借券爆量</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>連續三次 / 第一次處置</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-06-01 ~ 2026-06-12</t>
-        </is>
-      </c>
+          <t>30d 81946 股, 最新日 12 股</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1072,30 +1069,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>30d 93942 股, 最新日 700 股</t>
+          <t>30d 60438 股, 最新日 345 股</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1105,7 +1102,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1115,24 +1112,24 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-20 ~ 2026-06-02</t>
+          <t>2026-05-07 ~ 2026-05-20</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>立隆電</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1142,17 +1139,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>最近10個營業日內有6個營業日 / 聯亞光電工業股份有限公司股票(代號：3081)最近30個營業日內曾發布處置，又因最近10個營業日內有6個營業日經本中心公布注意交易資訊，爰自115年3月12日起10個營業日(115年3月12日至115年3月25日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>連續三次 / 第一次處置</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-12 ~ 2026-03-25</t>
+          <t>2026-06-01 ~ 2026-06-12</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1164,49 +1161,45 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>⚠️ 處置</t>
+          <t>🪦 借券爆量</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 聯亞光電工業股份有限公司股票(代號：3081)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年02月04日起10個營業日(115年02月04日至115年02月26日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-02-04 ~ 2026-02-26</t>
-        </is>
-      </c>
+          <t>30d 81507 股, 最新日 200 股</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1216,34 +1209,34 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 聯亞光電工業股份有限公司股票(代號：3081)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年01月30日起10個營業日(115年01月30日至115年02月23日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>連續三次 / 第一次處置</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-01-30 ~ 2026-02-23</t>
+          <t>2026-05-20 ~ 2026-06-02</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1253,17 +1246,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 大綜電腦系統股份有限公司股票(代號：3147)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年6月11日起10個營業日(115年6月11日至115年6月25日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>最近10個營業日內有6個營業日 / 聯亞光電工業股份有限公司股票(代號：3081)最近30個營業日內曾發布處置，又因最近10個營業日內有6個營業日經本中心公布注意交易資訊，爰自115年3月12日起10個營業日(115年3月12日至115年3月25日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-11 ~ 2026-06-25</t>
+          <t>2026-03-12 ~ 2026-03-25</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1275,12 +1268,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1290,17 +1283,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 大綜電腦系統股份有限公司股票(代號：3147)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年6月8日起10個營業日(115年6月8日至115年6月22日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 聯亞光電工業股份有限公司股票(代號：3081)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年02月04日起10個營業日(115年02月04日至115年02月26日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-08 ~ 2026-06-22</t>
+          <t>2026-02-04 ~ 2026-02-26</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1312,45 +1305,49 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>🪦 借券爆量</t>
+          <t>⚠️ 處置</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>30d 160548 股, 最新日 5376 股</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 聯亞光電工業股份有限公司股票(代號：3081)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年01月30日起10個營業日(115年01月30日至115年02月23日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-01-30 ~ 2026-02-23</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1360,17 +1357,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 威剛科技股份有限公司股票(代號：3260)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年3月19日起10個營業日(115年3月19日至115年4月1日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 大綜電腦系統股份有限公司股票(代號：3147)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年6月11日起10個營業日(115年6月11日至115年6月25日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-19 ~ 2026-04-01</t>
+          <t>2026-06-11 ~ 2026-06-25</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1382,12 +1379,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1397,17 +1394,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>連續3個營業日及沖銷標準 / 威剛科技股份有限公司股票(代號：3260)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，且最近3個營業日曾達本中心作業要點第四條第一項第十三款經本中心公布注意交易資訊，爰自115年01月07日起12個營業日(115年01月07日至115年01月22日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 大綜電腦系統股份有限公司股票(代號：3147)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年6月8日起10個營業日(115年6月8日至115年6月22日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-01-07 ~ 2026-01-22</t>
+          <t>2026-06-08 ~ 2026-06-22</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1419,34 +1416,30 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>⚠️ 處置</t>
+          <t>🪦 借券爆量</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>連續三次 / 第一次處置</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-04-17 ~ 2026-04-30</t>
-        </is>
-      </c>
+          <t>30d 133623 股, 最新日 132 股</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>C</t>
@@ -1456,12 +1449,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1471,34 +1464,34 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>最近十個營業日已有六次 / 第一次處置</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 威剛科技股份有限公司股票(代號：3260)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年3月19日起10個營業日(115年3月19日至115年4月1日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-30 ~ 2026-07-13</t>
+          <t>2026-03-19 ~ 2026-04-01</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1508,34 +1501,34 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>連續三次 / 第一次處置</t>
+          <t>連續3個營業日及沖銷標準 / 威剛科技股份有限公司股票(代號：3260)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，且最近3個營業日曾達本中心作業要點第四條第一項第十三款經本中心公布注意交易資訊，爰自115年01月07日起12個營業日(115年01月07日至115年01月22日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-13 ~ 2026-05-26</t>
+          <t>2026-01-07 ~ 2026-01-22</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1545,7 +1538,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1555,24 +1548,24 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-14 ~ 2026-04-27</t>
+          <t>2026-04-17 ~ 2026-04-30</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1582,34 +1575,34 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>連續三次 / 第二次處置</t>
+          <t>最近十個營業日已有六次 / 第一次處置</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-13 ~ 2026-05-26</t>
+          <t>2026-06-30 ~ 2026-07-13</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1619,7 +1612,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1629,90 +1622,98 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-24 ~ 2026-05-08</t>
+          <t>2026-05-13 ~ 2026-05-26</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>🪦 借券爆量</t>
+          <t>⚠️ 處置</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>30d 65387 股, 最新日 125 股</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
+          <t>連續三次 / 第一次處置</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-04-14 ~ 2026-04-27</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>🚫 暫停</t>
+          <t>⚠️ 處置</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>暫停8:00, 恢復2026-04-29</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
+          <t>連續三次 / 第二次處置</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-05-13 ~ 2026-05-26</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1722,7 +1723,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1732,24 +1733,24 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-16 ~ 2026-04-29</t>
+          <t>2026-04-24 ~ 2026-05-08</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1759,12 +1760,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>30d 79623 股, 最新日 331 股</t>
+          <t>30d 57073 股, 最新日 876 股</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -1777,34 +1778,30 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>信立</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>⚠️ 處置</t>
+          <t>🚫 暫停</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>連續5個營業日 / 華星光通科技股份有限公司股票(代號：4979)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年6月3日起10個營業日(115年6月3日至115年6月16日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-06-03 ~ 2026-06-16</t>
-        </is>
-      </c>
+          <t>暫停8:00, 恢復2026-04-29</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
           <t>B</t>
@@ -1814,12 +1811,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>六方科-KY</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1829,17 +1826,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>連續5個營業日 / 華星光通科技股份有限公司股票(代號：4979)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年5月13日起10個營業日(115年5月13日至115年5月26日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>連續三次 / 第一次處置</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-13 ~ 2026-05-26</t>
+          <t>2026-04-16 ~ 2026-04-29</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1851,34 +1848,30 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>⚠️ 處置</t>
+          <t>🪦 借券爆量</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 華星光通科技股份有限公司股票(代號：4979)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年4月21日起10個營業日(115年4月21日至115年5月5日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-04-21 ~ 2026-05-05</t>
-        </is>
-      </c>
+          <t>30d 89312 股, 最新日 3000 股</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
           <t>B</t>
@@ -1903,17 +1896,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>連續5個營業日 / 華星光通科技股份有限公司股票(代號：4979)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年3月27日起10個營業日(115年3月27日至115年4月13日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>連續5個營業日 / 華星光通科技股份有限公司股票(代號：4979)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年6月3日起10個營業日(115年6月3日至115年6月16日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-27 ~ 2026-04-13</t>
+          <t>2026-06-03 ~ 2026-06-16</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1940,17 +1933,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>連續5個營業日 / 華星光通科技股份有限公司股票(代號：4979)因連續5個營業日經本中心公布注意交易資訊，爰自115年3月3日起10個營業日(115年3月3日至115年3月16日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>連續5個營業日 / 華星光通科技股份有限公司股票(代號：4979)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年5月13日起10個營業日(115年5月13日至115年5月26日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-03 ~ 2026-03-16</t>
+          <t>2026-05-13 ~ 2026-05-26</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1962,12 +1955,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1977,17 +1970,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>連續三次 / 第一次處置</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 華星光通科技股份有限公司股票(代號：4979)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年4月21日起10個營業日(115年4月21日至115年5月5日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-13 ~ 2026-04-24</t>
+          <t>2026-04-21 ~ 2026-05-05</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1999,12 +1992,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2014,34 +2007,34 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>最近10個營業日內有6個營業日 / 建榮工業材料股份有限公司股票(代號：5340)最近30個營業日內曾發布處置，又因最近10個營業日內有6個營業日經本中心公布注意交易資訊，爰自115年4月21日起10個營業日(115年4月21日至115年5月5日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>連續5個營業日 / 華星光通科技股份有限公司股票(代號：4979)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年3月27日起10個營業日(115年3月27日至115年4月13日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-21 ~ 2026-05-05</t>
+          <t>2026-03-27 ~ 2026-04-13</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2051,34 +2044,34 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>連續5個營業日 / 建榮工業材料股份有限公司股票(代號：5340)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年3月17日起10個營業日(115年3月17日至115年3月30日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>連續5個營業日 / 華星光通科技股份有限公司股票(代號：4979)因連續5個營業日經本中心公布注意交易資訊，爰自115年3月3日起10個營業日(115年3月3日至115年3月16日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-17 ~ 2026-03-30</t>
+          <t>2026-03-03 ~ 2026-03-16</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2088,22 +2081,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>連續5個營業日 / 建榮工業材料股份有限公司股票(代號：5340)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年2月23日起10個營業日(115年2月23日至115年3月9日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>連續三次 / 第一次處置</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-02-23 ~ 2026-03-09</t>
+          <t>2026-04-13 ~ 2026-04-24</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -2125,17 +2118,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>連續5個營業日 / 建榮工業材料股份有限公司股票(代號：5340)因連續5個營業日經本中心公布注意交易資訊，爰自115年01月22日起10個營業日(115年01月22日至115年02月04日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>最近10個營業日內有6個營業日 / 建榮工業材料股份有限公司股票(代號：5340)最近30個營業日內曾發布處置，又因最近10個營業日內有6個營業日經本中心公布注意交易資訊，爰自115年4月21日起10個營業日(115年4月21日至115年5月5日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-01-22 ~ 2026-02-04</t>
+          <t>2026-04-21 ~ 2026-05-05</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2147,12 +2140,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>建榮</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2162,34 +2155,34 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 普萊德科技股份有限公司股票(代號：6263)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年5月15日起10個營業日(115年5月15日至115年5月28日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>連續5個營業日 / 建榮工業材料股份有限公司股票(代號：5340)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年3月17日起10個營業日(115年3月17日至115年3月30日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-15 ~ 2026-05-28</t>
+          <t>2026-03-17 ~ 2026-03-30</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>建榮</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2199,34 +2192,34 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 台燿科技股份有限公司股票(代號：6274)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年5月11日起10個營業日(115年5月11日至115年5月22日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>連續5個營業日 / 建榮工業材料股份有限公司股票(代號：5340)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年2月23日起10個營業日(115年2月23日至115年3月9日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-11 ~ 2026-05-22</t>
+          <t>2026-02-23 ~ 2026-03-09</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>建榮</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2236,34 +2229,34 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 台燿科技股份有限公司股票(代號：6274)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年4月17日起10個營業日(115年4月17日至115年4月30日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>連續5個營業日 / 建榮工業材料股份有限公司股票(代號：5340)因連續5個營業日經本中心公布注意交易資訊，爰自115年01月22日起10個營業日(115年01月22日至115年02月04日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-17 ~ 2026-04-30</t>
+          <t>2026-01-22 ~ 2026-02-04</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2273,17 +2266,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>最近十個營業日已有六次 / 第一次處置</t>
+          <t>最近10個營業日內有6個營業日 / 萬潤科技股份有限公司股票(代號：6187)因最近10個營業日內有6個營業日經本中心公布注意交易資訊，爰自115年6月17日起10個營業日(115年6月17日至115年7月1日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-08 ~ 2026-06-22</t>
+          <t>2026-06-17 ~ 2026-07-01</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2295,12 +2288,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2310,17 +2303,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>最近十個營業日已有六次 / 第一次處置</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 萬潤科技股份有限公司股票(代號：6187)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年3月30日起10個營業日(115年3月30日至115年4月14日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-22 ~ 2026-05-06</t>
+          <t>2026-03-30 ~ 2026-04-14</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2332,12 +2325,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2347,17 +2340,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>連續五次 / 第二次處置</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 萬潤科技股份有限公司股票(代號：6187)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年3月6日起10個營業日(115年3月6日至115年3月19日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-09 ~ 2026-03-20</t>
+          <t>2026-03-06 ~ 2026-03-19</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2369,12 +2362,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2384,17 +2377,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>最近十個營業日已有六次 / 第一次處置</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 萬潤科技股份有限公司股票(代號：6187)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年3月3日起10個營業日(115年3月3日至115年3月16日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-04 ~ 2026-02-26</t>
+          <t>2026-03-03 ~ 2026-03-16</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2406,12 +2399,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2421,17 +2414,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>連續三次 / 第一次處置</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 普萊德科技股份有限公司股票(代號：6263)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年5月15日起10個營業日(115年5月15日至115年5月28日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-03 ~ 2026-02-25</t>
+          <t>2026-05-15 ~ 2026-05-28</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2443,30 +2436,34 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>💀 下市</t>
+          <t>⚠️ 處置</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2024-01-25</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>已下市</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 台燿科技股份有限公司股票(代號：6274)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年5月11日起10個營業日(115年5月11日至115年5月22日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-05-11 ~ 2026-05-22</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr">
         <is>
           <t>B</t>
@@ -2476,12 +2473,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2491,34 +2488,34 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>最近十個營業日已有六次 / 第一次處置</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 台燿科技股份有限公司股票(代號：6274)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年4月17日起10個營業日(115年4月17日至115年4月30日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-26 ~ 2026-04-10</t>
+          <t>2026-04-17 ~ 2026-04-30</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2528,34 +2525,34 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 竹陞科技股份有限公司股票(代號：6739)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年02月03日起10個營業日(115年02月03日至115年02月25日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>最近十個營業日已有六次 / 第一次處置</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-02-03 ~ 2026-02-25</t>
+          <t>2026-06-08 ~ 2026-06-22</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2565,34 +2562,34 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>連續三次 / 第二次處置</t>
+          <t>最近十個營業日已有六次 / 第一次處置</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-24 ~ 2026-05-08</t>
+          <t>2026-04-22 ~ 2026-05-06</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2602,34 +2599,34 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>連續三次 / 第二次處置</t>
+          <t>連續五次 / 第二次處置</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-20 ~ 2026-04-02</t>
+          <t>2026-03-09 ~ 2026-03-20</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2639,34 +2636,34 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>連續三次 / 第一次處置</t>
+          <t>最近十個營業日已有六次 / 第一次處置</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-17 ~ 2026-03-30</t>
+          <t>2026-02-04 ~ 2026-02-26</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2676,7 +2673,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2686,61 +2683,57 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-24 ~ 2026-07-07</t>
+          <t>2026-02-03 ~ 2026-02-25</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>⚠️ 處置</t>
+          <t>💀 下市</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2024-01-25</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>最近十個營業日已有六次 / 第一次處置</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-04-15 ~ 2026-04-28</t>
-        </is>
-      </c>
+          <t>已下市</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2750,17 +2743,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>最近十個營業日已有六次 / 第二次處置</t>
+          <t>最近十個營業日已有六次 / 第一次處置</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-25 ~ 2026-03-11</t>
+          <t>2026-03-26 ~ 2026-04-10</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2772,35 +2765,294 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>6739</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>⚠️ 處置</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 竹陞科技股份有限公司股票(代號：6739)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年02月03日起10個營業日(115年02月03日至115年02月25日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-02-03 ~ 2026-02-25</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>8271</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>宇瞻</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>⚠️ 處置</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>連續三次 / 第二次處置</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-04-24 ~ 2026-05-08</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>8271</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>宇瞻</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>⚠️ 處置</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>連續三次 / 第二次處置</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-03-20 ~ 2026-04-02</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>8271</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>宇瞻</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>⚠️ 處置</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>連續三次 / 第一次處置</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-03-17 ~ 2026-03-30</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
           <t>8996</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>高力</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>⚠️ 處置</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>連續三次 / 第一次處置</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-06-24 ~ 2026-07-07</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>8996</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>⚠️ 處置</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>最近十個營業日已有六次 / 第一次處置</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-04-15 ~ 2026-04-28</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>8996</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>⚠️ 處置</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>最近十個營業日已有六次 / 第二次處置</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-02-25 ~ 2026-03-11</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>8996</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>⚠️ 處置</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
         <is>
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>最近十個營業日已有六次 / 第二次處置</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>2026-01-16 ~ 2026-01-29</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -2817,7 +3069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3225,141 +3477,141 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>連續5個營業日</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>華星光通科技股份有限公司股票(代號：4979)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年3月27日起10個營業日(115年3月27日至115年4月13日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>萬潤科技股份有限公司股票(代號：6187)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年3月3日起10個營業日(115年3月3日至115年3月16日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>連續三次</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>第一次處置</t>
+          <t>萬潤科技股份有限公司股票(代號：6187)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年3月6日起10個營業日(115年3月6日至115年3月19日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-19</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>連續三次</t>
+          <t>連續5個營業日</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>第一次處置</t>
+          <t>華星光通科技股份有限公司股票(代號：4979)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年3月27日起10個營業日(115年3月27日至115年4月13日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -3368,74 +3620,74 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>華星光通科技股份有限公司股票(代號：4979)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年4月21日起10個營業日(115年4月21日至115年5月5日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>萬潤科技股份有限公司股票(代號：6187)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年3月30日起10個營業日(115年3月30日至115年4月14日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-14</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>連續5個營業日</t>
+          <t>連續三次</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>華星光通科技股份有限公司股票(代號：4979)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年5月13日起10個營業日(115年5月13日至115年5月26日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>第一次處置</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -3453,19 +3705,19 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3479,167 +3731,167 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>連續5個營業日</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>華星光通科技股份有限公司股票(代號：4979)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年6月3日起10個營業日(115年6月3日至115年6月16日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>華星光通科技股份有限公司股票(代號：4979)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年4月21日起10個營業日(115年4月21日至115年5月5日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-05</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款</t>
+          <t>連續5個營業日</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>大綜電腦系統股份有限公司股票(代號：3147)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年6月8日起10個營業日(115年6月8日至115年6月22日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>華星光通科技股份有限公司股票(代號：4979)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年5月13日起10個營業日(115年5月13日至115年5月26日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款</t>
+          <t>連續三次</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>大綜電腦系統股份有限公司股票(代號：3147)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年6月11日起10個營業日(115年6月11日至115年6月25日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>第一次處置</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>最近十個營業日已有六次</t>
+          <t>連續5個營業日</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>第二次處置</t>
+          <t>華星光通科技股份有限公司股票(代號：4979)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年6月3日起10個營業日(115年6月3日至115年6月16日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -3648,38 +3900,38 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>聯亞光電工業股份有限公司股票(代號：3081)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年01月30日起10個營業日(115年01月30日至115年02月23日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>大綜電腦系統股份有限公司股票(代號：3147)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年6月8日起10個營業日(115年6月8日至115年6月22日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -3688,264 +3940,264 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>聯亞光電工業股份有限公司股票(代號：3081)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年02月04日起10個營業日(115年02月04日至115年02月26日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>大綜電腦系統股份有限公司股票(代號：3147)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年6月11日起10個營業日(115年6月11日至115年6月25日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>最近十個營業日已有六次</t>
+          <t>最近10個營業日內有6個營業日</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>第二次處置</t>
+          <t>萬潤科技股份有限公司股票(代號：6187)因最近10個營業日內有6個營業日經本中心公布注意交易資訊，爰自115年6月17日起10個營業日(115年6月17日至115年7月1日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>最近10個營業日內有6個營業日</t>
+          <t>最近十個營業日已有六次</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>聯亞光電工業股份有限公司股票(代號：3081)最近30個營業日內曾發布處置，又因最近10個營業日內有6個營業日經本中心公布注意交易資訊，爰自115年3月12日起10個營業日(115年3月12日至115年3月25日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>第二次處置</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-01-29</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>最近十個營業日已有六次</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>第一次處置</t>
+          <t>聯亞光電工業股份有限公司股票(代號：3081)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年01月30日起10個營業日(115年01月30日至115年02月23日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-02-23</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>連續三次</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>第一次處置</t>
+          <t>聯亞光電工業股份有限公司股票(代號：3081)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年02月04日起10個營業日(115年02月04日至115年02月26日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-02-26</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款</t>
+          <t>最近十個營業日已有六次</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>台燿科技股份有限公司股票(代號：6274)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年4月17日起10個營業日(115年4月17日至115年4月30日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>第二次處置</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-03-11</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款</t>
+          <t>最近10個營業日內有6個營業日</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>台燿科技股份有限公司股票(代號：6274)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年5月11日起10個營業日(115年5月11日至115年5月22日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>聯亞光電工業股份有限公司股票(代號：3081)最近30個營業日內曾發布處置，又因最近10個營業日內有6個營業日經本中心公布注意交易資訊，爰自115年3月12日起10個營業日(115年3月12日至115年3月25日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-03-25</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3963,7 +4215,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>連續三次</t>
+          <t>最近十個營業日已有六次</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3973,113 +4225,113 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>六方科-KY</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>連續3個營業日及沖銷標準</t>
+          <t>連續三次</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>威剛科技股份有限公司股票(代號：3260)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，且最近3個營業日曾達本中心作業要點第四條第一項第十三款經本中心公布注意交易資訊，爰自115年01月07日起12個營業日(115年01月07日至115年01月22日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>第一次處置</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>最近十個營業日已有六次</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>第二次處置</t>
+          <t>台燿科技股份有限公司股票(代號：6274)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年4月17日起10個營業日(115年4月17日至115年4月30日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -4088,42 +4340,42 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>竹陞科技股份有限公司股票(代號：6739)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年02月03日起10個營業日(115年02月03日至115年02月25日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>台燿科技股份有限公司股票(代號：6274)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年5月11日起10個營業日(115年5月11日至115年5月22日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>最近十個營業日已有六次</t>
+          <t>連續三次</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -4133,139 +4385,139 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-07-07</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>連續五次</t>
+          <t>連續3個營業日及沖銷標準</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>第二次處置</t>
+          <t>威剛科技股份有限公司股票(代號：3260)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，且最近3個營業日曾達本中心作業要點第四條第一項第十三款經本中心公布注意交易資訊，爰自115年01月07日起12個營業日(115年01月07日至115年01月22日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-01-22</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款</t>
+          <t>最近十個營業日已有六次</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>威剛科技股份有限公司股票(代號：3260)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年3月19日起10個營業日(115年3月19日至115年4月1日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>第二次處置</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-01-22</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>連續三次</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>第一次處置</t>
+          <t>竹陞科技股份有限公司股票(代號：6739)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年02月03日起10個營業日(115年02月03日至115年02月25日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-02-25</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4279,7 +4531,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -4293,73 +4545,73 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-02-26</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>連續三次</t>
+          <t>連續五次</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>第一次處置</t>
+          <t>第二次處置</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-03-20</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -4368,34 +4620,34 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>普萊德科技股份有限公司股票(代號：6263)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年5月15日起10個營業日(115年5月15日至115年5月28日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>威剛科技股份有限公司股票(代號：3260)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年3月19日起10個營業日(115年3月19日至115年4月1日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -4413,19 +4665,19 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4453,19 +4705,19 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4483,7 +4735,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>最近十個營業日已有六次</t>
+          <t>連續三次</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4493,73 +4745,73 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>連續5個營業日</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>建榮工業材料股份有限公司股票(代號：5340)因連續5個營業日經本中心公布注意交易資訊，爰自115年01月22日起10個營業日(115年01月22日至115年02月04日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>普萊德科技股份有限公司股票(代號：6263)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年5月15日起10個營業日(115年5月15日至115年5月28日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -4573,99 +4825,99 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>連續5個營業日</t>
+          <t>最近十個營業日已有六次</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>建榮工業材料股份有限公司股票(代號：5340)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年2月23日起10個營業日(115年2月23日至115年3月9日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>第一次處置</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-06-22</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>連續5個營業日</t>
+          <t>最近十個營業日已有六次</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>建榮工業材料股份有限公司股票(代號：5340)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年3月17日起10個營業日(115年3月17日至115年3月30日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>第一次處置</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4679,47 +4931,47 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>最近10個營業日內有6個營業日</t>
+          <t>連續5個營業日</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>建榮工業材料股份有限公司股票(代號：5340)最近30個營業日內曾發布處置，又因最近10個營業日內有6個營業日經本中心公布注意交易資訊，爰自115年4月21日起10個營業日(115年4月21日至115年5月5日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>建榮工業材料股份有限公司股票(代號：5340)因連續5個營業日經本中心公布注意交易資訊，爰自115年01月22日起10個營業日(115年01月22日至115年02月04日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -4733,149 +4985,149 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-02-25</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>建榮</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>連續三次</t>
+          <t>連續5個營業日</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>第一次處置</t>
+          <t>建榮工業材料股份有限公司股票(代號：5340)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年2月23日起10個營業日(115年2月23日至115年3月9日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>建榮</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>連續三次</t>
+          <t>連續5個營業日</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>第一次處置</t>
+          <t>建榮工業材料股份有限公司股票(代號：5340)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年3月17日起10個營業日(115年3月17日至115年3月30日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>建榮</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>連續三次</t>
+          <t>最近10個營業日內有6個營業日</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>第二次處置</t>
+          <t>建榮工業材料股份有限公司股票(代號：5340)最近30個營業日內曾發布處置，又因最近10個營業日內有6個營業日經本中心公布注意交易資訊，爰自115年4月21日起10個營業日(115年4月21日至115年5月5日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-05</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -4883,20 +5135,180 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
+          <t>連續三次</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>第一次處置</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>連續三次</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>第一次處置</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>連續三次</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>第一次處置</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>3653</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>連續三次</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>第二次處置</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
           <t>最近十個營業日已有六次</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>第一次處置</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>2026-06-18</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
@@ -4981,23 +5393,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C96"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>代號</t>
+          <t>stock_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>30d 借券量</t>
+          <t>date</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>最新日借券</t>
+          <t>end_date</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>reason</t>
         </is>
       </c>
     </row>
@@ -5007,1233 +5424,20 @@
           <t>2330</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>297937</v>
-      </c>
-      <c r="C2" t="n">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>236329</v>
-      </c>
-      <c r="C3" t="n">
-        <v>5080</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2317</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>222729</v>
-      </c>
-      <c r="C4" t="n">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>3231</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>160548</v>
-      </c>
-      <c r="C5" t="n">
-        <v>5376</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2356</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>113907</v>
-      </c>
-      <c r="C6" t="n">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>110061</v>
-      </c>
-      <c r="C7" t="n">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2301</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>95450</v>
-      </c>
-      <c r="C8" t="n">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2618</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>93942</v>
-      </c>
-      <c r="C9" t="n">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2327</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>80465</v>
-      </c>
-      <c r="C10" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>4904</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C11" t="n">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2382</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>70757</v>
-      </c>
-      <c r="C12" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>3711</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>65387</v>
-      </c>
-      <c r="C13" t="n">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2412</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>48467</v>
-      </c>
-      <c r="C14" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2308</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>45469</v>
-      </c>
-      <c r="C15" t="n">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>3045</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>42437</v>
-      </c>
-      <c r="C16" t="n">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2454</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>36624</v>
-      </c>
-      <c r="C17" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2379</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>17340</v>
-      </c>
-      <c r="C18" t="n">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2912</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>16945</v>
-      </c>
-      <c r="C19" t="n">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>1513</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>15578</v>
-      </c>
-      <c r="C20" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>3044</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>13777</v>
-      </c>
-      <c r="C21" t="n">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>6285</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>13623</v>
-      </c>
-      <c r="C22" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>12937</v>
-      </c>
-      <c r="C23" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>3450</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>11161</v>
-      </c>
-      <c r="C24" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>10933</v>
-      </c>
-      <c r="C25" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2395</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>9346</v>
-      </c>
-      <c r="C26" t="n">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>6189</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>8888</v>
-      </c>
-      <c r="C27" t="n">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>8926</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>8766</v>
-      </c>
-      <c r="C28" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>3293</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>8275</v>
-      </c>
-      <c r="C29" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>1514</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>8109</v>
-      </c>
-      <c r="C30" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2383</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>7858</v>
-      </c>
-      <c r="C31" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>3443</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>7295</v>
-      </c>
-      <c r="C32" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2421</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>7204</v>
-      </c>
-      <c r="C33" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>1503</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>6526</v>
-      </c>
-      <c r="C34" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>3017</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>6201</v>
-      </c>
-      <c r="C35" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2476</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>6054</v>
-      </c>
-      <c r="C36" t="n">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>6446</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>5447</v>
-      </c>
-      <c r="C37" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>5328</v>
-      </c>
-      <c r="C38" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>3008</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>5269</v>
-      </c>
-      <c r="C39" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>3406</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>5226</v>
-      </c>
-      <c r="C40" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>1560</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>4974</v>
-      </c>
-      <c r="C41" t="n">
-        <v>1547</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>1519</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>4801</v>
-      </c>
-      <c r="C42" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>6139</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>4623</v>
-      </c>
-      <c r="C43" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>3596</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>4515</v>
-      </c>
-      <c r="C44" t="n">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>3661</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>4395</v>
-      </c>
-      <c r="C45" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>6669</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>4373</v>
-      </c>
-      <c r="C46" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>6197</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>4342</v>
-      </c>
-      <c r="C47" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>1215</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>4197</v>
-      </c>
-      <c r="C48" t="n">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>5434</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>4142</v>
-      </c>
-      <c r="C49" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>4979</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>4073</v>
-      </c>
-      <c r="C50" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>3653</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>3857</v>
-      </c>
-      <c r="C51" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>6196</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>3800</v>
-      </c>
-      <c r="C52" t="n">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>3081</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>3755</v>
-      </c>
-      <c r="C53" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>3260</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>3755</v>
-      </c>
-      <c r="C54" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>5243</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>3692</v>
-      </c>
-      <c r="C55" t="n">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>8086</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>3579</v>
-      </c>
-      <c r="C56" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>2472</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>2716</v>
-      </c>
-      <c r="C57" t="n">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>3227</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>2643</v>
-      </c>
-      <c r="C58" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>1773</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>2628</v>
-      </c>
-      <c r="C59" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>9917</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>2587</v>
-      </c>
-      <c r="C60" t="n">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>1590</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>2554</v>
-      </c>
-      <c r="C61" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2645</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>2425</v>
-      </c>
-      <c r="C62" t="n">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>8996</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>2330</v>
-      </c>
-      <c r="C63" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>8210</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>1930</v>
-      </c>
-      <c r="C64" t="n">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>5904</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>1870</v>
-      </c>
-      <c r="C65" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>6223</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>1736</v>
-      </c>
-      <c r="C66" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>3324</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
-        <v>1616</v>
-      </c>
-      <c r="C67" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>2305</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>1410</v>
-      </c>
-      <c r="C68" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>2059</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
-        <v>1345</v>
-      </c>
-      <c r="C69" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>3689</t>
-        </is>
-      </c>
-      <c r="B70" t="n">
-        <v>1325</v>
-      </c>
-      <c r="C70" t="n">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>3147</t>
-        </is>
-      </c>
-      <c r="B71" t="n">
-        <v>1116</v>
-      </c>
-      <c r="C71" t="n">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>8271</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
-        <v>1028</v>
-      </c>
-      <c r="C72" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>6442</t>
-        </is>
-      </c>
-      <c r="B73" t="n">
-        <v>1015</v>
-      </c>
-      <c r="C73" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>2535</t>
-        </is>
-      </c>
-      <c r="B74" t="n">
-        <v>922</v>
-      </c>
-      <c r="C74" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>3402</t>
-        </is>
-      </c>
-      <c r="B75" t="n">
-        <v>915</v>
-      </c>
-      <c r="C75" t="n">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>1616</t>
-        </is>
-      </c>
-      <c r="B76" t="n">
-        <v>892</v>
-      </c>
-      <c r="C76" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>5269</t>
-        </is>
-      </c>
-      <c r="B77" t="n">
-        <v>841</v>
-      </c>
-      <c r="C77" t="n">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>3583</t>
-        </is>
-      </c>
-      <c r="B78" t="n">
-        <v>730</v>
-      </c>
-      <c r="C78" t="n">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>6510</t>
-        </is>
-      </c>
-      <c r="B79" t="n">
-        <v>685</v>
-      </c>
-      <c r="C79" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>3029</t>
-        </is>
-      </c>
-      <c r="B80" t="n">
-        <v>640</v>
-      </c>
-      <c r="C80" t="n">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>524</v>
-      </c>
-      <c r="C81" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>1618</t>
-        </is>
-      </c>
-      <c r="B82" t="n">
-        <v>438</v>
-      </c>
-      <c r="C82" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>5519</t>
-        </is>
-      </c>
-      <c r="B83" t="n">
-        <v>404</v>
-      </c>
-      <c r="C83" t="n">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>6263</t>
-        </is>
-      </c>
-      <c r="B84" t="n">
-        <v>370</v>
-      </c>
-      <c r="C84" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>5478</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
-        <v>297</v>
-      </c>
-      <c r="C85" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>1232</t>
-        </is>
-      </c>
-      <c r="B86" t="n">
-        <v>158</v>
-      </c>
-      <c r="C86" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>4506</t>
-        </is>
-      </c>
-      <c r="B87" t="n">
-        <v>148</v>
-      </c>
-      <c r="C87" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>5340</t>
-        </is>
-      </c>
-      <c r="B88" t="n">
-        <v>129</v>
-      </c>
-      <c r="C88" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>5225</t>
-        </is>
-      </c>
-      <c r="B89" t="n">
-        <v>114</v>
-      </c>
-      <c r="C89" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>2753</t>
-        </is>
-      </c>
-      <c r="B90" t="n">
-        <v>64</v>
-      </c>
-      <c r="C90" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>4933</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>57</v>
-      </c>
-      <c r="C91" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>6788</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
-        <v>47</v>
-      </c>
-      <c r="C92" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>3188</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
-        <v>45</v>
-      </c>
-      <c r="C93" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>4129</t>
-        </is>
-      </c>
-      <c r="B94" t="n">
-        <v>35</v>
-      </c>
-      <c r="C94" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>4303</t>
-        </is>
-      </c>
-      <c r="B95" t="n">
-        <v>28</v>
-      </c>
-      <c r="C95" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>6739</t>
-        </is>
-      </c>
-      <c r="B96" t="n">
-        <v>3</v>
-      </c>
-      <c r="C96" t="n">
-        <v>2</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>除息</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -6247,6 +5451,1337 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>代號</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>30d 借券量</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>最新日借券</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>299503</v>
+      </c>
+      <c r="C2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2317</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>184965</v>
+      </c>
+      <c r="C3" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>178228</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>133623</v>
+      </c>
+      <c r="C5" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2327</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>104272</v>
+      </c>
+      <c r="C6" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>4904</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>89312</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>88714</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2356</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>85406</v>
+      </c>
+      <c r="C9" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>81946</v>
+      </c>
+      <c r="C10" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2618</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>81507</v>
+      </c>
+      <c r="C11" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2412</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>60438</v>
+      </c>
+      <c r="C12" t="n">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>57073</v>
+      </c>
+      <c r="C13" t="n">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2308</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>51339</v>
+      </c>
+      <c r="C14" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2382</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>50657</v>
+      </c>
+      <c r="C15" t="n">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>3045</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>39632</v>
+      </c>
+      <c r="C16" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>29798</v>
+      </c>
+      <c r="C17" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>20590</v>
+      </c>
+      <c r="C18" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2912</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>18831</v>
+      </c>
+      <c r="C19" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2379</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>17308</v>
+      </c>
+      <c r="C20" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>16153</v>
+      </c>
+      <c r="C21" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>6285</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>15684</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3203</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1513</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>13285</v>
+      </c>
+      <c r="C23" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>8926</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>13209</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>12793</v>
+      </c>
+      <c r="C25" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>12308</v>
+      </c>
+      <c r="C26" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>3450</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>10039</v>
+      </c>
+      <c r="C27" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2395</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>9569</v>
+      </c>
+      <c r="C28" t="n">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>3293</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>8382</v>
+      </c>
+      <c r="C29" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>7944</v>
+      </c>
+      <c r="C30" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>6189</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>7858</v>
+      </c>
+      <c r="C31" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>1514</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>7561</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>7328</v>
+      </c>
+      <c r="C33" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2476</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>6411</v>
+      </c>
+      <c r="C34" t="n">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>6112</v>
+      </c>
+      <c r="C35" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>6068</v>
+      </c>
+      <c r="C36" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>3406</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>5810</v>
+      </c>
+      <c r="C37" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>5502</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>1519</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>5271</v>
+      </c>
+      <c r="C39" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>5434</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>4953</v>
+      </c>
+      <c r="C40" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>4945</v>
+      </c>
+      <c r="C41" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>1503</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>4936</v>
+      </c>
+      <c r="C42" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2421</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>4808</v>
+      </c>
+      <c r="C43" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>6139</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>4771</v>
+      </c>
+      <c r="C44" t="n">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>1560</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>4770</v>
+      </c>
+      <c r="C45" t="n">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>6446</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>4679</v>
+      </c>
+      <c r="C46" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>3596</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>4636</v>
+      </c>
+      <c r="C47" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>6196</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>4089</v>
+      </c>
+      <c r="C48" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>3260</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>3964</v>
+      </c>
+      <c r="C49" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>3661</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>3921</v>
+      </c>
+      <c r="C50" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>3920</v>
+      </c>
+      <c r="C51" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>3081</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>3833</v>
+      </c>
+      <c r="C52" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>5243</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>3719</v>
+      </c>
+      <c r="C53" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>3653</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>3498</v>
+      </c>
+      <c r="C54" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>8086</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>3476</v>
+      </c>
+      <c r="C55" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2472</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>3379</v>
+      </c>
+      <c r="C56" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>5439</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>3236</v>
+      </c>
+      <c r="C57" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>3012</v>
+      </c>
+      <c r="C58" t="n">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>4979</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>2699</v>
+      </c>
+      <c r="C59" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2645</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>2641</v>
+      </c>
+      <c r="C60" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>9917</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>2610</v>
+      </c>
+      <c r="C61" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>6197</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>2388</v>
+      </c>
+      <c r="C62" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>1590</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>2339</v>
+      </c>
+      <c r="C63" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>1773</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>2326</v>
+      </c>
+      <c r="C64" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>8996</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>2282</v>
+      </c>
+      <c r="C65" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>3227</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>1997</v>
+      </c>
+      <c r="C66" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>1913</v>
+      </c>
+      <c r="C67" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>8210</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>1906</v>
+      </c>
+      <c r="C68" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>1530</v>
+      </c>
+      <c r="C69" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2305</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>1419</v>
+      </c>
+      <c r="C70" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>5904</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>1383</v>
+      </c>
+      <c r="C71" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>1339</v>
+      </c>
+      <c r="C72" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>3689</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>1286</v>
+      </c>
+      <c r="C73" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2535</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>1209</v>
+      </c>
+      <c r="C74" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3147</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>1152</v>
+      </c>
+      <c r="C75" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>3583</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>933</v>
+      </c>
+      <c r="C76" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>1616</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>900</v>
+      </c>
+      <c r="C77" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>5269</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>879</v>
+      </c>
+      <c r="C78" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>6442</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>867</v>
+      </c>
+      <c r="C79" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>618</v>
+      </c>
+      <c r="C80" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>3029</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>602</v>
+      </c>
+      <c r="C81" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>6510</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>588</v>
+      </c>
+      <c r="C82" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>8271</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>548</v>
+      </c>
+      <c r="C83" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>1618</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>488</v>
+      </c>
+      <c r="C84" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>5274</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>471</v>
+      </c>
+      <c r="C85" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>3402</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>312</v>
+      </c>
+      <c r="C86" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>6263</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>311</v>
+      </c>
+      <c r="C87" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>5478</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>297</v>
+      </c>
+      <c r="C88" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>5340</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>260</v>
+      </c>
+      <c r="C89" t="n">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>5519</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>243</v>
+      </c>
+      <c r="C90" t="n">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>1232</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>170</v>
+      </c>
+      <c r="C91" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>4506</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>148</v>
+      </c>
+      <c r="C92" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2753</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>137</v>
+      </c>
+      <c r="C93" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>6739</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>75</v>
+      </c>
+      <c r="C94" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2640</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>59</v>
+      </c>
+      <c r="C95" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>4933</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>57</v>
+      </c>
+      <c r="C96" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>4129</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>55</v>
+      </c>
+      <c r="C97" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>6788</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>47</v>
+      </c>
+      <c r="C98" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>3188</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>45</v>
+      </c>
+      <c r="C99" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>5225</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>22</v>
+      </c>
+      <c r="C100" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>20</v>
+      </c>
+      <c r="C101" t="n">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/data/台股_警戒掃描.xlsx
+++ b/data/台股_警戒掃描.xlsx
@@ -10,9 +10,7 @@
     <sheet name="警戒總覽" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="處置股票" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="暫停交易" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="暫停融券" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="借券排行" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="下市" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="借券排行" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -418,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,67 +496,67 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>全友</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🪦 借券爆量</t>
+          <t>⚠️ 處置</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>30d 88714 股, 最新日 1470 股</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>連續三次 / 第一次處置</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-06-24 ~ 2026-07-07</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>⚠️ 處置</t>
+          <t>🪦 借券爆量</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>連續三次 / 第一次處置</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-06-24 ~ 2026-07-07</t>
-        </is>
-      </c>
+          <t>30d 151173 股, 最新日 282 股</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>B</t>
@@ -568,45 +566,49 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>🪦 借券爆量</t>
+          <t>⚠️ 處置</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>30d 51339 股, 最新日 450 股</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+          <t>連續三次 / 第一次處置</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-05-26 ~ 2026-06-08</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -616,67 +618,63 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>30d 184965 股, 最新日 73 股</t>
+          <t>30d 124179 股, 最新日 3360 股</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>⚠️ 處置</t>
+          <t>🪦 借券爆量</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>連續三次 / 第一次處置</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-05-26 ~ 2026-06-08</t>
-        </is>
-      </c>
+          <t>30d 278394 股, 最新日 1 股</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -686,12 +684,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>30d 104272 股, 最新日 30 股</t>
+          <t>30d 154178 股, 最新日 27 股</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -704,67 +702,67 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>📉 暫停融券</t>
+          <t>🪦 借券爆量</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>除息</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>~ 2026-06-10</t>
-        </is>
-      </c>
+          <t>30d 80639 股, 最新日 30 股</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>🪦 借券爆量</t>
+          <t>⚠️ 處置</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>30d 299503 股, 最新日 100 股</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
+          <t>連續三次 / 第一次處置</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-03-03 ~ 2026-03-16</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>A</t>
@@ -774,12 +772,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -789,34 +787,34 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>連續五次及當日沖銷標準 / 第一次處置</t>
+          <t>最近十個營業日已有六次 / 第一次處置</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-01-09 ~ 2026-01-26</t>
+          <t>2026-06-18 ~ 2026-07-02</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -826,12 +824,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>30d 178228 股, 最新日 2000 股</t>
+          <t>30d 58154 股, 最新日 54 股</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -844,12 +842,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -859,30 +857,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>30d 85406 股, 最新日 136 股</t>
+          <t>30d 70012 股, 最新日 572 股</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -892,7 +890,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -902,42 +900,46 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-03 ~ 2026-03-16</t>
+          <t>2026-05-07 ~ 2026-05-20</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>立隆電</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>🪦 借券爆量</t>
+          <t>⚠️ 處置</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>30d 50657 股, 最新日 388 股</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
+          <t>連續三次 / 第一次處置</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-06-01 ~ 2026-06-12</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>B</t>
@@ -947,34 +949,30 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>⚠️ 處置</t>
+          <t>🪦 借券爆量</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>最近十個營業日已有六次 / 第一次處置</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-06-18 ~ 2026-07-02</t>
-        </is>
-      </c>
+          <t>30d 81462 股, 最新日 18497 股</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>A</t>
@@ -984,12 +982,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -999,17 +997,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>最近十個營業日已有六次 / 第二次處置</t>
+          <t>連續三次 / 第一次處置</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-01-09 ~ 2026-01-22</t>
+          <t>2026-05-20 ~ 2026-06-02</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1021,78 +1019,86 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>🪦 借券爆量</t>
+          <t>⚠️ 處置</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>30d 81946 股, 最新日 12 股</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
+          <t>最近10個營業日內有6個營業日 / 聯亞光電工業股份有限公司股票(代號：3081)最近30個營業日內曾發布處置，又因最近10個營業日內有6個營業日經本中心公布注意交易資訊，爰自115年3月12日起10個營業日(115年3月12日至115年3月25日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-12 ~ 2026-03-25</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🪦 借券爆量</t>
+          <t>⚠️ 處置</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>30d 60438 股, 最新日 345 股</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 聯亞光電工業股份有限公司股票(代號：3081)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年02月04日起10個營業日(115年02月04日至115年02月26日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-02-04 ~ 2026-02-26</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1102,34 +1108,34 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>連續三次 / 第一次處置</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 聯亞光電工業股份有限公司股票(代號：3081)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年01月30日起10個營業日(115年01月30日至115年02月23日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-07 ~ 2026-05-20</t>
+          <t>2026-01-30 ~ 2026-02-23</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1139,17 +1145,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>連續三次 / 第一次處置</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 大綜電腦系統股份有限公司股票(代號：3147)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年7月6日起10個營業日(115年7月6日至115年7月17日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-01 ~ 2026-06-12</t>
+          <t>2026-07-06 ~ 2026-07-17</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1161,45 +1167,49 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>🪦 借券爆量</t>
+          <t>⚠️ 處置</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>30d 81507 股, 最新日 200 股</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 大綜電腦系統股份有限公司股票(代號：3147)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年6月11日起10個營業日(115年6月11日至115年6月25日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-06-11 ~ 2026-06-25</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1209,71 +1219,67 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>連續三次 / 第一次處置</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 大綜電腦系統股份有限公司股票(代號：3147)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年6月8日起10個營業日(115年6月8日至115年6月22日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-20 ~ 2026-06-02</t>
+          <t>2026-06-08 ~ 2026-06-22</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>⚠️ 處置</t>
+          <t>🪦 借券爆量</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>最近10個營業日內有6個營業日 / 聯亞光電工業股份有限公司股票(代號：3081)最近30個營業日內曾發布處置，又因最近10個營業日內有6個營業日經本中心公布注意交易資訊，爰自115年3月12日起10個營業日(115年3月12日至115年3月25日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-03-12 ~ 2026-03-25</t>
-        </is>
-      </c>
+          <t>30d 102952 股, 最新日 90 股</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1283,17 +1289,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 聯亞光電工業股份有限公司股票(代號：3081)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年02月04日起10個營業日(115年02月04日至115年02月26日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 威剛科技股份有限公司股票(代號：3260)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年3月19日起10個營業日(115年3月19日至115年4月1日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-02-04 ~ 2026-02-26</t>
+          <t>2026-03-19 ~ 2026-04-01</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1305,12 +1311,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1320,34 +1326,34 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 聯亞光電工業股份有限公司股票(代號：3081)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年01月30日起10個營業日(115年01月30日至115年02月23日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>連續三次 / 第一次處置</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-01-30 ~ 2026-02-23</t>
+          <t>2026-04-17 ~ 2026-04-30</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1357,34 +1363,34 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 大綜電腦系統股份有限公司股票(代號：3147)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年6月11日起10個營業日(115年6月11日至115年6月25日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>最近十個營業日已有六次 / 第一次處置</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-11 ~ 2026-06-25</t>
+          <t>2026-06-30 ~ 2026-07-13</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1394,67 +1400,71 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 大綜電腦系統股份有限公司股票(代號：3147)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年6月8日起10個營業日(115年6月8日至115年6月22日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>連續三次 / 第一次處置</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-08 ~ 2026-06-22</t>
+          <t>2026-05-13 ~ 2026-05-26</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>🪦 借券爆量</t>
+          <t>⚠️ 處置</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>30d 133623 股, 最新日 132 股</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
+          <t>連續三次 / 第一次處置</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-04-14 ~ 2026-04-27</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1464,34 +1474,34 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 威剛科技股份有限公司股票(代號：3260)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年3月19日起10個營業日(115年3月19日至115年4月1日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>連續三次 / 第二次處置</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-19 ~ 2026-04-01</t>
+          <t>2026-05-13 ~ 2026-05-26</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1501,108 +1511,100 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>連續3個營業日及沖銷標準 / 威剛科技股份有限公司股票(代號：3260)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，且最近3個營業日曾達本中心作業要點第四條第一項第十三款經本中心公布注意交易資訊，爰自115年01月07日起12個營業日(115年01月07日至115年01月22日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>連續三次 / 第一次處置</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-01-07 ~ 2026-01-22</t>
+          <t>2026-04-24 ~ 2026-05-08</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>⚠️ 處置</t>
+          <t>🪦 借券爆量</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>連續三次 / 第一次處置</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-04-17 ~ 2026-04-30</t>
-        </is>
-      </c>
+          <t>30d 53142 股, 最新日 129 股</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>信立</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>⚠️ 處置</t>
+          <t>🚫 暫停</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>最近十個營業日已有六次 / 第一次處置</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-06-30 ~ 2026-07-13</t>
-        </is>
-      </c>
+          <t>暫停8:00, 恢復2026-04-29</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>六方科-KY</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1612,7 +1614,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1622,61 +1624,57 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-13 ~ 2026-05-26</t>
+          <t>2026-04-16 ~ 2026-04-29</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>⚠️ 處置</t>
+          <t>🪦 借券爆量</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>連續三次 / 第一次處置</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-04-14 ~ 2026-04-27</t>
-        </is>
-      </c>
+          <t>30d 85610 股, 最新日 300 股</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1686,34 +1684,34 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>連續三次 / 第二次處置</t>
+          <t>連續5個營業日 / 華星光通科技股份有限公司股票(代號：4979)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年6月3日起10個營業日(115年6月3日至115年6月16日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-13 ~ 2026-05-26</t>
+          <t>2026-06-03 ~ 2026-06-16</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1723,52 +1721,56 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>連續三次 / 第一次處置</t>
+          <t>連續5個營業日 / 華星光通科技股份有限公司股票(代號：4979)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年5月13日起10個營業日(115年5月13日至115年5月26日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-24 ~ 2026-05-08</t>
+          <t>2026-05-13 ~ 2026-05-26</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>🪦 借券爆量</t>
+          <t>⚠️ 處置</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>30d 57073 股, 最新日 876 股</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 華星光通科技股份有限公司股票(代號：4979)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年4月21日起10個營業日(115年4月21日至115年5月5日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-04-21 ~ 2026-05-05</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>B</t>
@@ -1778,30 +1780,34 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>🚫 暫停</t>
+          <t>⚠️ 處置</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>暫停8:00, 恢復2026-04-29</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
+          <t>連續5個營業日 / 華星光通科技股份有限公司股票(代號：4979)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年3月27日起10個營業日(115年3月27日至115年4月13日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-03-27 ~ 2026-04-13</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>B</t>
@@ -1811,12 +1817,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1826,17 +1832,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>連續三次 / 第一次處置</t>
+          <t>連續5個營業日 / 華星光通科技股份有限公司股票(代號：4979)因連續5個營業日經本中心公布注意交易資訊，爰自115年3月3日起10個營業日(115年3月3日至115年3月16日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-16 ~ 2026-04-29</t>
+          <t>2026-03-03 ~ 2026-03-16</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1848,30 +1854,34 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>🪦 借券爆量</t>
+          <t>⚠️ 處置</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>30d 89312 股, 最新日 3000 股</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
+          <t>連續三次 / 第一次處置</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-04-13 ~ 2026-04-24</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
           <t>B</t>
@@ -1881,12 +1891,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>建榮</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1896,34 +1906,34 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>連續5個營業日 / 華星光通科技股份有限公司股票(代號：4979)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年6月3日起10個營業日(115年6月3日至115年6月16日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>最近10個營業日內有6個營業日 / 建榮工業材料股份有限公司股票(代號：5340)最近30個營業日內曾發布處置，又因最近10個營業日內有6個營業日經本中心公布注意交易資訊，爰自115年4月21日起10個營業日(115年4月21日至115年5月5日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-03 ~ 2026-06-16</t>
+          <t>2026-04-21 ~ 2026-05-05</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>建榮</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1933,34 +1943,34 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>連續5個營業日 / 華星光通科技股份有限公司股票(代號：4979)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年5月13日起10個營業日(115年5月13日至115年5月26日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>連續5個營業日 / 建榮工業材料股份有限公司股票(代號：5340)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年3月17日起10個營業日(115年3月17日至115年3月30日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-13 ~ 2026-05-26</t>
+          <t>2026-03-17 ~ 2026-03-30</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>建榮</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1970,34 +1980,34 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 華星光通科技股份有限公司股票(代號：4979)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年4月21日起10個營業日(115年4月21日至115年5月5日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>連續5個營業日 / 建榮工業材料股份有限公司股票(代號：5340)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年2月23日起10個營業日(115年2月23日至115年3月9日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-21 ~ 2026-05-05</t>
+          <t>2026-02-23 ~ 2026-03-09</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>建榮</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2007,34 +2017,34 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>連續5個營業日 / 華星光通科技股份有限公司股票(代號：4979)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年3月27日起10個營業日(115年3月27日至115年4月13日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>連續5個營業日 / 建榮工業材料股份有限公司股票(代號：5340)因連續5個營業日經本中心公布注意交易資訊，爰自115年01月22日起10個營業日(115年01月22日至115年02月04日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-27 ~ 2026-04-13</t>
+          <t>2026-01-22 ~ 2026-02-04</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2044,34 +2054,34 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>連續5個營業日 / 華星光通科技股份有限公司股票(代號：4979)因連續5個營業日經本中心公布注意交易資訊，爰自115年3月3日起10個營業日(115年3月3日至115年3月16日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>最近10個營業日內有6個營業日 / 萬潤科技股份有限公司股票(代號：6187)因最近10個營業日內有6個營業日經本中心公布注意交易資訊，爰自115年6月17日起10個營業日(115年6月17日至115年7月1日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-03 ~ 2026-03-16</t>
+          <t>2026-06-17 ~ 2026-07-01</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2081,34 +2091,34 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>連續三次 / 第一次處置</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 萬潤科技股份有限公司股票(代號：6187)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年3月30日起10個營業日(115年3月30日至115年4月14日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-13 ~ 2026-04-24</t>
+          <t>2026-03-30 ~ 2026-04-14</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2118,17 +2128,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>最近10個營業日內有6個營業日 / 建榮工業材料股份有限公司股票(代號：5340)最近30個營業日內曾發布處置，又因最近10個營業日內有6個營業日經本中心公布注意交易資訊，爰自115年4月21日起10個營業日(115年4月21日至115年5月5日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 萬潤科技股份有限公司股票(代號：6187)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年3月6日起10個營業日(115年3月6日至115年3月19日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-21 ~ 2026-05-05</t>
+          <t>2026-03-06 ~ 2026-03-19</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2140,12 +2150,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2155,17 +2165,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>連續5個營業日 / 建榮工業材料股份有限公司股票(代號：5340)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年3月17日起10個營業日(115年3月17日至115年3月30日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 萬潤科技股份有限公司股票(代號：6187)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年3月3日起10個營業日(115年3月3日至115年3月16日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-17 ~ 2026-03-30</t>
+          <t>2026-03-03 ~ 2026-03-16</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2177,12 +2187,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2192,34 +2202,34 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>連續5個營業日 / 建榮工業材料股份有限公司股票(代號：5340)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年2月23日起10個營業日(115年2月23日至115年3月9日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 普萊德科技股份有限公司股票(代號：6263)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年5月15日起10個營業日(115年5月15日至115年5月28日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-02-23 ~ 2026-03-09</t>
+          <t>2026-05-15 ~ 2026-05-28</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2229,34 +2239,34 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>連續5個營業日 / 建榮工業材料股份有限公司股票(代號：5340)因連續5個營業日經本中心公布注意交易資訊，爰自115年01月22日起10個營業日(115年01月22日至115年02月04日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 台燿科技股份有限公司股票(代號：6274)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年5月11日起10個營業日(115年5月11日至115年5月22日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-01-22 ~ 2026-02-04</t>
+          <t>2026-05-11 ~ 2026-05-22</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2266,34 +2276,34 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>最近10個營業日內有6個營業日 / 萬潤科技股份有限公司股票(代號：6187)因最近10個營業日內有6個營業日經本中心公布注意交易資訊，爰自115年6月17日起10個營業日(115年6月17日至115年7月1日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 台燿科技股份有限公司股票(代號：6274)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年4月17日起10個營業日(115年4月17日至115年4月30日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-17 ~ 2026-07-01</t>
+          <t>2026-04-17 ~ 2026-04-30</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2303,17 +2313,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 萬潤科技股份有限公司股票(代號：6187)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年3月30日起10個營業日(115年3月30日至115年4月14日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>最近十個營業日已有六次 / 第一次處置</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-30 ~ 2026-04-14</t>
+          <t>2026-06-08 ~ 2026-06-22</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2325,12 +2335,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2340,17 +2350,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 萬潤科技股份有限公司股票(代號：6187)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年3月6日起10個營業日(115年3月6日至115年3月19日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>最近十個營業日已有六次 / 第一次處置</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-06 ~ 2026-03-19</t>
+          <t>2026-04-22 ~ 2026-05-06</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2362,12 +2372,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2377,17 +2387,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 萬潤科技股份有限公司股票(代號：6187)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年3月3日起10個營業日(115年3月3日至115年3月16日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>連續五次 / 第二次處置</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-03 ~ 2026-03-16</t>
+          <t>2026-03-09 ~ 2026-03-20</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2399,12 +2409,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2414,34 +2424,34 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 普萊德科技股份有限公司股票(代號：6263)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年5月15日起10個營業日(115年5月15日至115年5月28日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>最近十個營業日已有六次 / 第一次處置</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-15 ~ 2026-05-28</t>
+          <t>2026-02-04 ~ 2026-02-26</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2451,17 +2461,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 台燿科技股份有限公司股票(代號：6274)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年5月11日起10個營業日(115年5月11日至115年5月22日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>連續三次 / 第一次處置</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-11 ~ 2026-05-22</t>
+          <t>2026-02-03 ~ 2026-02-25</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2473,12 +2483,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2488,34 +2498,34 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 台燿科技股份有限公司股票(代號：6274)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年4月17日起10個營業日(115年4月17日至115年4月30日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>最近十個營業日已有六次 / 第一次處置</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-17 ~ 2026-04-30</t>
+          <t>2026-03-26 ~ 2026-04-10</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2525,34 +2535,34 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>最近十個營業日已有六次 / 第一次處置</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 竹陞科技股份有限公司股票(代號：6739)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年02月03日起10個營業日(115年02月03日至115年02月25日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-08 ~ 2026-06-22</t>
+          <t>2026-02-03 ~ 2026-02-25</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2562,34 +2572,34 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>最近十個營業日已有六次 / 第一次處置</t>
+          <t>連續三次 / 第二次處置</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-22 ~ 2026-05-06</t>
+          <t>2026-04-24 ~ 2026-05-08</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2599,34 +2609,34 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>連續五次 / 第二次處置</t>
+          <t>連續三次 / 第二次處置</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-09 ~ 2026-03-20</t>
+          <t>2026-03-20 ~ 2026-04-02</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2636,34 +2646,34 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>最近十個營業日已有六次 / 第一次處置</t>
+          <t>連續三次 / 第一次處置</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-02-04 ~ 2026-02-26</t>
+          <t>2026-03-17 ~ 2026-03-30</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2673,7 +2683,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2683,57 +2693,61 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-02-03 ~ 2026-02-25</t>
+          <t>2026-06-24 ~ 2026-07-07</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>💀 下市</t>
+          <t>⚠️ 處置</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2024-01-25</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>已下市</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr"/>
+          <t>最近十個營業日已有六次 / 第一次處置</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-04-15 ~ 2026-04-28</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2743,17 +2757,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>最近十個營業日已有六次 / 第一次處置</t>
+          <t>最近十個營業日已有六次 / 第二次處置</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-26 ~ 2026-04-10</t>
+          <t>2026-02-25 ~ 2026-03-11</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2765,12 +2779,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2780,279 +2794,20 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 竹陞科技股份有限公司股票(代號：6739)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年02月03日起10個營業日(115年02月03日至115年02月25日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>最近十個營業日已有六次 / 第二次處置</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-03 ~ 2026-02-25</t>
+          <t>2026-01-16 ~ 2026-01-29</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>8271</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>宇瞻</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>⚠️ 處置</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>連續三次 / 第二次處置</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-04-24 ~ 2026-05-08</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>8271</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>宇瞻</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>⚠️ 處置</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>連續三次 / 第二次處置</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-03-20 ~ 2026-04-02</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>8271</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>宇瞻</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>⚠️ 處置</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>連續三次 / 第一次處置</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-03-17 ~ 2026-03-30</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>8996</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>高力</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>⚠️ 處置</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>連續三次 / 第一次處置</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-06-24 ~ 2026-07-07</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>8996</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>高力</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>⚠️ 處置</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>最近十個營業日已有六次 / 第一次處置</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-04-15 ~ 2026-04-28</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>8996</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>高力</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>⚠️ 處置</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>最近十個營業日已有六次 / 第二次處置</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-02-25 ~ 2026-03-11</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>8996</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>高力</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>⚠️ 處置</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>最近十個營業日已有六次 / 第二次處置</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-01-16 ~ 2026-01-29</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -3069,7 +2824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,40 +3152,40 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>連續五次及當日沖銷標準</t>
+          <t>連續5個營業日</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>第一次處置</t>
+          <t>華星光通科技股份有限公司股票(代號：4979)因連續5個營業日經本中心公布注意交易資訊，爰自115年3月3日起10個營業日(115年3月3日至115年3月16日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-03-16</t>
         </is>
       </c>
     </row>
@@ -3442,12 +3197,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -3455,12 +3210,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>連續5個營業日</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>華星光通科技股份有限公司股票(代號：4979)因連續5個營業日經本中心公布注意交易資訊，爰自115年3月3日起10個營業日(115年3月3日至115年3月16日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>萬潤科技股份有限公司股票(代號：6187)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年3月3日起10個營業日(115年3月3日至115年3月16日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -3477,7 +3232,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3491,7 +3246,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -3500,154 +3255,154 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>萬潤科技股份有限公司股票(代號：6187)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年3月3日起10個營業日(115年3月3日至115年3月16日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>萬潤科技股份有限公司股票(代號：6187)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年3月6日起10個營業日(115年3月6日至115年3月19日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-19</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款</t>
+          <t>連續5個營業日</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>萬潤科技股份有限公司股票(代號：6187)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年3月6日起10個營業日(115年3月6日至115年3月19日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>華星光通科技股份有限公司股票(代號：4979)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年3月27日起10個營業日(115年3月27日至115年4月13日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-13</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>連續5個營業日</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>華星光通科技股份有限公司股票(代號：4979)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年3月27日起10個營業日(115年3月27日至115年4月13日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>萬潤科技股份有限公司股票(代號：6187)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年3月30日起10個營業日(115年3月30日至115年4月14日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款</t>
+          <t>連續三次</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>萬潤科技股份有限公司股票(代號：6187)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年3月30日起10個營業日(115年3月30日至115年4月14日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>第一次處置</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -3665,59 +3420,59 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>連續三次</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>第一次處置</t>
+          <t>華星光通科技股份有限公司股票(代號：4979)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年4月21日起10個營業日(115年4月21日至115年5月5日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-05</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3731,153 +3486,153 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款</t>
+          <t>連續5個營業日</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>華星光通科技股份有限公司股票(代號：4979)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年4月21日起10個營業日(115年4月21日至115年5月5日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>華星光通科技股份有限公司股票(代號：4979)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年5月13日起10個營業日(115年5月13日至115年5月26日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>連續5個營業日</t>
+          <t>連續三次</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>華星光通科技股份有限公司股票(代號：4979)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年5月13日起10個營業日(115年5月13日至115年5月26日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>第一次處置</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>連續三次</t>
+          <t>連續5個營業日</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>第一次處置</t>
+          <t>華星光通科技股份有限公司股票(代號：4979)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年6月3日起10個營業日(115年6月3日至115年6月16日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>連續5個營業日</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>華星光通科技股份有限公司股票(代號：4979)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年6月3日起10個營業日(115年6月3日至115年6月16日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>大綜電腦系統股份有限公司股票(代號：3147)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年6月8日起10個營業日(115年6月8日至115年6月22日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-22</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3891,7 +3646,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -3900,97 +3655,97 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>大綜電腦系統股份有限公司股票(代號：3147)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年6月8日起10個營業日(115年6月8日至115年6月22日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>大綜電腦系統股份有限公司股票(代號：3147)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年6月11日起10個營業日(115年6月11日至115年6月25日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款</t>
+          <t>最近10個營業日內有6個營業日</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>大綜電腦系統股份有限公司股票(代號：3147)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年6月11日起10個營業日(115年6月11日至115年6月25日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>萬潤科技股份有限公司股票(代號：6187)因最近10個營業日內有6個營業日經本中心公布注意交易資訊，爰自115年6月17日起10個營業日(115年6月17日至115年7月1日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>最近10個營業日內有6個營業日</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>萬潤科技股份有限公司股票(代號：6187)因最近10個營業日內有6個營業日經本中心公布注意交易資訊，爰自115年6月17日起10個營業日(115年6月17日至115年7月1日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>大綜電腦系統股份有限公司股票(代號：3147)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年7月6日起10個營業日(115年7月6日至115年7月17日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-17</t>
         </is>
       </c>
     </row>
@@ -4397,61 +4152,61 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>連續3個營業日及沖銷標準</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>威剛科技股份有限公司股票(代號：3260)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，且最近3個營業日曾達本中心作業要點第四條第一項第十三款經本中心公布注意交易資訊，爰自115年01月07日起12個營業日(115年01月07日至115年01月22日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>竹陞科技股份有限公司股票(代號：6739)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年02月03日起10個營業日(115年02月03日至115年02月25日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-02-25</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -4460,194 +4215,194 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>第二次處置</t>
+          <t>第一次處置</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-02-26</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款</t>
+          <t>連續五次</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>竹陞科技股份有限公司股票(代號：6739)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年02月03日起10個營業日(115年02月03日至115年02月25日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>第二次處置</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-20</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>最近十個營業日已有六次</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>第一次處置</t>
+          <t>威剛科技股份有限公司股票(代號：3260)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年3月19日起10個營業日(115年3月19日至115年4月1日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>連續五次</t>
+          <t>連續三次</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>第二次處置</t>
+          <t>第一次處置</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款</t>
+          <t>最近十個營業日已有六次</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>威剛科技股份有限公司股票(代號：3260)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年3月19日起10個營業日(115年3月19日至115年4月1日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>第一次處置</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -4665,69 +4420,69 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>最近十個營業日已有六次</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>第一次處置</t>
+          <t>普萊德科技股份有限公司股票(代號：6263)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年5月15日起10個營業日(115年5月15日至115年5月28日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -4745,69 +4500,69 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款</t>
+          <t>最近十個營業日已有六次</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>普萊德科技股份有限公司股票(代號：6263)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年5月15日起10個營業日(115年5月15日至115年5月28日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>第一次處置</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-22</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -4815,7 +4570,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>連續三次</t>
+          <t>最近十個營業日已有六次</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4825,29 +4580,29 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>建榮</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -4855,47 +4610,47 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>最近十個營業日已有六次</t>
+          <t>連續5個營業日</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>第一次處置</t>
+          <t>建榮工業材料股份有限公司股票(代號：5340)因連續5個營業日經本中心公布注意交易資訊，爰自115年01月22日起10個營業日(115年01月22日至115年02月04日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-02-04</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>最近十個營業日已有六次</t>
+          <t>連續三次</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4905,19 +4660,19 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-02-25</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4931,7 +4686,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -4940,64 +4695,64 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>建榮工業材料股份有限公司股票(代號：5340)因連續5個營業日經本中心公布注意交易資訊，爰自115年01月22日起10個營業日(115年01月22日至115年02月04日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>建榮工業材料股份有限公司股票(代號：5340)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年2月23日起10個營業日(115年2月23日至115年3月9日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>建榮</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>連續三次</t>
+          <t>連續5個營業日</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>第一次處置</t>
+          <t>建榮工業材料股份有限公司股票(代號：5340)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年3月17日起10個營業日(115年3月17日至115年3月30日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5011,123 +4766,123 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>連續5個營業日</t>
+          <t>最近10個營業日內有6個營業日</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>建榮工業材料股份有限公司股票(代號：5340)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年2月23日起10個營業日(115年2月23日至115年3月9日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>建榮工業材料股份有限公司股票(代號：5340)最近30個營業日內曾發布處置，又因最近10個營業日內有6個營業日經本中心公布注意交易資訊，爰自115年4月21日起10個營業日(115年4月21日至115年5月5日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-05-05</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>連續5個營業日</t>
+          <t>連續三次</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>建榮工業材料股份有限公司股票(代號：5340)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年3月17日起10個營業日(115年3月17日至115年3月30日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>第一次處置</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>最近10個營業日內有6個營業日</t>
+          <t>連續三次</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>建榮工業材料股份有限公司股票(代號：5340)最近30個營業日內曾發布處置，又因最近10個營業日內有6個營業日經本中心公布注意交易資訊，爰自115年4月21日起10個營業日(115年4月21日至115年5月5日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>第一次處置</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -5145,29 +4900,29 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -5180,34 +4935,34 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>第一次處置</t>
+          <t>第二次處置</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -5215,7 +4970,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>連續三次</t>
+          <t>最近十個營業日已有六次</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -5225,90 +4980,10 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>3653</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>1</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>連續三次</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>第二次處置</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2383</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>台光電</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>1</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>最近十個營業日已有六次</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>第一次處置</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
@@ -5393,28 +5068,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:C100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>stock_id</t>
+          <t>代號</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>30d 借券量</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>end_date</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>reason</t>
+          <t>最新日借券</t>
         </is>
       </c>
     </row>
@@ -5424,116 +5094,63 @@
           <t>2330</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>除息</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C101"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>30d 借券量</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>最新日借券</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
-      </c>
       <c r="B2" t="n">
-        <v>299503</v>
+        <v>278394</v>
       </c>
       <c r="C2" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>184965</v>
+        <v>154178</v>
       </c>
       <c r="C3" t="n">
-        <v>73</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>178228</v>
+        <v>151173</v>
       </c>
       <c r="C4" t="n">
-        <v>2000</v>
+        <v>282</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>133623</v>
+        <v>124179</v>
       </c>
       <c r="C5" t="n">
-        <v>132</v>
+        <v>3360</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>104272</v>
+        <v>102952</v>
       </c>
       <c r="C6" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7">
@@ -5543,23 +5160,23 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>89312</v>
+        <v>85610</v>
       </c>
       <c r="C7" t="n">
-        <v>3000</v>
+        <v>300</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>88714</v>
+        <v>81462</v>
       </c>
       <c r="C8" t="n">
-        <v>1470</v>
+        <v>18497</v>
       </c>
     </row>
     <row r="9">
@@ -5569,101 +5186,101 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>85406</v>
+        <v>80639</v>
       </c>
       <c r="C9" t="n">
-        <v>136</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>81946</v>
+        <v>70012</v>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>572</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>81507</v>
+        <v>58154</v>
       </c>
       <c r="C11" t="n">
-        <v>200</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>60438</v>
+        <v>53142</v>
       </c>
       <c r="C12" t="n">
-        <v>345</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>57073</v>
+        <v>48163</v>
       </c>
       <c r="C13" t="n">
-        <v>876</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>51339</v>
+        <v>42339</v>
       </c>
       <c r="C14" t="n">
-        <v>450</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>50657</v>
+        <v>37589</v>
       </c>
       <c r="C15" t="n">
-        <v>388</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>39632</v>
+        <v>30224</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17">
@@ -5673,49 +5290,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>29798</v>
+        <v>19254</v>
       </c>
       <c r="C17" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>20590</v>
+        <v>16938</v>
       </c>
       <c r="C18" t="n">
-        <v>15</v>
+        <v>227</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18831</v>
+        <v>15258</v>
       </c>
       <c r="C19" t="n">
-        <v>150</v>
+        <v>184</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17308</v>
+        <v>14854</v>
       </c>
       <c r="C20" t="n">
-        <v>50</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21">
@@ -5725,85 +5342,85 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16153</v>
+        <v>14323</v>
       </c>
       <c r="C21" t="n">
-        <v>117</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>15684</v>
+        <v>11845</v>
       </c>
       <c r="C22" t="n">
-        <v>3203</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>13285</v>
+        <v>11027</v>
       </c>
       <c r="C23" t="n">
-        <v>500</v>
+        <v>177</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>13209</v>
+        <v>10144</v>
       </c>
       <c r="C24" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>12793</v>
+        <v>9759</v>
       </c>
       <c r="C25" t="n">
-        <v>18</v>
+        <v>276</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>12308</v>
+        <v>9627</v>
       </c>
       <c r="C26" t="n">
-        <v>200</v>
+        <v>135</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10039</v>
+        <v>9255</v>
       </c>
       <c r="C27" t="n">
         <v>6</v>
@@ -5812,92 +5429,92 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>9569</v>
+        <v>8572</v>
       </c>
       <c r="C28" t="n">
-        <v>577</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>8382</v>
+        <v>6290</v>
       </c>
       <c r="C29" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>7944</v>
+        <v>6194</v>
       </c>
       <c r="C30" t="n">
-        <v>180</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>7858</v>
+        <v>6105</v>
       </c>
       <c r="C31" t="n">
-        <v>35</v>
+        <v>93</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>7561</v>
+        <v>5945</v>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7328</v>
+        <v>5942</v>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>6411</v>
+        <v>5359</v>
       </c>
       <c r="C34" t="n">
-        <v>430</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35">
@@ -5907,10 +5524,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>6112</v>
+        <v>5344</v>
       </c>
       <c r="C35" t="n">
-        <v>120</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -5920,85 +5537,85 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>6068</v>
+        <v>5256</v>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>5810</v>
+        <v>5239</v>
       </c>
       <c r="C37" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>5502</v>
+        <v>4921</v>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>5271</v>
+        <v>4606</v>
       </c>
       <c r="C39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4953</v>
+        <v>4361</v>
       </c>
       <c r="C40" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4945</v>
+        <v>4249</v>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4936</v>
+        <v>4073</v>
       </c>
       <c r="C42" t="n">
         <v>10</v>
@@ -6007,349 +5624,349 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4808</v>
+        <v>4027</v>
       </c>
       <c r="C43" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4771</v>
+        <v>3696</v>
       </c>
       <c r="C44" t="n">
-        <v>148</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4770</v>
+        <v>3662</v>
       </c>
       <c r="C45" t="n">
-        <v>453</v>
+        <v>122</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4679</v>
+        <v>3646</v>
       </c>
       <c r="C46" t="n">
-        <v>6</v>
+        <v>272</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4636</v>
+        <v>3603</v>
       </c>
       <c r="C47" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4089</v>
+        <v>3566</v>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>61</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3964</v>
+        <v>3510</v>
       </c>
       <c r="C49" t="n">
-        <v>28</v>
+        <v>86</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3921</v>
+        <v>3399</v>
       </c>
       <c r="C50" t="n">
-        <v>15</v>
+        <v>274</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3920</v>
+        <v>3377</v>
       </c>
       <c r="C51" t="n">
-        <v>39</v>
+        <v>116</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3833</v>
+        <v>3157</v>
       </c>
       <c r="C52" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3719</v>
+        <v>3118</v>
       </c>
       <c r="C53" t="n">
-        <v>119</v>
+        <v>222</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3498</v>
+        <v>3074</v>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3476</v>
+        <v>2702</v>
       </c>
       <c r="C55" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3379</v>
+        <v>2653</v>
       </c>
       <c r="C56" t="n">
-        <v>9</v>
+        <v>137</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3236</v>
+        <v>2487</v>
       </c>
       <c r="C57" t="n">
-        <v>134</v>
+        <v>50</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>3012</v>
+        <v>2424</v>
       </c>
       <c r="C58" t="n">
-        <v>267</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2699</v>
+        <v>2384</v>
       </c>
       <c r="C59" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2641</v>
+        <v>2315</v>
       </c>
       <c r="C60" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2610</v>
+        <v>2216</v>
       </c>
       <c r="C61" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2388</v>
+        <v>2047</v>
       </c>
       <c r="C62" t="n">
-        <v>60</v>
+        <v>18</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2339</v>
+        <v>2034</v>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2326</v>
+        <v>1859</v>
       </c>
       <c r="C64" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2282</v>
+        <v>1856</v>
       </c>
       <c r="C65" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1997</v>
+        <v>1765</v>
       </c>
       <c r="C66" t="n">
-        <v>15</v>
+        <v>275</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1913</v>
+        <v>1715</v>
       </c>
       <c r="C67" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1906</v>
+        <v>1560</v>
       </c>
       <c r="C68" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1530</v>
+        <v>1500</v>
       </c>
       <c r="C69" t="n">
         <v>1</v>
@@ -6358,465 +5975,404 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1419</v>
+        <v>1331</v>
       </c>
       <c r="C70" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1383</v>
+        <v>1315</v>
       </c>
       <c r="C71" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1339</v>
+        <v>1164</v>
       </c>
       <c r="C72" t="n">
-        <v>48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1286</v>
+        <v>1076</v>
       </c>
       <c r="C73" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1209</v>
+        <v>1065</v>
       </c>
       <c r="C74" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1152</v>
+        <v>1053</v>
       </c>
       <c r="C75" t="n">
-        <v>16</v>
+        <v>51</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>933</v>
+        <v>909</v>
       </c>
       <c r="C76" t="n">
-        <v>9</v>
+        <v>68</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>900</v>
+        <v>827</v>
       </c>
       <c r="C77" t="n">
-        <v>1</v>
+        <v>217</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>879</v>
+        <v>763</v>
       </c>
       <c r="C78" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>867</v>
+        <v>684</v>
       </c>
       <c r="C79" t="n">
-        <v>139</v>
+        <v>295</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>618</v>
+        <v>662</v>
       </c>
       <c r="C80" t="n">
-        <v>3</v>
+        <v>89</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>602</v>
+        <v>634</v>
       </c>
       <c r="C81" t="n">
-        <v>128</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>588</v>
+        <v>617</v>
       </c>
       <c r="C82" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>548</v>
+        <v>571</v>
       </c>
       <c r="C83" t="n">
-        <v>25</v>
+        <v>213</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>488</v>
+        <v>548</v>
       </c>
       <c r="C84" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>471</v>
+        <v>506</v>
       </c>
       <c r="C85" t="n">
-        <v>51</v>
+        <v>14</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>312</v>
+        <v>446</v>
       </c>
       <c r="C86" t="n">
-        <v>84</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>311</v>
+        <v>297</v>
       </c>
       <c r="C87" t="n">
-        <v>35</v>
+        <v>250</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>297</v>
+        <v>267</v>
       </c>
       <c r="C88" t="n">
-        <v>250</v>
+        <v>10</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>260</v>
+        <v>241</v>
       </c>
       <c r="C89" t="n">
-        <v>196</v>
+        <v>38</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>243</v>
+        <v>170</v>
       </c>
       <c r="C90" t="n">
-        <v>243</v>
+        <v>16</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C91" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B92" t="n">
         <v>148</v>
       </c>
       <c r="C92" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="C93" t="n">
-        <v>65</v>
+        <v>107</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="C94" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="C95" t="n">
-        <v>59</v>
+        <v>27</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="C96" t="n">
-        <v>57</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C97" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C98" t="n">
-        <v>21</v>
+        <v>45</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C99" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="C100" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>4303</t>
-        </is>
-      </c>
-      <c r="B101" t="n">
-        <v>20</v>
-      </c>
-      <c r="C101" t="n">
-        <v>20</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>stock_id</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>stock_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2024-01-25</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>6446</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>藥華藥</t>
-        </is>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/data/台股_警戒掃描.xlsx
+++ b/data/台股_警戒掃描.xlsx
@@ -548,12 +548,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>30d 151173 股, 最新日 282 股</t>
+          <t>30d 160132 股, 最新日 7575 股</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -618,12 +618,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>30d 124179 股, 最新日 3360 股</t>
+          <t>30d 109069 股, 最新日 1113 股</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -651,12 +651,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>30d 278394 股, 最新日 1 股</t>
+          <t>30d 124308 股, 最新日 244 股</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -684,12 +684,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>30d 154178 股, 最新日 27 股</t>
+          <t>30d 125970 股, 最新日 1600 股</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -717,12 +717,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>30d 80639 股, 最新日 30 股</t>
+          <t>30d 111219 股, 最新日 141 股</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -824,12 +824,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>30d 58154 股, 最新日 54 股</t>
+          <t>30d 61965 股, 最新日 100 股</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -857,12 +857,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>30d 70012 股, 最新日 572 股</t>
+          <t>30d 85154 股, 最新日 217 股</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -964,12 +964,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>30d 81462 股, 最新日 18497 股</t>
+          <t>30d 122033 股, 最新日 37269 股</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -1019,37 +1019,33 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>⚠️ 處置</t>
+          <t>🪦 借券爆量</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>最近10個營業日內有6個營業日 / 聯亞光電工業股份有限公司股票(代號：3081)最近30個營業日內曾發布處置，又因最近10個營業日內有6個營業日經本中心公布注意交易資訊，爰自115年3月12日起10個營業日(115年3月12日至115年3月25日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-03-12 ~ 2026-03-25</t>
-        </is>
-      </c>
+          <t>30d 56880 股, 最新日 3823 股</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -1071,17 +1067,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 聯亞光電工業股份有限公司股票(代號：3081)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年02月04日起10個營業日(115年02月04日至115年02月26日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>最近10個營業日內有6個營業日 / 聯亞光電工業股份有限公司股票(代號：3081)最近30個營業日內曾發布處置，又因最近10個營業日內有6個營業日經本中心公布注意交易資訊，爰自115年3月12日起10個營業日(115年3月12日至115年3月25日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-02-04 ~ 2026-02-26</t>
+          <t>2026-03-12 ~ 2026-03-25</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1108,17 +1104,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 聯亞光電工業股份有限公司股票(代號：3081)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年01月30日起10個營業日(115年01月30日至115年02月23日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 聯亞光電工業股份有限公司股票(代號：3081)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年02月04日起10個營業日(115年02月04日至115年02月26日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-01-30 ~ 2026-02-23</t>
+          <t>2026-02-04 ~ 2026-02-26</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1130,12 +1126,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1145,17 +1141,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 大綜電腦系統股份有限公司股票(代號：3147)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年7月6日起10個營業日(115年7月6日至115年7月17日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 聯亞光電工業股份有限公司股票(代號：3081)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年01月30日起10個營業日(115年01月30日至115年02月23日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-06 ~ 2026-07-17</t>
+          <t>2026-01-30 ~ 2026-02-23</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1182,17 +1178,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 大綜電腦系統股份有限公司股票(代號：3147)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年6月11日起10個營業日(115年6月11日至115年6月25日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 大綜電腦系統股份有限公司股票(代號：3147)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年7月6日起10個營業日(115年7月6日至115年7月17日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-11 ~ 2026-06-25</t>
+          <t>2026-07-06 ~ 2026-07-17</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1219,17 +1215,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 大綜電腦系統股份有限公司股票(代號：3147)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年6月8日起10個營業日(115年6月8日至115年6月22日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 大綜電腦系統股份有限公司股票(代號：3147)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年6月11日起10個營業日(115年6月11日至115年6月25日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-08 ~ 2026-06-22</t>
+          <t>2026-06-11 ~ 2026-06-25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1241,82 +1237,82 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>🪦 借券爆量</t>
+          <t>⚠️ 處置</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>30d 102952 股, 最新日 90 股</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 大綜電腦系統股份有限公司股票(代號：3147)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年6月8日起10個營業日(115年6月8日至115年6月22日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-06-08 ~ 2026-06-22</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>⚠️ 處置</t>
+          <t>🪦 借券爆量</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 威剛科技股份有限公司股票(代號：3260)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年3月19日起10個營業日(115年3月19日至115年4月1日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-03-19 ~ 2026-04-01</t>
-        </is>
-      </c>
+          <t>30d 128958 股, 最新日 415 股</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1326,34 +1322,34 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>連續三次 / 第一次處置</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 威剛科技股份有限公司股票(代號：3260)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年3月19日起10個營業日(115年3月19日至115年4月1日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-17 ~ 2026-04-30</t>
+          <t>2026-03-19 ~ 2026-04-01</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1363,17 +1359,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>最近十個營業日已有六次 / 第一次處置</t>
+          <t>連續三次 / 第一次處置</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-30 ~ 2026-07-13</t>
+          <t>2026-04-17 ~ 2026-04-30</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1400,17 +1396,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>連續三次 / 第一次處置</t>
+          <t>最近十個營業日已有六次 / 第一次處置</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-13 ~ 2026-05-26</t>
+          <t>2026-06-30 ~ 2026-07-13</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1422,12 +1418,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1437,7 +1433,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1447,24 +1443,24 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-14 ~ 2026-04-27</t>
+          <t>2026-05-13 ~ 2026-05-26</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1474,17 +1470,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>連續三次 / 第二次處置</t>
+          <t>連續三次 / 第一次處置</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-13 ~ 2026-05-26</t>
+          <t>2026-04-14 ~ 2026-04-27</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1511,17 +1507,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>連續三次 / 第一次處置</t>
+          <t>連續三次 / 第二次處置</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-24 ~ 2026-05-08</t>
+          <t>2026-05-13 ~ 2026-05-26</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1533,60 +1529,64 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>🪦 借券爆量</t>
+          <t>⚠️ 處置</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>30d 53142 股, 最新日 129 股</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
+          <t>連續三次 / 第一次處置</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-04-24 ~ 2026-05-08</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>🚫 暫停</t>
+          <t>🪦 借券爆量</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>暫停8:00, 恢復2026-04-29</t>
+          <t>30d 52498 股, 最新日 282 股</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
@@ -1599,34 +1599,30 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>信立</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>⚠️ 處置</t>
+          <t>🚫 暫停</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>連續三次 / 第一次處置</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-04-16 ~ 2026-04-29</t>
-        </is>
-      </c>
+          <t>暫停8:00, 恢復2026-04-29</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>B</t>
@@ -1636,30 +1632,34 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>六方科-KY</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>🪦 借券爆量</t>
+          <t>⚠️ 處置</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>30d 85610 股, 最新日 300 股</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
+          <t>連續三次 / 第一次處置</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-04-16 ~ 2026-04-29</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>B</t>
@@ -1669,34 +1669,30 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>⚠️ 處置</t>
+          <t>🪦 借券爆量</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>連續5個營業日 / 華星光通科技股份有限公司股票(代號：4979)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年6月3日起10個營業日(115年6月3日至115年6月16日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-06-03 ~ 2026-06-16</t>
-        </is>
-      </c>
+          <t>30d 81768 股, 最新日 790 股</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>B</t>
@@ -1721,17 +1717,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>連續5個營業日 / 華星光通科技股份有限公司股票(代號：4979)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年5月13日起10個營業日(115年5月13日至115年5月26日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>連續5個營業日 / 華星光通科技股份有限公司股票(代號：4979)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年6月3日起10個營業日(115年6月3日至115年6月16日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-13 ~ 2026-05-26</t>
+          <t>2026-06-03 ~ 2026-06-16</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1758,17 +1754,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 華星光通科技股份有限公司股票(代號：4979)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年4月21日起10個營業日(115年4月21日至115年5月5日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>連續5個營業日 / 華星光通科技股份有限公司股票(代號：4979)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年5月13日起10個營業日(115年5月13日至115年5月26日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-21 ~ 2026-05-05</t>
+          <t>2026-05-13 ~ 2026-05-26</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1795,17 +1791,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>連續5個營業日 / 華星光通科技股份有限公司股票(代號：4979)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年3月27日起10個營業日(115年3月27日至115年4月13日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 華星光通科技股份有限公司股票(代號：4979)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年4月21日起10個營業日(115年4月21日至115年5月5日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-27 ~ 2026-04-13</t>
+          <t>2026-04-21 ~ 2026-05-05</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1832,17 +1828,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>連續5個營業日 / 華星光通科技股份有限公司股票(代號：4979)因連續5個營業日經本中心公布注意交易資訊，爰自115年3月3日起10個營業日(115年3月3日至115年3月16日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>連續5個營業日 / 華星光通科技股份有限公司股票(代號：4979)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年3月27日起10個營業日(115年3月27日至115年4月13日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-03 ~ 2026-03-16</t>
+          <t>2026-03-27 ~ 2026-04-13</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1854,12 +1850,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1869,17 +1865,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>連續三次 / 第一次處置</t>
+          <t>連續5個營業日 / 華星光通科技股份有限公司股票(代號：4979)因連續5個營業日經本中心公布注意交易資訊，爰自115年3月3日起10個營業日(115年3月3日至115年3月16日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-13 ~ 2026-04-24</t>
+          <t>2026-03-03 ~ 2026-03-16</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1891,12 +1887,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1906,22 +1902,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>最近10個營業日內有6個營業日 / 建榮工業材料股份有限公司股票(代號：5340)最近30個營業日內曾發布處置，又因最近10個營業日內有6個營業日經本中心公布注意交易資訊，爰自115年4月21日起10個營業日(115年4月21日至115年5月5日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>連續三次 / 第一次處置</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-21 ~ 2026-05-05</t>
+          <t>2026-04-13 ~ 2026-04-24</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1943,17 +1939,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>連續5個營業日 / 建榮工業材料股份有限公司股票(代號：5340)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年3月17日起10個營業日(115年3月17日至115年3月30日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>最近10個營業日內有6個營業日 / 建榮工業材料股份有限公司股票(代號：5340)最近30個營業日內曾發布處置，又因最近10個營業日內有6個營業日經本中心公布注意交易資訊，爰自115年4月21日起10個營業日(115年4月21日至115年5月5日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-17 ~ 2026-03-30</t>
+          <t>2026-04-21 ~ 2026-05-05</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1980,17 +1976,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>連續5個營業日 / 建榮工業材料股份有限公司股票(代號：5340)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年2月23日起10個營業日(115年2月23日至115年3月9日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>連續5個營業日 / 建榮工業材料股份有限公司股票(代號：5340)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年3月17日起10個營業日(115年3月17日至115年3月30日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-02-23 ~ 2026-03-09</t>
+          <t>2026-03-17 ~ 2026-03-30</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2017,17 +2013,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>連續5個營業日 / 建榮工業材料股份有限公司股票(代號：5340)因連續5個營業日經本中心公布注意交易資訊，爰自115年01月22日起10個營業日(115年01月22日至115年02月04日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>連續5個營業日 / 建榮工業材料股份有限公司股票(代號：5340)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年2月23日起10個營業日(115年2月23日至115年3月9日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-01-22 ~ 2026-02-04</t>
+          <t>2026-02-23 ~ 2026-03-09</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2039,12 +2035,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>建榮</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2054,17 +2050,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>最近10個營業日內有6個營業日 / 萬潤科技股份有限公司股票(代號：6187)因最近10個營業日內有6個營業日經本中心公布注意交易資訊，爰自115年6月17日起10個營業日(115年6月17日至115年7月1日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>連續5個營業日 / 建榮工業材料股份有限公司股票(代號：5340)因連續5個營業日經本中心公布注意交易資訊，爰自115年01月22日起10個營業日(115年01月22日至115年02月04日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-17 ~ 2026-07-01</t>
+          <t>2026-01-22 ~ 2026-02-04</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2091,17 +2087,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 萬潤科技股份有限公司股票(代號：6187)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年3月30日起10個營業日(115年3月30日至115年4月14日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>最近10個營業日內有6個營業日 / 萬潤科技股份有限公司股票(代號：6187)因最近10個營業日內有6個營業日經本中心公布注意交易資訊，爰自115年6月17日起10個營業日(115年6月17日至115年7月1日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-30 ~ 2026-04-14</t>
+          <t>2026-06-17 ~ 2026-07-01</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2128,17 +2124,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 萬潤科技股份有限公司股票(代號：6187)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年3月6日起10個營業日(115年3月6日至115年3月19日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 萬潤科技股份有限公司股票(代號：6187)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年3月30日起10個營業日(115年3月30日至115年4月14日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-06 ~ 2026-03-19</t>
+          <t>2026-03-30 ~ 2026-04-14</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2165,17 +2161,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 萬潤科技股份有限公司股票(代號：6187)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年3月3日起10個營業日(115年3月3日至115年3月16日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 萬潤科技股份有限公司股票(代號：6187)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年3月6日起10個營業日(115年3月6日至115年3月19日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-03 ~ 2026-03-16</t>
+          <t>2026-03-06 ~ 2026-03-19</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2187,12 +2183,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2202,34 +2198,34 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 普萊德科技股份有限公司股票(代號：6263)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年5月15日起10個營業日(115年5月15日至115年5月28日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 萬潤科技股份有限公司股票(代號：6187)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年3月3日起10個營業日(115年3月3日至115年3月16日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-15 ~ 2026-05-28</t>
+          <t>2026-03-03 ~ 2026-03-16</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2239,17 +2235,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 台燿科技股份有限公司股票(代號：6274)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年5月11日起10個營業日(115年5月11日至115年5月22日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 普萊德科技股份有限公司股票(代號：6263)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年5月15日起10個營業日(115年5月15日至115年5月28日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-11 ~ 2026-05-22</t>
+          <t>2026-05-15 ~ 2026-05-28</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2276,17 +2272,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 台燿科技股份有限公司股票(代號：6274)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年4月17日起10個營業日(115年4月17日至115年4月30日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 台燿科技股份有限公司股票(代號：6274)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年5月11日起10個營業日(115年5月11日至115年5月22日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-17 ~ 2026-04-30</t>
+          <t>2026-05-11 ~ 2026-05-22</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2298,12 +2294,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2313,22 +2309,22 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>最近十個營業日已有六次 / 第一次處置</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 台燿科技股份有限公司股票(代號：6274)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年4月17日起10個營業日(115年4月17日至115年4月30日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-08 ~ 2026-06-22</t>
+          <t>2026-04-17 ~ 2026-04-30</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2346,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2360,7 +2356,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-22 ~ 2026-05-06</t>
+          <t>2026-06-08 ~ 2026-06-22</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2387,17 +2383,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>連續五次 / 第二次處置</t>
+          <t>最近十個營業日已有六次 / 第一次處置</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-09 ~ 2026-03-20</t>
+          <t>2026-04-22 ~ 2026-05-06</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2424,17 +2420,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>最近十個營業日已有六次 / 第一次處置</t>
+          <t>連續五次 / 第二次處置</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-04 ~ 2026-02-26</t>
+          <t>2026-03-09 ~ 2026-03-20</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2446,12 +2442,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2461,34 +2457,34 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>連續三次 / 第一次處置</t>
+          <t>最近十個營業日已有六次 / 第一次處置</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-03 ~ 2026-02-25</t>
+          <t>2026-02-04 ~ 2026-02-26</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2498,34 +2494,34 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>最近十個營業日已有六次 / 第一次處置</t>
+          <t>連續三次 / 第一次處置</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-26 ~ 2026-04-10</t>
+          <t>2026-02-03 ~ 2026-02-25</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2535,34 +2531,34 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 竹陞科技股份有限公司股票(代號：6739)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年02月03日起10個營業日(115年02月03日至115年02月25日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>最近十個營業日已有六次 / 第一次處置</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-02-03 ~ 2026-02-25</t>
+          <t>2026-03-26 ~ 2026-04-10</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2572,17 +2568,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>連續三次 / 第二次處置</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 竹陞科技股份有限公司股票(代號：6739)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年02月03日起10個營業日(115年02月03日至115年02月25日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-24 ~ 2026-05-08</t>
+          <t>2026-02-03 ~ 2026-02-25</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2609,7 +2605,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2619,7 +2615,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-20 ~ 2026-04-02</t>
+          <t>2026-04-24 ~ 2026-05-08</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2646,17 +2642,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>連續三次 / 第一次處置</t>
+          <t>連續三次 / 第二次處置</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-17 ~ 2026-03-30</t>
+          <t>2026-03-20 ~ 2026-04-02</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2668,12 +2664,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2683,7 +2679,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2693,12 +2689,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-24 ~ 2026-07-07</t>
+          <t>2026-03-17 ~ 2026-03-30</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -2720,17 +2716,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>最近十個營業日已有六次 / 第一次處置</t>
+          <t>連續三次 / 第一次處置</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-15 ~ 2026-04-28</t>
+          <t>2026-06-24 ~ 2026-07-07</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2757,17 +2753,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>最近十個營業日已有六次 / 第二次處置</t>
+          <t>最近十個營業日已有六次 / 第一次處置</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-25 ~ 2026-03-11</t>
+          <t>2026-04-15 ~ 2026-04-28</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2794,7 +2790,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2804,7 +2800,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-01-16 ~ 2026-01-29</t>
+          <t>2026-02-25 ~ 2026-03-11</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2824,7 +2820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3752,47 +3748,47 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>最近十個營業日已有六次</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>第二次處置</t>
+          <t>聯亞光電工業股份有限公司股票(代號：3081)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年01月30日起10個營業日(115年01月30日至115年02月23日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-23</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3806,7 +3802,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -3815,154 +3811,154 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>聯亞光電工業股份有限公司股票(代號：3081)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年01月30日起10個營業日(115年01月30日至115年02月23日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>聯亞光電工業股份有限公司股票(代號：3081)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年02月04日起10個營業日(115年02月04日至115年02月26日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-26</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款</t>
+          <t>最近十個營業日已有六次</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>聯亞光電工業股份有限公司股票(代號：3081)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年02月04日起10個營業日(115年02月04日至115年02月26日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>第二次處置</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-11</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>最近十個營業日已有六次</t>
+          <t>最近10個營業日內有6個營業日</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>第二次處置</t>
+          <t>聯亞光電工業股份有限公司股票(代號：3081)最近30個營業日內曾發布處置，又因最近10個營業日內有6個營業日經本中心公布注意交易資訊，爰自115年3月12日起10個營業日(115年3月12日至115年3月25日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-25</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>最近10個營業日內有6個營業日</t>
+          <t>最近十個營業日已有六次</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>聯亞光電工業股份有限公司股票(代號：3081)最近30個營業日內曾發布處置，又因最近10個營業日內有6個營業日經本中心公布注意交易資訊，爰自115年3月12日起10個營業日(115年3月12日至115年3月25日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>第一次處置</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>六方科-KY</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -3970,7 +3966,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>最近十個營業日已有六次</t>
+          <t>連續三次</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3980,59 +3976,59 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>連續三次</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>第一次處置</t>
+          <t>台燿科技股份有限公司股票(代號：6274)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年4月17日起10個營業日(115年4月17日至115年4月30日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4055,144 +4051,144 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>台燿科技股份有限公司股票(代號：6274)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年4月17日起10個營業日(115年4月17日至115年4月30日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>台燿科技股份有限公司股票(代號：6274)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年5月11日起10個營業日(115年5月11日至115年5月22日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款</t>
+          <t>連續三次</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>台燿科技股份有限公司股票(代號：6274)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年5月11日起10個營業日(115年5月11日至115年5月22日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>第一次處置</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-07-07</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>連續三次</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>第一次處置</t>
+          <t>竹陞科技股份有限公司股票(代號：6739)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年02月03日起10個營業日(115年02月03日至115年02月25日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-02-25</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款</t>
+          <t>最近十個營業日已有六次</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>竹陞科技股份有限公司股票(代號：6739)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年02月03日起10個營業日(115年02月03日至115年02月25日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>第一次處置</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4210,119 +4206,119 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>最近十個營業日已有六次</t>
+          <t>連續五次</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>第一次處置</t>
+          <t>第二次處置</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-20</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>連續五次</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>第二次處置</t>
+          <t>威剛科技股份有限公司股票(代號：3260)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年3月19日起10個營業日(115年3月19日至115年4月1日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款</t>
+          <t>連續三次</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>威剛科技股份有限公司股票(代號：3260)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年3月19日起10個營業日(115年3月19日至115年4月1日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>第一次處置</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -4330,7 +4326,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>連續三次</t>
+          <t>最近十個營業日已有六次</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4340,29 +4336,29 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -4370,7 +4366,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>最近十個營業日已有六次</t>
+          <t>連續三次</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4380,109 +4376,109 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>連續三次</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>第一次處置</t>
+          <t>普萊德科技股份有限公司股票(代號：6263)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年5月15日起10個營業日(115年5月15日至115年5月28日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款</t>
+          <t>連續三次</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>普萊德科技股份有限公司股票(代號：6263)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年5月15日起10個營業日(115年5月15日至115年5月28日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>第一次處置</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -4490,7 +4486,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>連續三次</t>
+          <t>最近十個營業日已有六次</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4500,29 +4496,29 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-22</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -4540,29 +4536,29 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>建榮</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -4570,109 +4566,109 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>最近十個營業日已有六次</t>
+          <t>連續5個營業日</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>第一次處置</t>
+          <t>建榮工業材料股份有限公司股票(代號：5340)因連續5個營業日經本中心公布注意交易資訊，爰自115年01月22日起10個營業日(115年01月22日至115年02月04日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-02-04</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>連續5個營業日</t>
+          <t>連續三次</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>建榮工業材料股份有限公司股票(代號：5340)因連續5個營業日經本中心公布注意交易資訊，爰自115年01月22日起10個營業日(115年01月22日至115年02月04日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>第一次處置</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-25</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>建榮</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>連續三次</t>
+          <t>連續5個營業日</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>第一次處置</t>
+          <t>建榮工業材料股份有限公司股票(代號：5340)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年2月23日起10個營業日(115年2月23日至115年3月9日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4686,7 +4682,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -4695,24 +4691,24 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>建榮工業材料股份有限公司股票(代號：5340)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年2月23日起10個營業日(115年2月23日至115年3月9日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>建榮工業材料股份有限公司股票(代號：5340)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年3月17日起10個營業日(115年3月17日至115年3月30日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4726,83 +4722,83 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>連續5個營業日</t>
+          <t>最近10個營業日內有6個營業日</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>建榮工業材料股份有限公司股票(代號：5340)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年3月17日起10個營業日(115年3月17日至115年3月30日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>建榮工業材料股份有限公司股票(代號：5340)最近30個營業日內曾發布處置，又因最近10個營業日內有6個營業日經本中心公布注意交易資訊，爰自115年4月21日起10個營業日(115年4月21日至115年5月5日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-05-05</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>最近10個營業日內有6個營業日</t>
+          <t>連續三次</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>建榮工業材料股份有限公司股票(代號：5340)最近30個營業日內曾發布處置，又因最近10個營業日內有6個營業日經本中心公布注意交易資訊，爰自115年4月21日起10個營業日(115年4月21日至115年5月5日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>第一次處置</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -4820,29 +4816,29 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -4860,12 +4856,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
@@ -4877,12 +4873,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -4895,7 +4891,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>第一次處置</t>
+          <t>第二次處置</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -4912,17 +4908,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -4930,60 +4926,20 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>連續三次</t>
+          <t>最近十個營業日已有六次</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>第二次處置</t>
+          <t>第一次處置</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2383</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>台光電</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>1</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>最近十個營業日已有六次</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>第一次處置</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
@@ -5068,7 +5024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C100"/>
+  <dimension ref="A1:C99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5091,118 +5047,118 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>278394</v>
+        <v>160132</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>7575</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>154178</v>
+        <v>128958</v>
       </c>
       <c r="C3" t="n">
-        <v>27</v>
+        <v>415</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>151173</v>
+        <v>125970</v>
       </c>
       <c r="C4" t="n">
-        <v>282</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>124179</v>
+        <v>124308</v>
       </c>
       <c r="C5" t="n">
-        <v>3360</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>102952</v>
+        <v>122033</v>
       </c>
       <c r="C6" t="n">
-        <v>90</v>
+        <v>37269</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>85610</v>
+        <v>111219</v>
       </c>
       <c r="C7" t="n">
-        <v>300</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>81462</v>
+        <v>109069</v>
       </c>
       <c r="C8" t="n">
-        <v>18497</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>80639</v>
+        <v>85154</v>
       </c>
       <c r="C9" t="n">
-        <v>30</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>70012</v>
+        <v>81768</v>
       </c>
       <c r="C10" t="n">
-        <v>572</v>
+        <v>790</v>
       </c>
     </row>
     <row r="11">
@@ -5212,75 +5168,75 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>58154</v>
+        <v>61965</v>
       </c>
       <c r="C11" t="n">
-        <v>54</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>53142</v>
+        <v>56880</v>
       </c>
       <c r="C12" t="n">
-        <v>129</v>
+        <v>3823</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>48163</v>
+        <v>52498</v>
       </c>
       <c r="C13" t="n">
-        <v>21</v>
+        <v>282</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>42339</v>
+        <v>48578</v>
       </c>
       <c r="C14" t="n">
-        <v>175</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>37589</v>
+        <v>43747</v>
       </c>
       <c r="C15" t="n">
-        <v>1066</v>
+        <v>300</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>30224</v>
+        <v>30813</v>
       </c>
       <c r="C16" t="n">
-        <v>150</v>
+        <v>163</v>
       </c>
     </row>
     <row r="17">
@@ -5290,75 +5246,75 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19254</v>
+        <v>28544</v>
       </c>
       <c r="C17" t="n">
-        <v>100</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16938</v>
+        <v>22444</v>
       </c>
       <c r="C18" t="n">
-        <v>227</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15258</v>
+        <v>19214</v>
       </c>
       <c r="C19" t="n">
-        <v>184</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>14854</v>
+        <v>16863</v>
       </c>
       <c r="C20" t="n">
-        <v>18</v>
+        <v>372</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14323</v>
+        <v>15491</v>
       </c>
       <c r="C21" t="n">
-        <v>20</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>11845</v>
+        <v>14896</v>
       </c>
       <c r="C22" t="n">
-        <v>44</v>
+        <v>881</v>
       </c>
     </row>
     <row r="23">
@@ -5368,36 +5324,36 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>11027</v>
+        <v>14072</v>
       </c>
       <c r="C23" t="n">
-        <v>177</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10144</v>
+        <v>12080</v>
       </c>
       <c r="C24" t="n">
-        <v>9</v>
+        <v>242</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>9759</v>
+        <v>11896</v>
       </c>
       <c r="C25" t="n">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="26">
@@ -5407,114 +5363,114 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>9627</v>
+        <v>9199</v>
       </c>
       <c r="C26" t="n">
-        <v>135</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9255</v>
+        <v>8676</v>
       </c>
       <c r="C27" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>8572</v>
+        <v>7929</v>
       </c>
       <c r="C28" t="n">
-        <v>71</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>6290</v>
+        <v>7890</v>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>6194</v>
+        <v>7051</v>
       </c>
       <c r="C30" t="n">
-        <v>4</v>
+        <v>578</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>6105</v>
+        <v>6856</v>
       </c>
       <c r="C31" t="n">
-        <v>93</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>5945</v>
+        <v>6487</v>
       </c>
       <c r="C32" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5942</v>
+        <v>6186</v>
       </c>
       <c r="C33" t="n">
-        <v>26</v>
+        <v>200</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>5359</v>
+        <v>6013</v>
       </c>
       <c r="C34" t="n">
-        <v>100</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35">
@@ -5524,75 +5480,75 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>5344</v>
+        <v>5760</v>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>5256</v>
+        <v>5583</v>
       </c>
       <c r="C36" t="n">
-        <v>76</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>5239</v>
+        <v>5419</v>
       </c>
       <c r="C37" t="n">
-        <v>28</v>
+        <v>92</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4921</v>
+        <v>5117</v>
       </c>
       <c r="C38" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4606</v>
+        <v>4528</v>
       </c>
       <c r="C39" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4361</v>
+        <v>4517</v>
       </c>
       <c r="C40" t="n">
-        <v>8</v>
+        <v>371</v>
       </c>
     </row>
     <row r="41">
@@ -5602,348 +5558,348 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4249</v>
+        <v>4433</v>
       </c>
       <c r="C41" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4073</v>
+        <v>3944</v>
       </c>
       <c r="C42" t="n">
-        <v>10</v>
+        <v>149</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4027</v>
+        <v>3799</v>
       </c>
       <c r="C43" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3696</v>
+        <v>3647</v>
       </c>
       <c r="C44" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3662</v>
+        <v>3632</v>
       </c>
       <c r="C45" t="n">
-        <v>122</v>
+        <v>35</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3646</v>
+        <v>3423</v>
       </c>
       <c r="C46" t="n">
-        <v>272</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3603</v>
+        <v>3367</v>
       </c>
       <c r="C47" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3566</v>
+        <v>3302</v>
       </c>
       <c r="C48" t="n">
-        <v>61</v>
+        <v>37</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3510</v>
+        <v>3020</v>
       </c>
       <c r="C49" t="n">
-        <v>86</v>
+        <v>186</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3399</v>
+        <v>2868</v>
       </c>
       <c r="C50" t="n">
-        <v>274</v>
+        <v>34</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3377</v>
+        <v>2813</v>
       </c>
       <c r="C51" t="n">
-        <v>116</v>
+        <v>29</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3157</v>
+        <v>2689</v>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3118</v>
+        <v>2596</v>
       </c>
       <c r="C53" t="n">
-        <v>222</v>
+        <v>35</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3074</v>
+        <v>2580</v>
       </c>
       <c r="C54" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2702</v>
+        <v>2569</v>
       </c>
       <c r="C55" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2653</v>
+        <v>2568</v>
       </c>
       <c r="C56" t="n">
-        <v>137</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2487</v>
+        <v>2560</v>
       </c>
       <c r="C57" t="n">
-        <v>50</v>
+        <v>776</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2424</v>
+        <v>2537</v>
       </c>
       <c r="C58" t="n">
-        <v>203</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2384</v>
+        <v>2366</v>
       </c>
       <c r="C59" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2315</v>
+        <v>2040</v>
       </c>
       <c r="C60" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2216</v>
+        <v>2020</v>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2047</v>
+        <v>2002</v>
       </c>
       <c r="C62" t="n">
-        <v>18</v>
+        <v>58</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2034</v>
+        <v>1862</v>
       </c>
       <c r="C63" t="n">
-        <v>55</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1859</v>
+        <v>1838</v>
       </c>
       <c r="C64" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1856</v>
+        <v>1804</v>
       </c>
       <c r="C65" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1765</v>
+        <v>1591</v>
       </c>
       <c r="C66" t="n">
-        <v>275</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1715</v>
+        <v>1560</v>
       </c>
       <c r="C67" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
@@ -5953,36 +5909,36 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1560</v>
+        <v>1550</v>
       </c>
       <c r="C68" t="n">
-        <v>30</v>
+        <v>110</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>1500</v>
       </c>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1331</v>
+        <v>1366</v>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="71">
@@ -5992,127 +5948,127 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1315</v>
+        <v>1284</v>
       </c>
       <c r="C71" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1164</v>
+        <v>1178</v>
       </c>
       <c r="C72" t="n">
-        <v>62</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1076</v>
+        <v>1174</v>
       </c>
       <c r="C73" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1065</v>
+        <v>1158</v>
       </c>
       <c r="C74" t="n">
-        <v>7</v>
+        <v>39</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1053</v>
+        <v>1150</v>
       </c>
       <c r="C75" t="n">
-        <v>51</v>
+        <v>113</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>909</v>
+        <v>1075</v>
       </c>
       <c r="C76" t="n">
-        <v>68</v>
+        <v>42</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>827</v>
+        <v>947</v>
       </c>
       <c r="C77" t="n">
-        <v>217</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>763</v>
+        <v>827</v>
       </c>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>217</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>684</v>
+        <v>819</v>
       </c>
       <c r="C79" t="n">
-        <v>295</v>
+        <v>36</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>662</v>
+        <v>806</v>
       </c>
       <c r="C80" t="n">
-        <v>89</v>
+        <v>11</v>
       </c>
     </row>
     <row r="81">
@@ -6122,62 +6078,62 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>634</v>
+        <v>755</v>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>617</v>
+        <v>738</v>
       </c>
       <c r="C82" t="n">
-        <v>5</v>
+        <v>54</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>571</v>
+        <v>592</v>
       </c>
       <c r="C83" t="n">
-        <v>213</v>
+        <v>117</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>548</v>
+        <v>576</v>
       </c>
       <c r="C84" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>506</v>
+        <v>477</v>
       </c>
       <c r="C85" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="86">
@@ -6187,10 +6143,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="87">
@@ -6209,79 +6165,79 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C88" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="C89" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>170</v>
+        <v>218</v>
       </c>
       <c r="C90" t="n">
-        <v>16</v>
+        <v>52</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>166</v>
+        <v>191</v>
       </c>
       <c r="C91" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="C92" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>107</v>
+        <v>148</v>
       </c>
       <c r="C93" t="n">
-        <v>107</v>
+        <v>28</v>
       </c>
     </row>
     <row r="94">
@@ -6300,78 +6256,65 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="C95" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="C96" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="C97" t="n">
-        <v>9</v>
+        <v>43</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C98" t="n">
-        <v>45</v>
+        <v>27</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="C99" t="n">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>4303</t>
-        </is>
-      </c>
-      <c r="B100" t="n">
-        <v>8</v>
-      </c>
-      <c r="C100" t="n">
         <v>8</v>
       </c>
     </row>

--- a/data/台股_警戒掃描.xlsx
+++ b/data/台股_警戒掃描.xlsx
@@ -10,7 +10,8 @@
     <sheet name="警戒總覽" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="處置股票" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="暫停交易" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="借券排行" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="暫停融券" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="借券排行" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,20 +544,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🪦 借券爆量</t>
+          <t>📉 暫停融券</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>30d 160132 股, 最新日 7575 股</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
+          <t>除息</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>~ 2026-07-01</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>B</t>
@@ -566,37 +571,33 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>⚠️ 處置</t>
+          <t>🪦 借券爆量</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>連續三次 / 第一次處置</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-05-26 ~ 2026-06-08</t>
-        </is>
-      </c>
+          <t>30d 137569 股, 最新日 249 股</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -613,20 +614,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>🪦 借券爆量</t>
+          <t>⚠️ 處置</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>30d 109069 股, 最新日 1113 股</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
+          <t>連續三次 / 第一次處置</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-05-26 ~ 2026-06-08</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>C</t>
@@ -636,12 +641,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -651,30 +656,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>30d 124308 股, 最新日 244 股</t>
+          <t>30d 135021 股, 最新日 519 股</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -684,30 +689,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>30d 125970 股, 最新日 1600 股</t>
+          <t>30d 90896 股, 最新日 120 股</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -717,67 +722,63 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>30d 111219 股, 最新日 141 股</t>
+          <t>30d 169821 股, 最新日 800 股</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>⚠️ 處置</t>
+          <t>🪦 借券爆量</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>連續三次 / 第一次處置</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-03-03 ~ 2026-03-16</t>
-        </is>
-      </c>
+          <t>30d 112373 股, 最新日 741 股</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -787,17 +788,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>最近十個營業日已有六次 / 第一次處置</t>
+          <t>連續三次 / 第一次處置</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-18 ~ 2026-07-02</t>
+          <t>2026-03-03 ~ 2026-03-16</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -809,12 +810,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -824,170 +825,170 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>30d 61965 股, 最新日 100 股</t>
+          <t>30d 77238 股, 最新日 150 股</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>🪦 借券爆量</t>
+          <t>⚠️ 處置</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>30d 85154 股, 最新日 217 股</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
+          <t>最近十個營業日已有六次 / 第一次處置</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-06-18 ~ 2026-07-02</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>⚠️ 處置</t>
+          <t>🪦 借券爆量</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>連續三次 / 第一次處置</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-05-07 ~ 2026-05-20</t>
-        </is>
-      </c>
+          <t>30d 86387 股, 最新日 500 股</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>⚠️ 處置</t>
+          <t>🪦 借券爆量</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>連續三次 / 第一次處置</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-06-01 ~ 2026-06-12</t>
-        </is>
-      </c>
+          <t>30d 108660 股, 最新日 1886 股</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🪦 借券爆量</t>
+          <t>⚠️ 處置</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>30d 122033 股, 最新日 37269 股</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
+          <t>連續三次 / 第一次處置</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-05-07 ~ 2026-05-20</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>立隆電</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -997,7 +998,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1007,24 +1008,24 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-20 ~ 2026-06-02</t>
+          <t>2026-06-01 ~ 2026-06-12</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1034,12 +1035,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>30d 56880 股, 最新日 3823 股</t>
+          <t>30d 114492 股, 最新日 6289 股</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -1052,49 +1053,49 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>八方雲集</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>⚠️ 處置</t>
+          <t>📉 暫停融券</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>最近10個營業日內有6個營業日 / 聯亞光電工業股份有限公司股票(代號：3081)最近30個營業日內曾發布處置，又因最近10個營業日內有6個營業日經本中心公布注意交易資訊，爰自115年3月12日起10個營業日(115年3月12日至115年3月25日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>除息</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-12 ~ 2026-03-25</t>
+          <t>~ 2026-07-01</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1104,71 +1105,67 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 聯亞光電工業股份有限公司股票(代號：3081)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年02月04日起10個營業日(115年02月04日至115年02月26日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>連續三次 / 第一次處置</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-04 ~ 2026-02-26</t>
+          <t>2026-05-20 ~ 2026-06-02</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>⚠️ 處置</t>
+          <t>🪦 借券爆量</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 聯亞光電工業股份有限公司股票(代號：3081)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年01月30日起10個營業日(115年01月30日至115年02月23日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-01-30 ~ 2026-02-23</t>
-        </is>
-      </c>
+          <t>30d 60299 股, 最新日 6 股</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1178,17 +1175,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 大綜電腦系統股份有限公司股票(代號：3147)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年7月6日起10個營業日(115年7月6日至115年7月17日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>最近10個營業日內有6個營業日 / 聯亞光電工業股份有限公司股票(代號：3081)最近30個營業日內曾發布處置，又因最近10個營業日內有6個營業日經本中心公布注意交易資訊，爰自115年3月12日起10個營業日(115年3月12日至115年3月25日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-06 ~ 2026-07-17</t>
+          <t>2026-03-12 ~ 2026-03-25</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1200,12 +1197,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1215,17 +1212,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 大綜電腦系統股份有限公司股票(代號：3147)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年6月11日起10個營業日(115年6月11日至115年6月25日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 聯亞光電工業股份有限公司股票(代號：3081)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年02月04日起10個營業日(115年02月04日至115年02月26日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-11 ~ 2026-06-25</t>
+          <t>2026-02-04 ~ 2026-02-26</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1237,12 +1234,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1252,17 +1249,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 大綜電腦系統股份有限公司股票(代號：3147)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年6月8日起10個營業日(115年6月8日至115年6月22日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 聯亞光電工業股份有限公司股票(代號：3081)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年01月30日起10個營業日(115年01月30日至115年02月23日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-08 ~ 2026-06-22</t>
+          <t>2026-01-30 ~ 2026-02-23</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1274,45 +1271,49 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>🪦 借券爆量</t>
+          <t>⚠️ 處置</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>30d 128958 股, 最新日 415 股</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 大綜電腦系統股份有限公司股票(代號：3147)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年7月6日起10個營業日(115年7月6日至115年7月17日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-07-06 ~ 2026-07-17</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1322,17 +1323,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 威剛科技股份有限公司股票(代號：3260)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年3月19日起10個營業日(115年3月19日至115年4月1日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 大綜電腦系統股份有限公司股票(代號：3147)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年6月11日起10個營業日(115年6月11日至115年6月25日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-19 ~ 2026-04-01</t>
+          <t>2026-06-11 ~ 2026-06-25</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1344,12 +1345,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1359,56 +1360,52 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>連續三次 / 第一次處置</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 大綜電腦系統股份有限公司股票(代號：3147)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年6月8日起10個營業日(115年6月8日至115年6月22日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-17 ~ 2026-04-30</t>
+          <t>2026-06-08 ~ 2026-06-22</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>⚠️ 處置</t>
+          <t>🪦 借券爆量</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>最近十個營業日已有六次 / 第一次處置</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-06-30 ~ 2026-07-13</t>
-        </is>
-      </c>
+          <t>30d 158635 股, 最新日 240 股</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>C</t>
@@ -1418,12 +1415,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1433,34 +1430,34 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>連續三次 / 第一次處置</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 威剛科技股份有限公司股票(代號：3260)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年3月19日起10個營業日(115年3月19日至115年4月1日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-13 ~ 2026-05-26</t>
+          <t>2026-03-19 ~ 2026-04-01</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1470,7 +1467,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1480,24 +1477,24 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-14 ~ 2026-04-27</t>
+          <t>2026-04-17 ~ 2026-04-30</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1507,34 +1504,34 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>連續三次 / 第二次處置</t>
+          <t>最近十個營業日已有六次 / 第一次處置</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-13 ~ 2026-05-26</t>
+          <t>2026-06-30 ~ 2026-07-13</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1544,7 +1541,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1554,90 +1551,98 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-24 ~ 2026-05-08</t>
+          <t>2026-05-13 ~ 2026-05-26</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>🪦 借券爆量</t>
+          <t>⚠️ 處置</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>30d 52498 股, 最新日 282 股</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
+          <t>連續三次 / 第一次處置</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-04-14 ~ 2026-04-27</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>🚫 暫停</t>
+          <t>⚠️ 處置</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>暫停8:00, 恢復2026-04-29</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
+          <t>連續三次 / 第二次處置</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-05-13 ~ 2026-05-26</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1647,7 +1652,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1657,24 +1662,24 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-16 ~ 2026-04-29</t>
+          <t>2026-04-24 ~ 2026-05-08</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1684,12 +1689,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>30d 81768 股, 最新日 790 股</t>
+          <t>30d 55364 股, 最新日 145 股</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
@@ -1702,34 +1707,30 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>信立</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>⚠️ 處置</t>
+          <t>🚫 暫停</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>連續5個營業日 / 華星光通科技股份有限公司股票(代號：4979)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年6月3日起10個營業日(115年6月3日至115年6月16日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-06-03 ~ 2026-06-16</t>
-        </is>
-      </c>
+          <t>暫停8:00, 恢復2026-04-29</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
           <t>B</t>
@@ -1739,12 +1740,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>六方科-KY</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1754,17 +1755,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>連續5個營業日 / 華星光通科技股份有限公司股票(代號：4979)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年5月13日起10個營業日(115年5月13日至115年5月26日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>連續三次 / 第一次處置</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-13 ~ 2026-05-26</t>
+          <t>2026-04-16 ~ 2026-04-29</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1776,34 +1777,30 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>⚠️ 處置</t>
+          <t>🪦 借券爆量</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 華星光通科技股份有限公司股票(代號：4979)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年4月21日起10個營業日(115年4月21日至115年5月5日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-04-21 ~ 2026-05-05</t>
-        </is>
-      </c>
+          <t>30d 62234 股, 最新日 24 股</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
           <t>B</t>
@@ -1828,17 +1825,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>連續5個營業日 / 華星光通科技股份有限公司股票(代號：4979)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年3月27日起10個營業日(115年3月27日至115年4月13日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>連續5個營業日 / 華星光通科技股份有限公司股票(代號：4979)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年6月3日起10個營業日(115年6月3日至115年6月16日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-27 ~ 2026-04-13</t>
+          <t>2026-06-03 ~ 2026-06-16</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1865,17 +1862,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>連續5個營業日 / 華星光通科技股份有限公司股票(代號：4979)因連續5個營業日經本中心公布注意交易資訊，爰自115年3月3日起10個營業日(115年3月3日至115年3月16日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>連續5個營業日 / 華星光通科技股份有限公司股票(代號：4979)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年5月13日起10個營業日(115年5月13日至115年5月26日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-03 ~ 2026-03-16</t>
+          <t>2026-05-13 ~ 2026-05-26</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1887,12 +1884,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1902,17 +1899,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>連續三次 / 第一次處置</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 華星光通科技股份有限公司股票(代號：4979)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年4月21日起10個營業日(115年4月21日至115年5月5日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-13 ~ 2026-04-24</t>
+          <t>2026-04-21 ~ 2026-05-05</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1924,12 +1921,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1939,34 +1936,34 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>最近10個營業日內有6個營業日 / 建榮工業材料股份有限公司股票(代號：5340)最近30個營業日內曾發布處置，又因最近10個營業日內有6個營業日經本中心公布注意交易資訊，爰自115年4月21日起10個營業日(115年4月21日至115年5月5日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>連續5個營業日 / 華星光通科技股份有限公司股票(代號：4979)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年3月27日起10個營業日(115年3月27日至115年4月13日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-21 ~ 2026-05-05</t>
+          <t>2026-03-27 ~ 2026-04-13</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1976,34 +1973,34 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>連續5個營業日 / 建榮工業材料股份有限公司股票(代號：5340)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年3月17日起10個營業日(115年3月17日至115年3月30日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>連續5個營業日 / 華星光通科技股份有限公司股票(代號：4979)因連續5個營業日經本中心公布注意交易資訊，爰自115年3月3日起10個營業日(115年3月3日至115年3月16日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-17 ~ 2026-03-30</t>
+          <t>2026-03-03 ~ 2026-03-16</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2013,22 +2010,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>連續5個營業日 / 建榮工業材料股份有限公司股票(代號：5340)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年2月23日起10個營業日(115年2月23日至115年3月9日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>連續三次 / 第一次處置</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-02-23 ~ 2026-03-09</t>
+          <t>2026-04-13 ~ 2026-04-24</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -2050,17 +2047,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>連續5個營業日 / 建榮工業材料股份有限公司股票(代號：5340)因連續5個營業日經本中心公布注意交易資訊，爰自115年01月22日起10個營業日(115年01月22日至115年02月04日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>最近10個營業日內有6個營業日 / 建榮工業材料股份有限公司股票(代號：5340)最近30個營業日內曾發布處置，又因最近10個營業日內有6個營業日經本中心公布注意交易資訊，爰自115年4月21日起10個營業日(115年4月21日至115年5月5日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-01-22 ~ 2026-02-04</t>
+          <t>2026-04-21 ~ 2026-05-05</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2072,12 +2069,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>建榮</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2087,17 +2084,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>最近10個營業日內有6個營業日 / 萬潤科技股份有限公司股票(代號：6187)因最近10個營業日內有6個營業日經本中心公布注意交易資訊，爰自115年6月17日起10個營業日(115年6月17日至115年7月1日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>連續5個營業日 / 建榮工業材料股份有限公司股票(代號：5340)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年3月17日起10個營業日(115年3月17日至115年3月30日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-17 ~ 2026-07-01</t>
+          <t>2026-03-17 ~ 2026-03-30</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2109,12 +2106,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>建榮</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2124,17 +2121,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 萬潤科技股份有限公司股票(代號：6187)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年3月30日起10個營業日(115年3月30日至115年4月14日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>連續5個營業日 / 建榮工業材料股份有限公司股票(代號：5340)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年2月23日起10個營業日(115年2月23日至115年3月9日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-30 ~ 2026-04-14</t>
+          <t>2026-02-23 ~ 2026-03-09</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2161,17 +2158,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 萬潤科技股份有限公司股票(代號：6187)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年3月6日起10個營業日(115年3月6日至115年3月19日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>最近10個營業日內有6個營業日 / 萬潤科技股份有限公司股票(代號：6187)因最近10個營業日內有6個營業日經本中心公布注意交易資訊，爰自115年6月17日起10個營業日(115年6月17日至115年7月1日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-06 ~ 2026-03-19</t>
+          <t>2026-06-17 ~ 2026-07-01</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2198,17 +2195,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 萬潤科技股份有限公司股票(代號：6187)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年3月3日起10個營業日(115年3月3日至115年3月16日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 萬潤科技股份有限公司股票(代號：6187)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年3月30日起10個營業日(115年3月30日至115年4月14日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-03 ~ 2026-03-16</t>
+          <t>2026-03-30 ~ 2026-04-14</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2220,12 +2217,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2235,34 +2232,34 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 普萊德科技股份有限公司股票(代號：6263)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年5月15日起10個營業日(115年5月15日至115年5月28日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 萬潤科技股份有限公司股票(代號：6187)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年3月6日起10個營業日(115年3月6日至115年3月19日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-15 ~ 2026-05-28</t>
+          <t>2026-03-06 ~ 2026-03-19</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2272,71 +2269,71 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 台燿科技股份有限公司股票(代號：6274)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年5月11日起10個營業日(115年5月11日至115年5月22日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 萬潤科技股份有限公司股票(代號：6187)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年3月3日起10個營業日(115年3月3日至115年3月16日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-11 ~ 2026-05-22</t>
+          <t>2026-03-03 ~ 2026-03-16</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>⚠️ 處置</t>
+          <t>📉 暫停融券</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 台燿科技股份有限公司股票(代號：6274)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年4月17日起10個營業日(115年4月17日至115年4月30日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>除息</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-17 ~ 2026-04-30</t>
+          <t>~ 2026-07-01</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2346,34 +2343,34 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>最近十個營業日已有六次 / 第一次處置</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 普萊德科技股份有限公司股票(代號：6263)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年5月15日起10個營業日(115年5月15日至115年5月28日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-08 ~ 2026-06-22</t>
+          <t>2026-05-15 ~ 2026-05-28</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2383,34 +2380,34 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>最近十個營業日已有六次 / 第一次處置</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 台燿科技股份有限公司股票(代號：6274)最近30個營業日內曾發布處置，又因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年5月11日起10個營業日(115年5月11日至115年5月22日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-22 ~ 2026-05-06</t>
+          <t>2026-05-11 ~ 2026-05-22</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2420,22 +2417,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>連續五次 / 第二次處置</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 台燿科技股份有限公司股票(代號：6274)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年4月17日起10個營業日(115年4月17日至115年4月30日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-09 ~ 2026-03-20</t>
+          <t>2026-04-17 ~ 2026-04-30</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -2457,7 +2454,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2467,7 +2464,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-04 ~ 2026-02-26</t>
+          <t>2026-06-08 ~ 2026-06-22</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2479,12 +2476,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2494,34 +2491,34 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>連續三次 / 第一次處置</t>
+          <t>最近十個營業日已有六次 / 第一次處置</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-03 ~ 2026-02-25</t>
+          <t>2026-04-22 ~ 2026-05-06</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2531,17 +2528,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>最近十個營業日已有六次 / 第一次處置</t>
+          <t>連續五次 / 第二次處置</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-26 ~ 2026-04-10</t>
+          <t>2026-03-09 ~ 2026-03-20</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2553,12 +2550,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2568,34 +2565,34 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 竹陞科技股份有限公司股票(代號：6739)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年02月03日起10個營業日(115年02月03日至115年02月25日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>最近十個營業日已有六次 / 第一次處置</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-03 ~ 2026-02-25</t>
+          <t>2026-02-04 ~ 2026-02-26</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2605,17 +2602,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>連續三次 / 第二次處置</t>
+          <t>連續三次 / 第一次處置</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-24 ~ 2026-05-08</t>
+          <t>2026-02-03 ~ 2026-02-25</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2627,12 +2624,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2642,34 +2639,34 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>連續三次 / 第二次處置</t>
+          <t>最近十個營業日已有六次 / 第一次處置</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-20 ~ 2026-04-02</t>
+          <t>2026-03-26 ~ 2026-04-10</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2679,17 +2676,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>連續三次 / 第一次處置</t>
+          <t>因連續3個營業日達本中心作業要點第四條第一項第一款 / 竹陞科技股份有限公司股票(代號：6739)因連續3個營業日達本中心作業要點第四條第一項第一款經本中心公布注意交易資訊，爰自115年02月03日起10個營業日(115年02月03日至115年02月25日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-17 ~ 2026-03-30</t>
+          <t>2026-02-03 ~ 2026-02-25</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2701,12 +2698,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2716,34 +2713,34 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>連續三次 / 第一次處置</t>
+          <t>連續三次 / 第二次處置</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-24 ~ 2026-07-07</t>
+          <t>2026-04-24 ~ 2026-05-08</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2753,57 +2750,205 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>最近十個營業日已有六次 / 第一次處置</t>
+          <t>連續三次 / 第二次處置</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-15 ~ 2026-04-28</t>
+          <t>2026-03-20 ~ 2026-04-02</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>8271</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>宇瞻</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>⚠️ 處置</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>連續三次 / 第一次處置</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-03-17 ~ 2026-03-30</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>8926</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>台汽電</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>📉 暫停融券</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>除息</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>~ 2026-07-01</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
           <t>8996</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>高力</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>⚠️ 處置</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>連續三次 / 第一次處置</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-06-24 ~ 2026-07-07</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>8996</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>⚠️ 處置</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>最近十個營業日已有六次 / 第一次處置</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-04-15 ~ 2026-04-28</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>8996</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>高力</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>⚠️ 處置</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
         <is>
           <t>2026-02-24</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>最近十個營業日已有六次 / 第二次處置</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>2026-02-25 ~ 2026-03-11</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -2820,7 +2965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4548,87 +4693,87 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>連續5個營業日</t>
+          <t>連續三次</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>建榮工業材料股份有限公司股票(代號：5340)因連續5個營業日經本中心公布注意交易資訊，爰自115年01月22日起10個營業日(115年01月22日至115年02月04日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每5分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券數量單筆達10交易單位或多筆累積達30交易單位以上時，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>第一次處置</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-25</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>建榮</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>連續三次</t>
+          <t>連續5個營業日</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>第一次處置</t>
+          <t>建榮工業材料股份有限公司股票(代號：5340)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年2月23日起10個營業日(115年2月23日至115年3月9日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4642,7 +4787,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -4651,24 +4796,24 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>建榮工業材料股份有限公司股票(代號：5340)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年2月23日起10個營業日(115年2月23日至115年3月9日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>建榮工業材料股份有限公司股票(代號：5340)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年3月17日起10個營業日(115年3月17日至115年3月30日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-30</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4682,83 +4827,83 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>連續5個營業日</t>
+          <t>最近10個營業日內有6個營業日</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>建榮工業材料股份有限公司股票(代號：5340)最近30個營業日內曾發布處置，又因連續5個營業日經本中心公布注意交易資訊，爰自115年3月17日起10個營業日(115年3月17日至115年3月30日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>建榮工業材料股份有限公司股票(代號：5340)最近30個營業日內曾發布處置，又因最近10個營業日內有6個營業日經本中心公布注意交易資訊，爰自115年4月21日起10個營業日(115年4月21日至115年5月5日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-05-05</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>最近10個營業日內有6個營業日</t>
+          <t>連續三次</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>建榮工業材料股份有限公司股票(代號：5340)最近30個營業日內曾發布處置，又因最近10個營業日內有6個營業日經本中心公布注意交易資訊，爰自115年4月21日起10個營業日(115年4月21日至115年5月5日，如遇休市、有價證券停止買賣、全日暫停交易則順延執行)改以人工管制之撮合終端機執行撮合作業(約每20分鐘撮合一次)，各證券商於投資人每日委託買賣該有價證券，應就其當日已委託之買賣，向該投資人收取全部之買進價金或賣出證券。信用交易部分，則收足融資自備款或融券保證金。但信用交易了結及違約專戶委託買賣該有價證券時，不在此限。</t>
+          <t>第一次處置</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-08</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -4776,29 +4921,29 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -4816,12 +4961,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
@@ -4833,12 +4978,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -4851,7 +4996,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>第一次處置</t>
+          <t>第二次處置</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -4868,17 +5013,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -4886,60 +5031,20 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>連續三次</t>
+          <t>最近十個營業日已有六次</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>第二次處置</t>
+          <t>第一次處置</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2383</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>台光電</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>1</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>最近十個營業日已有六次</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>第一次處置</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
@@ -5024,23 +5129,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C99"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>代號</t>
+          <t>stock_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>30d 借券量</t>
+          <t>date</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>最新日借券</t>
+          <t>end_date</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>reason</t>
         </is>
       </c>
     </row>
@@ -5050,50 +5160,169 @@
           <t>2317</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>160132</v>
-      </c>
-      <c r="C2" t="n">
-        <v>7575</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>除息</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3231</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>128958</v>
-      </c>
-      <c r="C3" t="n">
-        <v>415</v>
+          <t>2753</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>除息</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2344</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>125970</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1600</v>
+          <t>6197</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>除息</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>8926</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>除息</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C102"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>代號</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>30d 借券量</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>最新日借券</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>169821</v>
+      </c>
+      <c r="C2" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>158635</v>
+      </c>
+      <c r="C3" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2317</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>137569</v>
+      </c>
+      <c r="C4" t="n">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2327</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>124308</v>
+        <v>135021</v>
       </c>
       <c r="C5" t="n">
-        <v>244</v>
+        <v>519</v>
       </c>
     </row>
     <row r="6">
@@ -5103,10 +5332,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>122033</v>
+        <v>114492</v>
       </c>
       <c r="C6" t="n">
-        <v>37269</v>
+        <v>6289</v>
       </c>
     </row>
     <row r="7">
@@ -5116,114 +5345,114 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>111219</v>
+        <v>112373</v>
       </c>
       <c r="C7" t="n">
-        <v>141</v>
+        <v>741</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>109069</v>
+        <v>108660</v>
       </c>
       <c r="C8" t="n">
-        <v>1113</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>85154</v>
+        <v>90896</v>
       </c>
       <c r="C9" t="n">
-        <v>217</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>81768</v>
+        <v>86387</v>
       </c>
       <c r="C10" t="n">
-        <v>790</v>
+        <v>500</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>61965</v>
+        <v>77238</v>
       </c>
       <c r="C11" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>56880</v>
+        <v>62234</v>
       </c>
       <c r="C12" t="n">
-        <v>3823</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>52498</v>
+        <v>60299</v>
       </c>
       <c r="C13" t="n">
-        <v>282</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>48578</v>
+        <v>55364</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>43747</v>
+        <v>38495</v>
       </c>
       <c r="C15" t="n">
-        <v>300</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="16">
@@ -5233,36 +5462,36 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>30813</v>
+        <v>33460</v>
       </c>
       <c r="C16" t="n">
-        <v>163</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>28544</v>
+        <v>28900</v>
       </c>
       <c r="C17" t="n">
-        <v>22</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>22444</v>
+        <v>28100</v>
       </c>
       <c r="C18" t="n">
-        <v>61</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19">
@@ -5272,10 +5501,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>19214</v>
+        <v>22117</v>
       </c>
       <c r="C19" t="n">
-        <v>69</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20">
@@ -5285,10 +5514,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16863</v>
+        <v>21071</v>
       </c>
       <c r="C20" t="n">
-        <v>372</v>
+        <v>527</v>
       </c>
     </row>
     <row r="21">
@@ -5298,62 +5527,62 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15491</v>
+        <v>14996</v>
       </c>
       <c r="C21" t="n">
-        <v>67</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>14896</v>
+        <v>14471</v>
       </c>
       <c r="C22" t="n">
-        <v>881</v>
+        <v>115</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>14072</v>
+        <v>12570</v>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>300</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>12080</v>
+        <v>12505</v>
       </c>
       <c r="C24" t="n">
-        <v>242</v>
+        <v>660</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>11896</v>
+        <v>10982</v>
       </c>
       <c r="C25" t="n">
-        <v>273</v>
+        <v>488</v>
       </c>
     </row>
     <row r="26">
@@ -5363,62 +5592,62 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>9199</v>
+        <v>9580</v>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>207</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>8676</v>
+        <v>9225</v>
       </c>
       <c r="C27" t="n">
-        <v>50</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>7929</v>
+        <v>8763</v>
       </c>
       <c r="C28" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>7890</v>
+        <v>8504</v>
       </c>
       <c r="C29" t="n">
-        <v>109</v>
+        <v>455</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>7051</v>
+        <v>8121</v>
       </c>
       <c r="C30" t="n">
-        <v>578</v>
+        <v>600</v>
       </c>
     </row>
     <row r="31">
@@ -5428,49 +5657,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>6856</v>
+        <v>7421</v>
       </c>
       <c r="C31" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>6487</v>
+        <v>7235</v>
       </c>
       <c r="C32" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>6186</v>
+        <v>7100</v>
       </c>
       <c r="C33" t="n">
-        <v>200</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>6013</v>
+        <v>6886</v>
       </c>
       <c r="C34" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35">
@@ -5480,10 +5709,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>5760</v>
+        <v>6573</v>
       </c>
       <c r="C35" t="n">
-        <v>4</v>
+        <v>96</v>
       </c>
     </row>
     <row r="36">
@@ -5493,150 +5722,150 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>5583</v>
+        <v>6553</v>
       </c>
       <c r="C36" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>5419</v>
+        <v>6515</v>
       </c>
       <c r="C37" t="n">
-        <v>92</v>
+        <v>42</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>5117</v>
+        <v>6324</v>
       </c>
       <c r="C38" t="n">
-        <v>17</v>
+        <v>169</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4528</v>
+        <v>5126</v>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>62</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4517</v>
+        <v>4693</v>
       </c>
       <c r="C40" t="n">
-        <v>371</v>
+        <v>77</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4433</v>
+        <v>4326</v>
       </c>
       <c r="C41" t="n">
-        <v>26</v>
+        <v>716</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3944</v>
+        <v>4228</v>
       </c>
       <c r="C42" t="n">
-        <v>149</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3799</v>
+        <v>4124</v>
       </c>
       <c r="C43" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3647</v>
+        <v>4052</v>
       </c>
       <c r="C44" t="n">
-        <v>20</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3632</v>
+        <v>3783</v>
       </c>
       <c r="C45" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3423</v>
+        <v>3696</v>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3367</v>
+        <v>3619</v>
       </c>
       <c r="C47" t="n">
         <v>5</v>
@@ -5645,131 +5874,131 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3302</v>
+        <v>3491</v>
       </c>
       <c r="C48" t="n">
-        <v>37</v>
+        <v>95</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3020</v>
+        <v>3189</v>
       </c>
       <c r="C49" t="n">
-        <v>186</v>
+        <v>76</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2868</v>
+        <v>3173</v>
       </c>
       <c r="C50" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2813</v>
+        <v>3134</v>
       </c>
       <c r="C51" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2689</v>
+        <v>3064</v>
       </c>
       <c r="C52" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2596</v>
+        <v>3062</v>
       </c>
       <c r="C53" t="n">
-        <v>35</v>
+        <v>187</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2580</v>
+        <v>2950</v>
       </c>
       <c r="C54" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2569</v>
+        <v>2819</v>
       </c>
       <c r="C55" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2568</v>
+        <v>2760</v>
       </c>
       <c r="C56" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2560</v>
+        <v>2650</v>
       </c>
       <c r="C57" t="n">
-        <v>776</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58">
@@ -5779,205 +6008,205 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2537</v>
+        <v>2603</v>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>58</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2366</v>
+        <v>2558</v>
       </c>
       <c r="C59" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2040</v>
+        <v>2461</v>
       </c>
       <c r="C60" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2020</v>
+        <v>2192</v>
       </c>
       <c r="C61" t="n">
-        <v>18</v>
+        <v>81</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2002</v>
+        <v>1850</v>
       </c>
       <c r="C62" t="n">
-        <v>58</v>
+        <v>30</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1862</v>
+        <v>1821</v>
       </c>
       <c r="C63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1838</v>
+        <v>1762</v>
       </c>
       <c r="C64" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1804</v>
+        <v>1761</v>
       </c>
       <c r="C65" t="n">
-        <v>10</v>
+        <v>46</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1591</v>
+        <v>1729</v>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1560</v>
+        <v>1682</v>
       </c>
       <c r="C67" t="n">
-        <v>3</v>
+        <v>182</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1550</v>
+        <v>1501</v>
       </c>
       <c r="C68" t="n">
-        <v>110</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1500</v>
+        <v>1478</v>
       </c>
       <c r="C69" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1366</v>
+        <v>1455</v>
       </c>
       <c r="C70" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1284</v>
+        <v>1450</v>
       </c>
       <c r="C71" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1178</v>
+        <v>1392</v>
       </c>
       <c r="C72" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1174</v>
+        <v>1383</v>
       </c>
       <c r="C73" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74">
@@ -5987,192 +6216,192 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1158</v>
+        <v>1377</v>
       </c>
       <c r="C74" t="n">
-        <v>39</v>
+        <v>65</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1150</v>
+        <v>1355</v>
       </c>
       <c r="C75" t="n">
-        <v>113</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1075</v>
+        <v>1345</v>
       </c>
       <c r="C76" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>947</v>
+        <v>1164</v>
       </c>
       <c r="C77" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>827</v>
+        <v>1092</v>
       </c>
       <c r="C78" t="n">
-        <v>217</v>
+        <v>17</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>819</v>
+        <v>1017</v>
       </c>
       <c r="C79" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>806</v>
+        <v>1005</v>
       </c>
       <c r="C80" t="n">
-        <v>11</v>
+        <v>973</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>755</v>
+        <v>846</v>
       </c>
       <c r="C81" t="n">
-        <v>2</v>
+        <v>118</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>738</v>
+        <v>827</v>
       </c>
       <c r="C82" t="n">
-        <v>54</v>
+        <v>217</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>592</v>
+        <v>825</v>
       </c>
       <c r="C83" t="n">
-        <v>117</v>
+        <v>24</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>576</v>
+        <v>703</v>
       </c>
       <c r="C84" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>477</v>
+        <v>605</v>
       </c>
       <c r="C85" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>457</v>
+        <v>493</v>
       </c>
       <c r="C86" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>297</v>
+        <v>491</v>
       </c>
       <c r="C87" t="n">
-        <v>250</v>
+        <v>46</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>263</v>
+        <v>441</v>
       </c>
       <c r="C88" t="n">
-        <v>18</v>
+        <v>80</v>
       </c>
     </row>
     <row r="89">
@@ -6182,114 +6411,114 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>235</v>
+        <v>371</v>
       </c>
       <c r="C89" t="n">
-        <v>10</v>
+        <v>161</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>218</v>
+        <v>337</v>
       </c>
       <c r="C90" t="n">
-        <v>52</v>
+        <v>138</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>191</v>
+        <v>298</v>
       </c>
       <c r="C91" t="n">
-        <v>41</v>
+        <v>13</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>161</v>
+        <v>276</v>
       </c>
       <c r="C92" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>148</v>
+        <v>266</v>
       </c>
       <c r="C93" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>94</v>
+        <v>229</v>
       </c>
       <c r="C94" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>75</v>
+        <v>219</v>
       </c>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>52</v>
+        <v>153</v>
       </c>
       <c r="C96" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="C97" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="98">
@@ -6299,23 +6528,62 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>37</v>
+        <v>85</v>
       </c>
       <c r="C98" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="C99" t="n">
-        <v>8</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>5225</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>43</v>
+      </c>
+      <c r="C100" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>6690</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>21</v>
+      </c>
+      <c r="C101" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>3188</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>2</v>
+      </c>
+      <c r="C102" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data/台股_警戒掃描.xlsx
+++ b/data/台股_警戒掃描.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,12 +472,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>30d 167568 股, 最新日 472 股</t>
+          <t>30d 150096 股, 最新日 111 股</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -505,12 +505,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>30d 150393 股, 最新日 422 股</t>
+          <t>30d 136047 股, 最新日 250 股</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -538,12 +538,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>30d 67376 股, 最新日 192 股</t>
+          <t>30d 57065 股, 最新日 72 股</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -571,12 +571,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>30d 182086 股, 最新日 20 股</t>
+          <t>30d 174862 股, 最新日 95 股</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -604,12 +604,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>30d 120414 股, 最新日 994 股</t>
+          <t>30d 101982 股, 最新日 392 股</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -637,12 +637,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>30d 116913 股, 最新日 5 股</t>
+          <t>30d 116565 股, 最新日 200 股</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -670,12 +670,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>30d 98417 股, 最新日 126 股</t>
+          <t>30d 108509 股, 最新日 806 股</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -703,12 +703,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>30d 112151 股, 最新日 297 股</t>
+          <t>30d 101276 股, 最新日 52 股</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -736,12 +736,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>30d 152323 股, 最新日 1426 股</t>
+          <t>30d 147451 股, 最新日 343 股</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -769,12 +769,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>30d 69524 股, 最新日 361 股</t>
+          <t>30d 58354 股, 最新日 2088 股</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -802,12 +802,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>30d 230490 股, 最新日 2 股</t>
+          <t>30d 228706 股, 最新日 663 股</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -835,49 +835,16 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>30d 74401 股, 最新日 410 股</t>
+          <t>30d 62780 股, 最新日 12 股</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>4904</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>遠傳</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>🪦 借券爆量</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>30d 55615 股, 最新日 368 股</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -894,7 +861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C103"/>
+  <dimension ref="A1:C102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -921,10 +888,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>230490</v>
+        <v>228706</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>663</v>
       </c>
     </row>
     <row r="3">
@@ -934,10 +901,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>182086</v>
+        <v>174862</v>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4">
@@ -947,10 +914,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>167568</v>
+        <v>150096</v>
       </c>
       <c r="C4" t="n">
-        <v>472</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5">
@@ -960,10 +927,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>152323</v>
+        <v>147451</v>
       </c>
       <c r="C5" t="n">
-        <v>1426</v>
+        <v>343</v>
       </c>
     </row>
     <row r="6">
@@ -973,62 +940,62 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>150393</v>
+        <v>136047</v>
       </c>
       <c r="C6" t="n">
-        <v>422</v>
+        <v>250</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>120414</v>
+        <v>116565</v>
       </c>
       <c r="C7" t="n">
-        <v>994</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>116913</v>
+        <v>108509</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>806</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>112151</v>
+        <v>101982</v>
       </c>
       <c r="C9" t="n">
-        <v>297</v>
+        <v>392</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>98417</v>
+        <v>101276</v>
       </c>
       <c r="C10" t="n">
-        <v>126</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11">
@@ -1038,10 +1005,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>74401</v>
+        <v>62780</v>
       </c>
       <c r="C11" t="n">
-        <v>410</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -1051,10 +1018,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>69524</v>
+        <v>58354</v>
       </c>
       <c r="C12" t="n">
-        <v>361</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="13">
@@ -1064,23 +1031,23 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>67376</v>
+        <v>57065</v>
       </c>
       <c r="C13" t="n">
-        <v>192</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>55615</v>
+        <v>44065</v>
       </c>
       <c r="C14" t="n">
-        <v>368</v>
+        <v>556</v>
       </c>
     </row>
     <row r="15">
@@ -1090,23 +1057,23 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>44841</v>
+        <v>42415</v>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>40679</v>
+        <v>31316</v>
       </c>
       <c r="C16" t="n">
-        <v>64</v>
+        <v>450</v>
       </c>
     </row>
     <row r="17">
@@ -1116,10 +1083,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>35062</v>
+        <v>29232</v>
       </c>
       <c r="C17" t="n">
-        <v>87</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
@@ -1129,10 +1096,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>22128</v>
+        <v>20984</v>
       </c>
       <c r="C18" t="n">
-        <v>1007</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19">
@@ -1142,62 +1109,62 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18591</v>
+        <v>20199</v>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>116</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17130</v>
+        <v>19005</v>
       </c>
       <c r="C20" t="n">
-        <v>46</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14512</v>
+        <v>16461</v>
       </c>
       <c r="C21" t="n">
-        <v>14</v>
+        <v>322</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>14406</v>
+        <v>15642</v>
       </c>
       <c r="C22" t="n">
-        <v>56</v>
+        <v>638</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>14252</v>
+        <v>11335</v>
       </c>
       <c r="C23" t="n">
-        <v>144</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24">
@@ -1207,23 +1174,23 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>12570</v>
+        <v>10499</v>
       </c>
       <c r="C24" t="n">
-        <v>202</v>
+        <v>291</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>11677</v>
+        <v>10114</v>
       </c>
       <c r="C25" t="n">
-        <v>155</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1233,36 +1200,36 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>11653</v>
+        <v>10014</v>
       </c>
       <c r="C26" t="n">
-        <v>47</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10895</v>
+        <v>9422</v>
       </c>
       <c r="C27" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>8614</v>
+        <v>8265</v>
       </c>
       <c r="C28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29">
@@ -1272,88 +1239,88 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>8304</v>
+        <v>8148</v>
       </c>
       <c r="C29" t="n">
-        <v>42</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>7851</v>
+        <v>8048</v>
       </c>
       <c r="C30" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>7627</v>
+        <v>7943</v>
       </c>
       <c r="C31" t="n">
-        <v>40</v>
+        <v>409</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>7462</v>
+        <v>7098</v>
       </c>
       <c r="C32" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7169</v>
+        <v>6581</v>
       </c>
       <c r="C33" t="n">
-        <v>71</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>6669</v>
+        <v>6490</v>
       </c>
       <c r="C34" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>5985</v>
+        <v>6327</v>
       </c>
       <c r="C35" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
@@ -1363,166 +1330,166 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>5917</v>
+        <v>6053</v>
       </c>
       <c r="C36" t="n">
-        <v>53</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>5806</v>
+        <v>5606</v>
       </c>
       <c r="C37" t="n">
-        <v>682</v>
+        <v>54</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>5790</v>
+        <v>5517</v>
       </c>
       <c r="C38" t="n">
-        <v>224</v>
+        <v>319</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>5389</v>
+        <v>5395</v>
       </c>
       <c r="C39" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4712</v>
+        <v>5178</v>
       </c>
       <c r="C40" t="n">
-        <v>171</v>
+        <v>44</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4629</v>
+        <v>5106</v>
       </c>
       <c r="C41" t="n">
-        <v>64</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4343</v>
+        <v>4383</v>
       </c>
       <c r="C42" t="n">
-        <v>68</v>
+        <v>33</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4296</v>
+        <v>4136</v>
       </c>
       <c r="C43" t="n">
-        <v>440</v>
+        <v>62</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4114</v>
+        <v>4120</v>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>280</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4104</v>
+        <v>3943</v>
       </c>
       <c r="C45" t="n">
-        <v>12</v>
+        <v>126</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3925</v>
+        <v>3787</v>
       </c>
       <c r="C46" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3675</v>
+        <v>3722</v>
       </c>
       <c r="C47" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3589</v>
+        <v>3709</v>
       </c>
       <c r="C48" t="n">
-        <v>22</v>
+        <v>553</v>
       </c>
     </row>
     <row r="49">
@@ -1532,7 +1499,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3473</v>
+        <v>3636</v>
       </c>
       <c r="C49" t="n">
         <v>5</v>
@@ -1541,92 +1508,92 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3436</v>
+        <v>3557</v>
       </c>
       <c r="C50" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3426</v>
+        <v>3501</v>
       </c>
       <c r="C51" t="n">
-        <v>332</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3345</v>
+        <v>3284</v>
       </c>
       <c r="C52" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3262</v>
+        <v>3243</v>
       </c>
       <c r="C53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3116</v>
+        <v>3173</v>
       </c>
       <c r="C54" t="n">
-        <v>395</v>
+        <v>12</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2688</v>
+        <v>2752</v>
       </c>
       <c r="C55" t="n">
-        <v>21</v>
+        <v>395</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2683</v>
+        <v>2717</v>
       </c>
       <c r="C56" t="n">
-        <v>359</v>
+        <v>164</v>
       </c>
     </row>
     <row r="57">
@@ -1636,75 +1603,75 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2628</v>
+        <v>2709</v>
       </c>
       <c r="C57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2397</v>
+        <v>2657</v>
       </c>
       <c r="C58" t="n">
-        <v>298</v>
+        <v>30</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2380</v>
+        <v>2647</v>
       </c>
       <c r="C59" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2288</v>
+        <v>2563</v>
       </c>
       <c r="C60" t="n">
-        <v>13</v>
+        <v>99</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2246</v>
+        <v>2396</v>
       </c>
       <c r="C61" t="n">
-        <v>101</v>
+        <v>243</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2235</v>
+        <v>2371</v>
       </c>
       <c r="C62" t="n">
-        <v>194</v>
+        <v>11</v>
       </c>
     </row>
     <row r="63">
@@ -1714,88 +1681,88 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2228</v>
+        <v>2256</v>
       </c>
       <c r="C63" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2185</v>
+        <v>2209</v>
       </c>
       <c r="C64" t="n">
-        <v>16</v>
+        <v>104</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2118</v>
+        <v>2149</v>
       </c>
       <c r="C65" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2032</v>
+        <v>1903</v>
       </c>
       <c r="C66" t="n">
-        <v>56</v>
+        <v>12</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2009</v>
+        <v>1797</v>
       </c>
       <c r="C67" t="n">
-        <v>386</v>
+        <v>9</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1939</v>
+        <v>1768</v>
       </c>
       <c r="C68" t="n">
-        <v>5</v>
+        <v>950</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1836</v>
+        <v>1636</v>
       </c>
       <c r="C69" t="n">
-        <v>97</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -1805,7 +1772,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1643</v>
+        <v>1634</v>
       </c>
       <c r="C70" t="n">
         <v>648</v>
@@ -1814,14 +1781,14 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1517</v>
+        <v>1483</v>
       </c>
       <c r="C71" t="n">
-        <v>549</v>
+        <v>174</v>
       </c>
     </row>
     <row r="72">
@@ -1831,85 +1798,85 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1449</v>
+        <v>1303</v>
       </c>
       <c r="C72" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1414</v>
+        <v>1203</v>
       </c>
       <c r="C73" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1357</v>
+        <v>1118</v>
       </c>
       <c r="C74" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1327</v>
+        <v>1057</v>
       </c>
       <c r="C75" t="n">
-        <v>83</v>
+        <v>14</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1282</v>
+        <v>1023</v>
       </c>
       <c r="C76" t="n">
-        <v>9</v>
+        <v>549</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1164</v>
+        <v>1007</v>
       </c>
       <c r="C77" t="n">
-        <v>14</v>
+        <v>54</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1126</v>
+        <v>1002</v>
       </c>
       <c r="C78" t="n">
         <v>6</v>
@@ -1918,144 +1885,144 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1109</v>
+        <v>992</v>
       </c>
       <c r="C79" t="n">
-        <v>94</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1078</v>
+        <v>977</v>
       </c>
       <c r="C80" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1069</v>
+        <v>931</v>
       </c>
       <c r="C81" t="n">
-        <v>90</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>975</v>
+        <v>894</v>
       </c>
       <c r="C82" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>934</v>
+        <v>800</v>
       </c>
       <c r="C83" t="n">
-        <v>20</v>
+        <v>94</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>793</v>
+        <v>739</v>
       </c>
       <c r="C84" t="n">
-        <v>141</v>
+        <v>15</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>772</v>
+        <v>557</v>
       </c>
       <c r="C85" t="n">
-        <v>217</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>762</v>
+        <v>502</v>
       </c>
       <c r="C86" t="n">
-        <v>422</v>
+        <v>124</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>589</v>
+        <v>408</v>
       </c>
       <c r="C87" t="n">
-        <v>95</v>
+        <v>27</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>462</v>
+        <v>329</v>
       </c>
       <c r="C88" t="n">
-        <v>5</v>
+        <v>138</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>378</v>
+        <v>319</v>
       </c>
       <c r="C89" t="n">
-        <v>130</v>
+        <v>100</v>
       </c>
     </row>
     <row r="90">
@@ -2065,7 +2032,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>369</v>
+        <v>263</v>
       </c>
       <c r="C90" t="n">
         <v>83</v>
@@ -2074,79 +2041,79 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>337</v>
+        <v>260</v>
       </c>
       <c r="C91" t="n">
-        <v>138</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>319</v>
+        <v>242</v>
       </c>
       <c r="C92" t="n">
-        <v>100</v>
+        <v>11</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>266</v>
+        <v>115</v>
       </c>
       <c r="C93" t="n">
-        <v>88</v>
+        <v>13</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>243</v>
+        <v>78</v>
       </c>
       <c r="C94" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>151</v>
+        <v>59</v>
       </c>
       <c r="C95" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>113</v>
+        <v>50</v>
       </c>
       <c r="C96" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="97">
@@ -2156,7 +2123,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="C97" t="n">
         <v>1</v>
@@ -2169,7 +2136,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="C98" t="n">
         <v>36</v>
@@ -2178,65 +2145,52 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="C99" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="C100" t="n">
-        <v>44</v>
+        <v>21</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="C101" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C102" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>3188</t>
-        </is>
-      </c>
-      <c r="B103" t="n">
-        <v>2</v>
-      </c>
-      <c r="C103" t="n">
         <v>2</v>
       </c>
     </row>

--- a/data/台股_警戒掃描.xlsx
+++ b/data/台股_警戒掃描.xlsx
@@ -472,12 +472,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>30d 150096 股, 最新日 111 股</t>
+          <t>30d 143004 股, 最新日 468 股</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -505,12 +505,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>30d 136047 股, 最新日 250 股</t>
+          <t>30d 141537 股, 最新日 70 股</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -538,12 +538,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>30d 57065 股, 最新日 72 股</t>
+          <t>30d 55549 股, 最新日 800 股</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -571,12 +571,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>30d 174862 股, 最新日 95 股</t>
+          <t>30d 182138 股, 最新日 290 股</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -604,12 +604,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>30d 101982 股, 最新日 392 股</t>
+          <t>30d 85646 股, 最新日 1212 股</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -637,12 +637,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>30d 116565 股, 最新日 200 股</t>
+          <t>30d 156073 股, 最新日 1960 股</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -670,12 +670,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>30d 108509 股, 最新日 806 股</t>
+          <t>30d 109612 股, 最新日 340 股</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -703,12 +703,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>30d 101276 股, 最新日 52 股</t>
+          <t>30d 83220 股, 最新日 66 股</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -736,12 +736,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>30d 147451 股, 最新日 343 股</t>
+          <t>30d 100689 股, 最新日 1427 股</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -769,12 +769,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>30d 58354 股, 最新日 2088 股</t>
+          <t>30d 57669 股, 最新日 4500 股</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -802,12 +802,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>30d 228706 股, 最新日 663 股</t>
+          <t>30d 222865 股, 最新日 4 股</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -835,12 +835,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>30d 62780 股, 最新日 12 股</t>
+          <t>30d 54077 股, 最新日 16 股</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -861,7 +861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C102"/>
+  <dimension ref="A1:C103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,10 +888,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>228706</v>
+        <v>222865</v>
       </c>
       <c r="C2" t="n">
-        <v>663</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -901,36 +901,36 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>174862</v>
+        <v>182138</v>
       </c>
       <c r="C3" t="n">
-        <v>95</v>
+        <v>290</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>150096</v>
+        <v>156073</v>
       </c>
       <c r="C4" t="n">
-        <v>111</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>147451</v>
+        <v>143004</v>
       </c>
       <c r="C5" t="n">
-        <v>343</v>
+        <v>468</v>
       </c>
     </row>
     <row r="6">
@@ -940,36 +940,36 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>136047</v>
+        <v>141537</v>
       </c>
       <c r="C6" t="n">
-        <v>250</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>116565</v>
+        <v>109612</v>
       </c>
       <c r="C7" t="n">
-        <v>200</v>
+        <v>340</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>108509</v>
+        <v>100689</v>
       </c>
       <c r="C8" t="n">
-        <v>806</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="9">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>101982</v>
+        <v>85646</v>
       </c>
       <c r="C9" t="n">
-        <v>392</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="10">
@@ -992,49 +992,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>101276</v>
+        <v>83220</v>
       </c>
       <c r="C10" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>62780</v>
+        <v>57669</v>
       </c>
       <c r="C11" t="n">
-        <v>12</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>58354</v>
+        <v>55549</v>
       </c>
       <c r="C12" t="n">
-        <v>2088</v>
+        <v>800</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>57065</v>
+        <v>54077</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>44065</v>
+        <v>38994</v>
       </c>
       <c r="C14" t="n">
-        <v>556</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>42415</v>
+        <v>35749</v>
       </c>
       <c r="C15" t="n">
-        <v>120</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="16">
@@ -1070,166 +1070,166 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>31316</v>
+        <v>25549</v>
       </c>
       <c r="C16" t="n">
-        <v>450</v>
+        <v>154</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>29232</v>
+        <v>21306</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>20984</v>
+        <v>20723</v>
       </c>
       <c r="C18" t="n">
-        <v>131</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>20199</v>
+        <v>19444</v>
       </c>
       <c r="C19" t="n">
-        <v>116</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>19005</v>
+        <v>16857</v>
       </c>
       <c r="C20" t="n">
-        <v>1042</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16461</v>
+        <v>14987</v>
       </c>
       <c r="C21" t="n">
-        <v>322</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>15642</v>
+        <v>14424</v>
       </c>
       <c r="C22" t="n">
-        <v>638</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>11335</v>
+        <v>14142</v>
       </c>
       <c r="C23" t="n">
-        <v>28</v>
+        <v>116</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10499</v>
+        <v>13887</v>
       </c>
       <c r="C24" t="n">
-        <v>291</v>
+        <v>638</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10114</v>
+        <v>13400</v>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>500</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>10014</v>
+        <v>10177</v>
       </c>
       <c r="C26" t="n">
-        <v>12</v>
+        <v>65</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9422</v>
+        <v>10007</v>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>459</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>8265</v>
+        <v>9459</v>
       </c>
       <c r="C28" t="n">
-        <v>19</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29">
@@ -1239,179 +1239,179 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>8148</v>
+        <v>8723</v>
       </c>
       <c r="C29" t="n">
-        <v>59</v>
+        <v>149</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>8048</v>
+        <v>7796</v>
       </c>
       <c r="C30" t="n">
-        <v>40</v>
+        <v>155</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>7943</v>
+        <v>7579</v>
       </c>
       <c r="C31" t="n">
-        <v>409</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>7098</v>
+        <v>7544</v>
       </c>
       <c r="C32" t="n">
-        <v>4</v>
+        <v>65</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>6581</v>
+        <v>7488</v>
       </c>
       <c r="C33" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>6490</v>
+        <v>7071</v>
       </c>
       <c r="C34" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>6327</v>
+        <v>6525</v>
       </c>
       <c r="C35" t="n">
-        <v>5</v>
+        <v>711</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>6053</v>
+        <v>6488</v>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>93</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>5606</v>
+        <v>6182</v>
       </c>
       <c r="C37" t="n">
-        <v>54</v>
+        <v>718</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>5517</v>
+        <v>6089</v>
       </c>
       <c r="C38" t="n">
-        <v>319</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>5395</v>
+        <v>5977</v>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>5178</v>
+        <v>5220</v>
       </c>
       <c r="C40" t="n">
-        <v>44</v>
+        <v>99</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>5106</v>
+        <v>4932</v>
       </c>
       <c r="C41" t="n">
-        <v>6</v>
+        <v>43</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4383</v>
+        <v>4866</v>
       </c>
       <c r="C42" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="43">
@@ -1421,478 +1421,478 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4136</v>
+        <v>4691</v>
       </c>
       <c r="C43" t="n">
-        <v>62</v>
+        <v>324</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4120</v>
+        <v>4578</v>
       </c>
       <c r="C44" t="n">
-        <v>280</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3943</v>
+        <v>4489</v>
       </c>
       <c r="C45" t="n">
-        <v>126</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3787</v>
+        <v>4315</v>
       </c>
       <c r="C46" t="n">
-        <v>18</v>
+        <v>68</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3722</v>
+        <v>4039</v>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3709</v>
+        <v>3941</v>
       </c>
       <c r="C48" t="n">
-        <v>553</v>
+        <v>24</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3636</v>
+        <v>3926</v>
       </c>
       <c r="C49" t="n">
-        <v>5</v>
+        <v>837</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3557</v>
+        <v>3859</v>
       </c>
       <c r="C50" t="n">
-        <v>25</v>
+        <v>182</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3501</v>
+        <v>3811</v>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>126</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3284</v>
+        <v>3704</v>
       </c>
       <c r="C52" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3243</v>
+        <v>3541</v>
       </c>
       <c r="C53" t="n">
-        <v>10</v>
+        <v>51</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3173</v>
+        <v>3532</v>
       </c>
       <c r="C54" t="n">
-        <v>12</v>
+        <v>53</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2752</v>
+        <v>3084</v>
       </c>
       <c r="C55" t="n">
-        <v>395</v>
+        <v>655</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2717</v>
+        <v>2929</v>
       </c>
       <c r="C56" t="n">
-        <v>164</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2709</v>
+        <v>2833</v>
       </c>
       <c r="C57" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2657</v>
+        <v>2775</v>
       </c>
       <c r="C58" t="n">
-        <v>30</v>
+        <v>149</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2647</v>
+        <v>2768</v>
       </c>
       <c r="C59" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2563</v>
+        <v>2737</v>
       </c>
       <c r="C60" t="n">
-        <v>99</v>
+        <v>344</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2396</v>
+        <v>2737</v>
       </c>
       <c r="C61" t="n">
-        <v>243</v>
+        <v>349</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2371</v>
+        <v>2720</v>
       </c>
       <c r="C62" t="n">
-        <v>11</v>
+        <v>240</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2256</v>
+        <v>2674</v>
       </c>
       <c r="C63" t="n">
-        <v>21</v>
+        <v>253</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2209</v>
+        <v>2610</v>
       </c>
       <c r="C64" t="n">
-        <v>104</v>
+        <v>135</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2149</v>
+        <v>2567</v>
       </c>
       <c r="C65" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1903</v>
+        <v>2536</v>
       </c>
       <c r="C66" t="n">
-        <v>12</v>
+        <v>553</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1797</v>
+        <v>2424</v>
       </c>
       <c r="C67" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1768</v>
+        <v>2389</v>
       </c>
       <c r="C68" t="n">
-        <v>950</v>
+        <v>228</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1636</v>
+        <v>2350</v>
       </c>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1634</v>
+        <v>2090</v>
       </c>
       <c r="C70" t="n">
-        <v>648</v>
+        <v>74</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1483</v>
+        <v>2085</v>
       </c>
       <c r="C71" t="n">
-        <v>174</v>
+        <v>54</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1303</v>
+        <v>1895</v>
       </c>
       <c r="C72" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1203</v>
+        <v>1834</v>
       </c>
       <c r="C73" t="n">
-        <v>21</v>
+        <v>52</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1118</v>
+        <v>1722</v>
       </c>
       <c r="C74" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1057</v>
+        <v>1561</v>
       </c>
       <c r="C75" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1023</v>
+        <v>1324</v>
       </c>
       <c r="C76" t="n">
-        <v>549</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1007</v>
+        <v>1198</v>
       </c>
       <c r="C77" t="n">
-        <v>54</v>
+        <v>27</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1002</v>
+        <v>1181</v>
       </c>
       <c r="C78" t="n">
-        <v>6</v>
+        <v>118</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>992</v>
+        <v>1135</v>
       </c>
       <c r="C79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>977</v>
+        <v>990</v>
       </c>
       <c r="C80" t="n">
         <v>11</v>
@@ -1911,14 +1911,14 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>931</v>
+        <v>947</v>
       </c>
       <c r="C81" t="n">
-        <v>6</v>
+        <v>150</v>
       </c>
     </row>
     <row r="82">
@@ -1928,36 +1928,36 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>894</v>
+        <v>899</v>
       </c>
       <c r="C82" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>800</v>
+        <v>858</v>
       </c>
       <c r="C83" t="n">
-        <v>94</v>
+        <v>42</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>739</v>
+        <v>833</v>
       </c>
       <c r="C84" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85">
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>557</v>
+        <v>613</v>
       </c>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>107</v>
       </c>
     </row>
     <row r="86">
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="C86" t="n">
-        <v>124</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
@@ -1993,10 +1993,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>408</v>
+        <v>472</v>
       </c>
       <c r="C87" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="88">
@@ -2006,62 +2006,62 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>329</v>
+        <v>416</v>
       </c>
       <c r="C88" t="n">
-        <v>138</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>319</v>
+        <v>370</v>
       </c>
       <c r="C89" t="n">
-        <v>100</v>
+        <v>159</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>263</v>
+        <v>319</v>
       </c>
       <c r="C90" t="n">
-        <v>83</v>
+        <v>100</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>260</v>
+        <v>242</v>
       </c>
       <c r="C91" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>242</v>
+        <v>206</v>
       </c>
       <c r="C92" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="93">
@@ -2071,36 +2071,36 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>115</v>
+        <v>152</v>
       </c>
       <c r="C93" t="n">
-        <v>13</v>
+        <v>78</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="C94" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>59</v>
+        <v>113</v>
       </c>
       <c r="C95" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="96">
@@ -2110,75 +2110,75 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>50</v>
+        <v>109</v>
       </c>
       <c r="C96" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>49</v>
+        <v>83</v>
       </c>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="C98" t="n">
-        <v>36</v>
+        <v>73</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="C99" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="C100" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C101" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="102">
@@ -2188,9 +2188,22 @@
         </is>
       </c>
       <c r="B102" t="n">
+        <v>5</v>
+      </c>
+      <c r="C102" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>3188</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
         <v>2</v>
       </c>
-      <c r="C102" t="n">
+      <c r="C103" t="n">
         <v>2</v>
       </c>
     </row>

--- a/data/台股_警戒掃描.xlsx
+++ b/data/台股_警戒掃描.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,12 +472,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>30d 143004 股, 最新日 468 股</t>
+          <t>30d 137436 股, 最新日 122 股</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -505,12 +505,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>30d 141537 股, 最新日 70 股</t>
+          <t>30d 108637 股, 最新日 7 股</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -523,12 +523,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -538,30 +538,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>30d 55549 股, 最新日 800 股</t>
+          <t>30d 194285 股, 最新日 55 股</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -571,30 +571,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>30d 182138 股, 最新日 290 股</t>
+          <t>30d 82873 股, 最新日 171 股</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -604,12 +604,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>30d 85646 股, 最新日 1212 股</t>
+          <t>30d 146734 股, 最新日 342 股</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -622,12 +622,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -637,30 +637,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>30d 156073 股, 最新日 1960 股</t>
+          <t>30d 97879 股, 最新日 2000 股</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -670,12 +670,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>30d 109612 股, 最新日 340 股</t>
+          <t>30d 63160 股, 最新日 157 股</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -688,12 +688,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -703,30 +703,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>30d 83220 股, 最新日 66 股</t>
+          <t>30d 85567 股, 最新日 230 股</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -736,12 +736,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>30d 100689 股, 最新日 1427 股</t>
+          <t>30d 53448 股, 最新日 500 股</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -754,12 +754,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -769,30 +769,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>30d 57669 股, 最新日 4500 股</t>
+          <t>30d 230888 股, 最新日 353 股</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -802,49 +802,16 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>30d 222865 股, 最新日 4 股</t>
+          <t>30d 59298 股, 最新日 73 股</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>3711</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>日月光投控</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>🪦 借券爆量</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>30d 54077 股, 最新日 16 股</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -861,7 +828,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C103"/>
+  <dimension ref="A1:C102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,10 +855,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>222865</v>
+        <v>230888</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>353</v>
       </c>
     </row>
     <row r="3">
@@ -901,10 +868,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>182138</v>
+        <v>194285</v>
       </c>
       <c r="C3" t="n">
-        <v>290</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
@@ -914,10 +881,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>156073</v>
+        <v>146734</v>
       </c>
       <c r="C4" t="n">
-        <v>1960</v>
+        <v>342</v>
       </c>
     </row>
     <row r="5">
@@ -927,10 +894,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>143004</v>
+        <v>137436</v>
       </c>
       <c r="C5" t="n">
-        <v>468</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6">
@@ -940,10 +907,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>141537</v>
+        <v>108637</v>
       </c>
       <c r="C6" t="n">
-        <v>70</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -953,10 +920,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>109612</v>
+        <v>97879</v>
       </c>
       <c r="C7" t="n">
-        <v>340</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="8">
@@ -966,10 +933,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>100689</v>
+        <v>85567</v>
       </c>
       <c r="C8" t="n">
-        <v>1427</v>
+        <v>230</v>
       </c>
     </row>
     <row r="9">
@@ -979,10 +946,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>85646</v>
+        <v>82873</v>
       </c>
       <c r="C9" t="n">
-        <v>1212</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10">
@@ -992,49 +959,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>83220</v>
+        <v>63160</v>
       </c>
       <c r="C10" t="n">
-        <v>66</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>57669</v>
+        <v>59298</v>
       </c>
       <c r="C11" t="n">
-        <v>4500</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>55549</v>
+        <v>53448</v>
       </c>
       <c r="C12" t="n">
-        <v>800</v>
+        <v>500</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>54077</v>
+        <v>48189</v>
       </c>
       <c r="C13" t="n">
-        <v>16</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14">
@@ -1044,49 +1011,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>38994</v>
+        <v>35312</v>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>35749</v>
+        <v>24292</v>
       </c>
       <c r="C15" t="n">
-        <v>1435</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>25549</v>
+        <v>21363</v>
       </c>
       <c r="C16" t="n">
-        <v>154</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>21306</v>
+        <v>19921</v>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>820</v>
       </c>
     </row>
     <row r="18">
@@ -1096,504 +1063,504 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>20723</v>
+        <v>19431</v>
       </c>
       <c r="C18" t="n">
-        <v>95</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>19444</v>
+        <v>17648</v>
       </c>
       <c r="C19" t="n">
-        <v>102</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16857</v>
+        <v>16967</v>
       </c>
       <c r="C20" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14987</v>
+        <v>16503</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>108</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>14424</v>
+        <v>15880</v>
       </c>
       <c r="C22" t="n">
-        <v>100</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>14142</v>
+        <v>15086</v>
       </c>
       <c r="C23" t="n">
-        <v>116</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>13887</v>
+        <v>12303</v>
       </c>
       <c r="C24" t="n">
-        <v>638</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>13400</v>
+        <v>11238</v>
       </c>
       <c r="C25" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>10177</v>
+        <v>11045</v>
       </c>
       <c r="C26" t="n">
-        <v>65</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10007</v>
+        <v>10678</v>
       </c>
       <c r="C27" t="n">
-        <v>459</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>9459</v>
+        <v>10268</v>
       </c>
       <c r="C28" t="n">
-        <v>63</v>
+        <v>170</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>8723</v>
+        <v>9468</v>
       </c>
       <c r="C29" t="n">
-        <v>149</v>
+        <v>272</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>7796</v>
+        <v>9030</v>
       </c>
       <c r="C30" t="n">
-        <v>155</v>
+        <v>103</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>7579</v>
+        <v>8954</v>
       </c>
       <c r="C31" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>7544</v>
+        <v>8655</v>
       </c>
       <c r="C32" t="n">
-        <v>65</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7488</v>
+        <v>7399</v>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>7071</v>
+        <v>6665</v>
       </c>
       <c r="C34" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>6525</v>
+        <v>6407</v>
       </c>
       <c r="C35" t="n">
-        <v>711</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>6488</v>
+        <v>6276</v>
       </c>
       <c r="C36" t="n">
-        <v>93</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>6182</v>
+        <v>5986</v>
       </c>
       <c r="C37" t="n">
-        <v>718</v>
+        <v>40</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>6089</v>
+        <v>5712</v>
       </c>
       <c r="C38" t="n">
-        <v>30</v>
+        <v>118</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>5977</v>
+        <v>5331</v>
       </c>
       <c r="C39" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>5220</v>
+        <v>4955</v>
       </c>
       <c r="C40" t="n">
-        <v>99</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4932</v>
+        <v>4788</v>
       </c>
       <c r="C41" t="n">
-        <v>43</v>
+        <v>484</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4866</v>
+        <v>4759</v>
       </c>
       <c r="C42" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4691</v>
+        <v>4441</v>
       </c>
       <c r="C43" t="n">
-        <v>324</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4578</v>
+        <v>4273</v>
       </c>
       <c r="C44" t="n">
-        <v>19</v>
+        <v>50</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4489</v>
+        <v>4250</v>
       </c>
       <c r="C45" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4315</v>
+        <v>4246</v>
       </c>
       <c r="C46" t="n">
-        <v>68</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4039</v>
+        <v>4212</v>
       </c>
       <c r="C47" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3941</v>
+        <v>4114</v>
       </c>
       <c r="C48" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3926</v>
+        <v>3988</v>
       </c>
       <c r="C49" t="n">
-        <v>837</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3859</v>
+        <v>3903</v>
       </c>
       <c r="C50" t="n">
-        <v>182</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3811</v>
+        <v>3851</v>
       </c>
       <c r="C51" t="n">
-        <v>126</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3704</v>
+        <v>3761</v>
       </c>
       <c r="C52" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3541</v>
+        <v>3464</v>
       </c>
       <c r="C53" t="n">
-        <v>51</v>
+        <v>70</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3532</v>
+        <v>3360</v>
       </c>
       <c r="C54" t="n">
-        <v>53</v>
+        <v>20</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3084</v>
+        <v>3349</v>
       </c>
       <c r="C55" t="n">
-        <v>655</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2929</v>
+        <v>3119</v>
       </c>
       <c r="C56" t="n">
-        <v>3</v>
+        <v>80</v>
       </c>
     </row>
     <row r="57">
@@ -1603,88 +1570,88 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2833</v>
+        <v>3050</v>
       </c>
       <c r="C57" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2775</v>
+        <v>2991</v>
       </c>
       <c r="C58" t="n">
-        <v>149</v>
+        <v>120</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2768</v>
+        <v>2906</v>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>920</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2737</v>
+        <v>2844</v>
       </c>
       <c r="C60" t="n">
-        <v>344</v>
+        <v>30</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2737</v>
+        <v>2536</v>
       </c>
       <c r="C61" t="n">
-        <v>349</v>
+        <v>31</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2720</v>
+        <v>2517</v>
       </c>
       <c r="C62" t="n">
-        <v>240</v>
+        <v>15</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2674</v>
+        <v>2505</v>
       </c>
       <c r="C63" t="n">
-        <v>253</v>
+        <v>34</v>
       </c>
     </row>
     <row r="64">
@@ -1694,283 +1661,283 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2610</v>
+        <v>2481</v>
       </c>
       <c r="C64" t="n">
-        <v>135</v>
+        <v>79</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2567</v>
+        <v>2464</v>
       </c>
       <c r="C65" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2536</v>
+        <v>2318</v>
       </c>
       <c r="C66" t="n">
-        <v>553</v>
+        <v>96</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2424</v>
+        <v>2221</v>
       </c>
       <c r="C67" t="n">
-        <v>16</v>
+        <v>361</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2389</v>
+        <v>2196</v>
       </c>
       <c r="C68" t="n">
-        <v>228</v>
+        <v>32</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2350</v>
+        <v>2178</v>
       </c>
       <c r="C69" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2090</v>
+        <v>2042</v>
       </c>
       <c r="C70" t="n">
-        <v>74</v>
+        <v>9</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>2085</v>
+        <v>2030</v>
       </c>
       <c r="C71" t="n">
-        <v>54</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1895</v>
+        <v>1862</v>
       </c>
       <c r="C72" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1834</v>
+        <v>1838</v>
       </c>
       <c r="C73" t="n">
-        <v>52</v>
+        <v>11</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1722</v>
+        <v>1789</v>
       </c>
       <c r="C74" t="n">
-        <v>3</v>
+        <v>133</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1561</v>
+        <v>1778</v>
       </c>
       <c r="C75" t="n">
-        <v>39</v>
+        <v>16</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1324</v>
+        <v>1728</v>
       </c>
       <c r="C76" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1198</v>
+        <v>1586</v>
       </c>
       <c r="C77" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1181</v>
+        <v>1342</v>
       </c>
       <c r="C78" t="n">
-        <v>118</v>
+        <v>19</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1135</v>
+        <v>922</v>
       </c>
       <c r="C79" t="n">
-        <v>2</v>
+        <v>150</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>990</v>
+        <v>870</v>
       </c>
       <c r="C80" t="n">
-        <v>11</v>
+        <v>118</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>947</v>
+        <v>842</v>
       </c>
       <c r="C81" t="n">
-        <v>150</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>899</v>
+        <v>758</v>
       </c>
       <c r="C82" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>858</v>
+        <v>745</v>
       </c>
       <c r="C83" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>833</v>
+        <v>568</v>
       </c>
       <c r="C84" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>613</v>
+        <v>494</v>
       </c>
       <c r="C85" t="n">
-        <v>107</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -1980,7 +1947,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>505</v>
+        <v>441</v>
       </c>
       <c r="C86" t="n">
         <v>3</v>
@@ -1993,7 +1960,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>472</v>
+        <v>392</v>
       </c>
       <c r="C87" t="n">
         <v>26</v>
@@ -2002,118 +1969,118 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>416</v>
+        <v>369</v>
       </c>
       <c r="C88" t="n">
-        <v>5</v>
+        <v>159</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>370</v>
+        <v>342</v>
       </c>
       <c r="C89" t="n">
-        <v>159</v>
+        <v>242</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>319</v>
+        <v>293</v>
       </c>
       <c r="C90" t="n">
-        <v>100</v>
+        <v>159</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>242</v>
+        <v>212</v>
       </c>
       <c r="C91" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>206</v>
+        <v>116</v>
       </c>
       <c r="C92" t="n">
-        <v>20</v>
+        <v>78</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>152</v>
+        <v>109</v>
       </c>
       <c r="C93" t="n">
-        <v>78</v>
+        <v>59</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>150</v>
+        <v>97</v>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>113</v>
+        <v>87</v>
       </c>
       <c r="C95" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="C96" t="n">
-        <v>59</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97">
@@ -2123,87 +2090,74 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C97" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C98" t="n">
-        <v>73</v>
+        <v>50</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>78</v>
+        <v>39</v>
       </c>
       <c r="C99" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C100" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C101" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C102" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>3188</t>
-        </is>
-      </c>
-      <c r="B103" t="n">
-        <v>2</v>
-      </c>
-      <c r="C103" t="n">
         <v>2</v>
       </c>
     </row>

--- a/data/台股_警戒掃描.xlsx
+++ b/data/台股_警戒掃描.xlsx
@@ -457,12 +457,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -472,30 +472,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>30d 137436 股, 最新日 122 股</t>
+          <t>30d 68888 股, 最新日 1136 股</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -505,30 +505,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>30d 108637 股, 最新日 7 股</t>
+          <t>30d 106759 股, 最新日 1274 股</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -538,12 +538,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>30d 194285 股, 最新日 55 股</t>
+          <t>30d 81644 股, 最新日 93 股</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -556,12 +556,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -571,30 +571,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>30d 82873 股, 最新日 171 股</t>
+          <t>30d 151914 股, 最新日 1500 股</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -604,12 +604,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>30d 146734 股, 最新日 342 股</t>
+          <t>30d 71964 股, 最新日 1911 股</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -622,12 +622,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -637,30 +637,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>30d 97879 股, 最新日 2000 股</t>
+          <t>30d 127727 股, 最新日 25 股</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -670,12 +670,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>30d 63160 股, 最新日 157 股</t>
+          <t>30d 85024 股, 最新日 1200 股</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -703,12 +703,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>30d 85567 股, 最新日 230 股</t>
+          <t>30d 57034 股, 最新日 738 股</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -736,12 +736,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>30d 53448 股, 最新日 500 股</t>
+          <t>30d 55139 股, 最新日 2 股</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -769,12 +769,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>30d 230888 股, 最新日 353 股</t>
+          <t>30d 136131 股, 最新日 4630 股</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -802,12 +802,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>30d 59298 股, 最新日 73 股</t>
+          <t>30d 57239 股, 最新日 122 股</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -828,7 +828,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C102"/>
+  <dimension ref="A1:C100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -851,27 +851,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>230888</v>
+        <v>151914</v>
       </c>
       <c r="C2" t="n">
-        <v>353</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>194285</v>
+        <v>136131</v>
       </c>
       <c r="C3" t="n">
-        <v>55</v>
+        <v>4630</v>
       </c>
     </row>
     <row r="4">
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>146734</v>
+        <v>127727</v>
       </c>
       <c r="C4" t="n">
-        <v>342</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
@@ -894,88 +894,88 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>137436</v>
+        <v>106759</v>
       </c>
       <c r="C5" t="n">
-        <v>122</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>108637</v>
+        <v>85024</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>97879</v>
+        <v>81644</v>
       </c>
       <c r="C7" t="n">
-        <v>2000</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>85567</v>
+        <v>71964</v>
       </c>
       <c r="C8" t="n">
-        <v>230</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>82873</v>
+        <v>68888</v>
       </c>
       <c r="C9" t="n">
-        <v>171</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>63160</v>
+        <v>57239</v>
       </c>
       <c r="C10" t="n">
-        <v>157</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>59298</v>
+        <v>57034</v>
       </c>
       <c r="C11" t="n">
-        <v>73</v>
+        <v>738</v>
       </c>
     </row>
     <row r="12">
@@ -985,62 +985,62 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>53448</v>
+        <v>55139</v>
       </c>
       <c r="C12" t="n">
-        <v>500</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>48189</v>
+        <v>47202</v>
       </c>
       <c r="C13" t="n">
-        <v>147</v>
+        <v>618</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>35312</v>
+        <v>45212</v>
       </c>
       <c r="C14" t="n">
-        <v>3200</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24292</v>
+        <v>22494</v>
       </c>
       <c r="C15" t="n">
-        <v>130</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>21363</v>
+        <v>18550</v>
       </c>
       <c r="C16" t="n">
-        <v>59</v>
+        <v>424</v>
       </c>
     </row>
     <row r="17">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19921</v>
+        <v>17273</v>
       </c>
       <c r="C17" t="n">
-        <v>820</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18">
@@ -1063,153 +1063,153 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>19431</v>
+        <v>16704</v>
       </c>
       <c r="C18" t="n">
-        <v>61</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17648</v>
+        <v>15516</v>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16967</v>
+        <v>15496</v>
       </c>
       <c r="C20" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16503</v>
+        <v>15158</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>300</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>15880</v>
+        <v>13570</v>
       </c>
       <c r="C22" t="n">
-        <v>12</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>15086</v>
+        <v>12676</v>
       </c>
       <c r="C23" t="n">
-        <v>65</v>
+        <v>668</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>12303</v>
+        <v>11583</v>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>508</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>11238</v>
+        <v>11500</v>
       </c>
       <c r="C25" t="n">
-        <v>700</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>11045</v>
+        <v>11157</v>
       </c>
       <c r="C26" t="n">
-        <v>49</v>
+        <v>950</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10678</v>
+        <v>10682</v>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10268</v>
+        <v>9908</v>
       </c>
       <c r="C28" t="n">
-        <v>170</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>9468</v>
+        <v>9537</v>
       </c>
       <c r="C29" t="n">
-        <v>272</v>
+        <v>530</v>
       </c>
     </row>
     <row r="30">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>9030</v>
+        <v>8934</v>
       </c>
       <c r="C30" t="n">
-        <v>103</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31">
@@ -1232,62 +1232,62 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>8954</v>
+        <v>8610</v>
       </c>
       <c r="C31" t="n">
-        <v>26</v>
+        <v>213</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>8655</v>
+        <v>7779</v>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7399</v>
+        <v>7220</v>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>6665</v>
+        <v>6175</v>
       </c>
       <c r="C34" t="n">
-        <v>38</v>
+        <v>344</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>6407</v>
+        <v>5816</v>
       </c>
       <c r="C35" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="36">
@@ -1297,153 +1297,153 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>6276</v>
+        <v>5510</v>
       </c>
       <c r="C36" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>5986</v>
+        <v>5380</v>
       </c>
       <c r="C37" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>5712</v>
+        <v>5323</v>
       </c>
       <c r="C38" t="n">
-        <v>118</v>
+        <v>125</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>5331</v>
+        <v>4736</v>
       </c>
       <c r="C39" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4955</v>
+        <v>4431</v>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4788</v>
+        <v>4263</v>
       </c>
       <c r="C41" t="n">
-        <v>484</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4759</v>
+        <v>4179</v>
       </c>
       <c r="C42" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4441</v>
+        <v>4171</v>
       </c>
       <c r="C43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4273</v>
+        <v>3928</v>
       </c>
       <c r="C44" t="n">
-        <v>50</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4250</v>
+        <v>3835</v>
       </c>
       <c r="C45" t="n">
-        <v>25</v>
+        <v>51</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4246</v>
+        <v>3796</v>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4212</v>
+        <v>3737</v>
       </c>
       <c r="C47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4114</v>
+        <v>3695</v>
       </c>
       <c r="C48" t="n">
         <v>12</v>
@@ -1462,235 +1462,235 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3988</v>
+        <v>3626</v>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>39</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3903</v>
+        <v>3545</v>
       </c>
       <c r="C50" t="n">
-        <v>20</v>
+        <v>54</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3851</v>
+        <v>3305</v>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>502</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3761</v>
+        <v>3265</v>
       </c>
       <c r="C52" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3464</v>
+        <v>3194</v>
       </c>
       <c r="C53" t="n">
-        <v>70</v>
+        <v>150</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3360</v>
+        <v>3107</v>
       </c>
       <c r="C54" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3349</v>
+        <v>2961</v>
       </c>
       <c r="C55" t="n">
-        <v>4</v>
+        <v>58</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3119</v>
+        <v>2848</v>
       </c>
       <c r="C56" t="n">
-        <v>80</v>
+        <v>63</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3050</v>
+        <v>2757</v>
       </c>
       <c r="C57" t="n">
-        <v>26</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2991</v>
+        <v>2539</v>
       </c>
       <c r="C58" t="n">
-        <v>120</v>
+        <v>93</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2906</v>
+        <v>2489</v>
       </c>
       <c r="C59" t="n">
-        <v>920</v>
+        <v>20</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2844</v>
+        <v>2400</v>
       </c>
       <c r="C60" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2536</v>
+        <v>2337</v>
       </c>
       <c r="C61" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2517</v>
+        <v>2269</v>
       </c>
       <c r="C62" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2505</v>
+        <v>2089</v>
       </c>
       <c r="C63" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2481</v>
+        <v>2028</v>
       </c>
       <c r="C64" t="n">
-        <v>79</v>
+        <v>96</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2464</v>
+        <v>2022</v>
       </c>
       <c r="C65" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2318</v>
+        <v>1989</v>
       </c>
       <c r="C66" t="n">
-        <v>96</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67">
@@ -1700,23 +1700,23 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2221</v>
+        <v>1871</v>
       </c>
       <c r="C67" t="n">
-        <v>361</v>
+        <v>55</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2196</v>
+        <v>1843</v>
       </c>
       <c r="C68" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="69">
@@ -1726,75 +1726,75 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2178</v>
+        <v>1829</v>
       </c>
       <c r="C69" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2042</v>
+        <v>1616</v>
       </c>
       <c r="C70" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>2030</v>
+        <v>1548</v>
       </c>
       <c r="C71" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1862</v>
+        <v>1403</v>
       </c>
       <c r="C72" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1838</v>
+        <v>1393</v>
       </c>
       <c r="C73" t="n">
-        <v>11</v>
+        <v>150</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1789</v>
+        <v>1300</v>
       </c>
       <c r="C74" t="n">
-        <v>133</v>
+        <v>42</v>
       </c>
     </row>
     <row r="75">
@@ -1804,98 +1804,98 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1778</v>
+        <v>1176</v>
       </c>
       <c r="C75" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1728</v>
+        <v>1125</v>
       </c>
       <c r="C76" t="n">
-        <v>6</v>
+        <v>64</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1586</v>
+        <v>889</v>
       </c>
       <c r="C77" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1342</v>
+        <v>826</v>
       </c>
       <c r="C78" t="n">
-        <v>19</v>
+        <v>118</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>922</v>
+        <v>745</v>
       </c>
       <c r="C79" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>870</v>
+        <v>732</v>
       </c>
       <c r="C80" t="n">
-        <v>118</v>
+        <v>693</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>842</v>
+        <v>493</v>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>758</v>
+        <v>455</v>
       </c>
       <c r="C82" t="n">
         <v>3</v>
@@ -1904,14 +1904,14 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>745</v>
+        <v>345</v>
       </c>
       <c r="C83" t="n">
-        <v>3</v>
+        <v>103</v>
       </c>
     </row>
     <row r="84">
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>568</v>
+        <v>319</v>
       </c>
       <c r="C84" t="n">
         <v>27</v>
@@ -1930,131 +1930,131 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>494</v>
+        <v>291</v>
       </c>
       <c r="C85" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>441</v>
+        <v>286</v>
       </c>
       <c r="C86" t="n">
-        <v>3</v>
+        <v>159</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>392</v>
+        <v>264</v>
       </c>
       <c r="C87" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>369</v>
+        <v>255</v>
       </c>
       <c r="C88" t="n">
-        <v>159</v>
+        <v>41</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>342</v>
+        <v>222</v>
       </c>
       <c r="C89" t="n">
-        <v>242</v>
+        <v>150</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>293</v>
+        <v>186</v>
       </c>
       <c r="C90" t="n">
-        <v>159</v>
+        <v>27</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>212</v>
+        <v>169</v>
       </c>
       <c r="C91" t="n">
-        <v>10</v>
+        <v>87</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>116</v>
+        <v>159</v>
       </c>
       <c r="C92" t="n">
-        <v>78</v>
+        <v>159</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="C93" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C94" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95">
@@ -2064,101 +2064,75 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C95" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C96" t="n">
-        <v>3</v>
+        <v>78</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>59</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="C98" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="C99" t="n">
-        <v>39</v>
+        <v>7</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C100" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>5225</t>
-        </is>
-      </c>
-      <c r="B101" t="n">
-        <v>5</v>
-      </c>
-      <c r="C101" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>3188</t>
-        </is>
-      </c>
-      <c r="B102" t="n">
-        <v>2</v>
-      </c>
-      <c r="C102" t="n">
-        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data/台股_警戒掃描.xlsx
+++ b/data/台股_警戒掃描.xlsx
@@ -472,12 +472,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>30d 68888 股, 最新日 1136 股</t>
+          <t>30d 72798 股, 最新日 23 股</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -505,12 +505,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>30d 106759 股, 最新日 1274 股</t>
+          <t>30d 94442 股, 最新日 901 股</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -538,12 +538,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>30d 81644 股, 最新日 93 股</t>
+          <t>30d 80639 股, 最新日 2948 股</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -571,12 +571,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>30d 151914 股, 最新日 1500 股</t>
+          <t>30d 155618 股, 最新日 392 股</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -604,12 +604,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>30d 71964 股, 最新日 1911 股</t>
+          <t>30d 86111 股, 最新日 150 股</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -637,12 +637,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>30d 127727 股, 最新日 25 股</t>
+          <t>30d 137246 股, 最新日 150 股</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -670,12 +670,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>30d 85024 股, 最新日 1200 股</t>
+          <t>30d 90537 股, 最新日 4000 股</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -703,12 +703,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>30d 57034 股, 最新日 738 股</t>
+          <t>30d 89933 股, 最新日 295 股</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -736,12 +736,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>30d 55139 股, 最新日 2 股</t>
+          <t>30d 61819 股, 最新日 3 股</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -769,12 +769,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>30d 136131 股, 最新日 4630 股</t>
+          <t>30d 105507 股, 最新日 250 股</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -802,12 +802,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>30d 57239 股, 最新日 122 股</t>
+          <t>30d 56415 股, 最新日 541 股</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -855,36 +855,36 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>151914</v>
+        <v>155618</v>
       </c>
       <c r="C2" t="n">
-        <v>1500</v>
+        <v>392</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>136131</v>
+        <v>137246</v>
       </c>
       <c r="C3" t="n">
-        <v>4630</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>127727</v>
+        <v>105507</v>
       </c>
       <c r="C4" t="n">
-        <v>25</v>
+        <v>250</v>
       </c>
     </row>
     <row r="5">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>106759</v>
+        <v>94442</v>
       </c>
       <c r="C5" t="n">
-        <v>1274</v>
+        <v>901</v>
       </c>
     </row>
     <row r="6">
@@ -907,23 +907,23 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>85024</v>
+        <v>90537</v>
       </c>
       <c r="C6" t="n">
-        <v>1200</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>81644</v>
+        <v>89933</v>
       </c>
       <c r="C7" t="n">
-        <v>93</v>
+        <v>295</v>
       </c>
     </row>
     <row r="8">
@@ -933,140 +933,140 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>71964</v>
+        <v>86111</v>
       </c>
       <c r="C8" t="n">
-        <v>1911</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>68888</v>
+        <v>80639</v>
       </c>
       <c r="C9" t="n">
-        <v>1136</v>
+        <v>2948</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>57239</v>
+        <v>72798</v>
       </c>
       <c r="C10" t="n">
-        <v>122</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>57034</v>
+        <v>61819</v>
       </c>
       <c r="C11" t="n">
-        <v>738</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>55139</v>
+        <v>56415</v>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>541</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>47202</v>
+        <v>42024</v>
       </c>
       <c r="C13" t="n">
-        <v>618</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>45212</v>
+        <v>38737</v>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>341</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22494</v>
+        <v>21777</v>
       </c>
       <c r="C15" t="n">
-        <v>1053</v>
+        <v>491</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18550</v>
+        <v>19750</v>
       </c>
       <c r="C16" t="n">
-        <v>424</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17273</v>
+        <v>18120</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16704</v>
+        <v>16076</v>
       </c>
       <c r="C18" t="n">
-        <v>38</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -1076,101 +1076,101 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15516</v>
+        <v>16000</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>15496</v>
+        <v>15628</v>
       </c>
       <c r="C20" t="n">
-        <v>9</v>
+        <v>422</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15158</v>
+        <v>15415</v>
       </c>
       <c r="C21" t="n">
-        <v>300</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>13570</v>
+        <v>13795</v>
       </c>
       <c r="C22" t="n">
-        <v>2384</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>12676</v>
+        <v>13468</v>
       </c>
       <c r="C23" t="n">
-        <v>668</v>
+        <v>730</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>11583</v>
+        <v>11744</v>
       </c>
       <c r="C24" t="n">
-        <v>508</v>
+        <v>794</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>11500</v>
+        <v>10912</v>
       </c>
       <c r="C25" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>11157</v>
+        <v>10888</v>
       </c>
       <c r="C26" t="n">
-        <v>950</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27">
@@ -1180,114 +1180,114 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10682</v>
+        <v>10659</v>
       </c>
       <c r="C27" t="n">
-        <v>51</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>9908</v>
+        <v>10530</v>
       </c>
       <c r="C28" t="n">
-        <v>60</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>9537</v>
+        <v>10363</v>
       </c>
       <c r="C29" t="n">
-        <v>530</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>8934</v>
+        <v>10019</v>
       </c>
       <c r="C30" t="n">
-        <v>292</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>8610</v>
+        <v>9909</v>
       </c>
       <c r="C31" t="n">
-        <v>213</v>
+        <v>256</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>7779</v>
+        <v>9029</v>
       </c>
       <c r="C32" t="n">
-        <v>13</v>
+        <v>74</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7220</v>
+        <v>8589</v>
       </c>
       <c r="C33" t="n">
-        <v>100</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>6175</v>
+        <v>6563</v>
       </c>
       <c r="C34" t="n">
-        <v>344</v>
+        <v>192</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>5816</v>
+        <v>6495</v>
       </c>
       <c r="C35" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -1297,36 +1297,36 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>5510</v>
+        <v>6268</v>
       </c>
       <c r="C36" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>5380</v>
+        <v>5748</v>
       </c>
       <c r="C37" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>5323</v>
+        <v>5290</v>
       </c>
       <c r="C38" t="n">
-        <v>125</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -1336,7 +1336,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4736</v>
+        <v>5218</v>
       </c>
       <c r="C39" t="n">
         <v>50</v>
@@ -1345,105 +1345,105 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4431</v>
+        <v>5176</v>
       </c>
       <c r="C40" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4263</v>
+        <v>4743</v>
       </c>
       <c r="C41" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4179</v>
+        <v>4551</v>
       </c>
       <c r="C42" t="n">
-        <v>120</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4171</v>
+        <v>4511</v>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3928</v>
+        <v>4467</v>
       </c>
       <c r="C44" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3835</v>
+        <v>4439</v>
       </c>
       <c r="C45" t="n">
-        <v>51</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3796</v>
+        <v>4395</v>
       </c>
       <c r="C46" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3737</v>
+        <v>4160</v>
       </c>
       <c r="C47" t="n">
-        <v>3</v>
+        <v>219</v>
       </c>
     </row>
     <row r="48">
@@ -1453,23 +1453,23 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3695</v>
+        <v>4134</v>
       </c>
       <c r="C48" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3626</v>
+        <v>4117</v>
       </c>
       <c r="C49" t="n">
-        <v>39</v>
+        <v>130</v>
       </c>
     </row>
     <row r="50">
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3545</v>
+        <v>3590</v>
       </c>
       <c r="C50" t="n">
-        <v>54</v>
+        <v>307</v>
       </c>
     </row>
     <row r="51">
@@ -1492,270 +1492,270 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3305</v>
+        <v>3582</v>
       </c>
       <c r="C51" t="n">
-        <v>502</v>
+        <v>257</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3265</v>
+        <v>3311</v>
       </c>
       <c r="C52" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3194</v>
+        <v>3253</v>
       </c>
       <c r="C53" t="n">
-        <v>150</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3107</v>
+        <v>3230</v>
       </c>
       <c r="C54" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2961</v>
+        <v>2869</v>
       </c>
       <c r="C55" t="n">
-        <v>58</v>
+        <v>414</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2848</v>
+        <v>2809</v>
       </c>
       <c r="C56" t="n">
-        <v>63</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2757</v>
+        <v>2804</v>
       </c>
       <c r="C57" t="n">
-        <v>322</v>
+        <v>300</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2539</v>
+        <v>2610</v>
       </c>
       <c r="C58" t="n">
-        <v>93</v>
+        <v>113</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2489</v>
+        <v>2474</v>
       </c>
       <c r="C59" t="n">
-        <v>20</v>
+        <v>88</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2400</v>
+        <v>2459</v>
       </c>
       <c r="C60" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2337</v>
+        <v>2320</v>
       </c>
       <c r="C61" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2269</v>
+        <v>2246</v>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>91</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2089</v>
+        <v>2194</v>
       </c>
       <c r="C63" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2028</v>
+        <v>2192</v>
       </c>
       <c r="C64" t="n">
-        <v>96</v>
+        <v>11</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2022</v>
+        <v>2160</v>
       </c>
       <c r="C65" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1989</v>
+        <v>2120</v>
       </c>
       <c r="C66" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1871</v>
+        <v>1939</v>
       </c>
       <c r="C67" t="n">
-        <v>55</v>
+        <v>150</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1843</v>
+        <v>1928</v>
       </c>
       <c r="C68" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1829</v>
+        <v>1799</v>
       </c>
       <c r="C69" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1616</v>
+        <v>1744</v>
       </c>
       <c r="C70" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1548</v>
+        <v>1514</v>
       </c>
       <c r="C71" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
     </row>
     <row r="72">
@@ -1765,166 +1765,166 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1403</v>
+        <v>1371</v>
       </c>
       <c r="C72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1393</v>
+        <v>1250</v>
       </c>
       <c r="C73" t="n">
-        <v>150</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1300</v>
+        <v>1055</v>
       </c>
       <c r="C74" t="n">
-        <v>42</v>
+        <v>150</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1176</v>
+        <v>872</v>
       </c>
       <c r="C75" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1125</v>
+        <v>867</v>
       </c>
       <c r="C76" t="n">
-        <v>64</v>
+        <v>17</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>889</v>
+        <v>853</v>
       </c>
       <c r="C77" t="n">
-        <v>1</v>
+        <v>502</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>826</v>
+        <v>761</v>
       </c>
       <c r="C78" t="n">
-        <v>118</v>
+        <v>90</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>745</v>
+        <v>693</v>
       </c>
       <c r="C79" t="n">
-        <v>6</v>
+        <v>693</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>732</v>
+        <v>585</v>
       </c>
       <c r="C80" t="n">
-        <v>693</v>
+        <v>69</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>493</v>
+        <v>532</v>
       </c>
       <c r="C81" t="n">
-        <v>8</v>
+        <v>50</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>455</v>
+        <v>530</v>
       </c>
       <c r="C82" t="n">
-        <v>3</v>
+        <v>132</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>345</v>
+        <v>415</v>
       </c>
       <c r="C83" t="n">
-        <v>103</v>
+        <v>189</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>319</v>
+        <v>402</v>
       </c>
       <c r="C84" t="n">
-        <v>27</v>
+        <v>125</v>
       </c>
     </row>
     <row r="85">
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>291</v>
+        <v>373</v>
       </c>
       <c r="C85" t="n">
         <v>26</v>
@@ -1943,53 +1943,53 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>286</v>
+        <v>370</v>
       </c>
       <c r="C86" t="n">
-        <v>159</v>
+        <v>8</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>264</v>
+        <v>345</v>
       </c>
       <c r="C87" t="n">
-        <v>3</v>
+        <v>103</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C88" t="n">
-        <v>41</v>
+        <v>89</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C89" t="n">
-        <v>150</v>
+        <v>94</v>
       </c>
     </row>
     <row r="90">
@@ -1999,36 +1999,36 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>186</v>
+        <v>222</v>
       </c>
       <c r="C90" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>169</v>
+        <v>211</v>
       </c>
       <c r="C91" t="n">
-        <v>87</v>
+        <v>24</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>159</v>
+        <v>203</v>
       </c>
       <c r="C92" t="n">
-        <v>159</v>
+        <v>100</v>
       </c>
     </row>
     <row r="93">
@@ -2038,7 +2038,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C93" t="n">
         <v>1</v>
@@ -2047,14 +2047,14 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C94" t="n">
-        <v>3</v>
+        <v>61</v>
       </c>
     </row>
     <row r="95">
@@ -2064,75 +2064,75 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="C96" t="n">
-        <v>78</v>
+        <v>59</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="C97" t="n">
-        <v>59</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="C98" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="C99" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C100" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
